--- a/Datasets/primary_info.xlsx
+++ b/Datasets/primary_info.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniofleicester-my.sharepoint.com/personal/crn4_leicester_ac_uk/Documents/PhD/WP2/3. Create tool/Datasets/Chronic rhinosinusitis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniofleicester-my.sharepoint.com/personal/crn4_leicester_ac_uk/Documents/PhD/WP2/3. Create tool/Datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="154" documentId="8_{E5D5BD41-529D-4D09-876A-F6CD97CB8226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E4CC3F2-6E04-46BF-9ABF-2CE20039E87A}"/>
+  <xr:revisionPtr revIDLastSave="175" documentId="13_ncr:1_{009773F8-B678-42EB-90F1-9F0C232CDCBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{822D7B83-ECDF-49B6-A4B0-022AF6B2BE2D}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E19E56DC-86BE-4713-A769-C66B74D62B61}"/>
+    <workbookView xWindow="-4290" yWindow="2370" windowWidth="8535" windowHeight="4530" xr2:uid="{E19E56DC-86BE-4713-A769-C66B74D62B61}"/>
   </bookViews>
   <sheets>
     <sheet name="Studies" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="106">
   <si>
     <t>Study</t>
   </si>
@@ -220,9 +220,6 @@
     <t>Not applicable</t>
   </si>
   <si>
-    <t>Covalescent plasma</t>
-  </si>
-  <si>
     <t>Ivermectin COVID-19</t>
   </si>
   <si>
@@ -235,9 +232,6 @@
     <t>Krolewiecki 2021</t>
   </si>
   <si>
-    <t>Ivermectin COVID-20</t>
-  </si>
-  <si>
     <t>Non-small cell lung cancer</t>
   </si>
   <si>
@@ -277,9 +271,6 @@
     <t>Wang 2020</t>
   </si>
   <si>
-    <t>Systemic coricosteroids COVID-19</t>
-  </si>
-  <si>
     <t>Corral-Gudino 2021</t>
   </si>
   <si>
@@ -308,6 +299,63 @@
   </si>
   <si>
     <t>Angus 2020b</t>
+  </si>
+  <si>
+    <t>Rob_tool</t>
+  </si>
+  <si>
+    <t>Systemic corticosteroids COVID-19</t>
+  </si>
+  <si>
+    <t>Outcome</t>
+  </si>
+  <si>
+    <t>QoL</t>
+  </si>
+  <si>
+    <t>VAS</t>
+  </si>
+  <si>
+    <t>Avoidance</t>
+  </si>
+  <si>
+    <t>SAEs</t>
+  </si>
+  <si>
+    <t>AEs</t>
+  </si>
+  <si>
+    <t>Mortality</t>
+  </si>
+  <si>
+    <t>Worsening</t>
+  </si>
+  <si>
+    <t>Improvement</t>
+  </si>
+  <si>
+    <t>Viral clearance</t>
+  </si>
+  <si>
+    <t>Mohan 2021</t>
+  </si>
+  <si>
+    <t>Pott-Junior 2021</t>
+  </si>
+  <si>
+    <t>Survival</t>
+  </si>
+  <si>
+    <t>WHO Solidarity France 2021</t>
+  </si>
+  <si>
+    <t>Mortality30</t>
+  </si>
+  <si>
+    <t>Mortality120</t>
+  </si>
+  <si>
+    <t>Edalatifard 2020</t>
   </si>
 </sst>
 </file>
@@ -349,9 +397,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -666,27 +715,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FF7956F-2BD5-4B54-899A-FD221CF1CF1D}">
-  <dimension ref="A1:W48"/>
+  <dimension ref="A1:X105"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.54296875" customWidth="1"/>
-    <col min="7" max="7" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.6328125" customWidth="1"/>
-    <col min="11" max="11" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.6328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.54296875" customWidth="1"/>
+    <col min="8" max="8" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.6328125" customWidth="1"/>
+    <col min="12" max="12" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.6328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -694,118 +744,121 @@
         <v>34</v>
       </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>30</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>32</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>7</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>8</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>9</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>10</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>20</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" t="s">
-        <v>73</v>
-      </c>
       <c r="W1" t="s">
+        <v>71</v>
+      </c>
+      <c r="X1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>15</v>
       </c>
       <c r="B2" s="1">
         <v>44256</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>12.8</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2">
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2">
         <v>30</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>30.2</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>19.600000000000001</v>
       </c>
-      <c r="J2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2">
         <v>30</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>13.213193</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>-17.399999999999999</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>-25.442701</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>-9.3572989999999994</v>
       </c>
-      <c r="P2" t="s">
-        <v>22</v>
-      </c>
       <c r="Q2" t="s">
         <v>22</v>
       </c>
@@ -816,61 +869,67 @@
         <v>22</v>
       </c>
       <c r="T2" t="s">
+        <v>22</v>
+      </c>
+      <c r="U2" t="s">
         <v>24</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="W2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="1">
         <v>44256</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>18.579999999999998</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>14.92</v>
       </c>
-      <c r="F3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3">
+      <c r="G3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3">
         <v>143</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>40.49</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>23.06</v>
       </c>
-      <c r="J3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3">
         <v>133</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>40.053310000000003</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>-21.91</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>-26.529411</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>-17.290589000000001</v>
       </c>
-      <c r="P3" t="s">
-        <v>22</v>
-      </c>
       <c r="Q3" t="s">
         <v>22</v>
       </c>
@@ -881,61 +940,67 @@
         <v>22</v>
       </c>
       <c r="T3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="V3" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="1">
         <v>44256</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" t="s">
         <v>13</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>23.89</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>18.77</v>
       </c>
-      <c r="F4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4">
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4">
         <v>295</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>42.16</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>23.36</v>
       </c>
-      <c r="J4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4">
         <v>153</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>46.733497</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>-18.27</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>-22.546531999999999</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>-13.993468</v>
       </c>
-      <c r="P4" t="s">
-        <v>22</v>
-      </c>
       <c r="Q4" t="s">
         <v>22</v>
       </c>
@@ -946,1224 +1011,1302 @@
         <v>22</v>
       </c>
       <c r="T4" t="s">
+        <v>22</v>
+      </c>
+      <c r="U4" t="s">
         <v>24</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="W4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>35</v>
       </c>
       <c r="B5" s="1">
         <v>44317</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" t="s">
         <v>36</v>
       </c>
-      <c r="D5" t="s">
-        <v>31</v>
-      </c>
       <c r="E5" t="s">
         <v>31</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5">
         <v>34</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>235</v>
       </c>
-      <c r="H5" t="s">
-        <v>31</v>
-      </c>
       <c r="I5" t="s">
         <v>31</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="s">
         <v>31</v>
       </c>
       <c r="K5">
+        <v>31</v>
+      </c>
+      <c r="L5">
         <v>229</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>1.527301</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>1.0687709999999999</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>0.68051099999999998</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>1.67855</v>
       </c>
-      <c r="W5" t="s">
+      <c r="X5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="1">
         <v>44317</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" t="s">
         <v>37</v>
       </c>
-      <c r="D6" t="s">
-        <v>31</v>
-      </c>
       <c r="E6" t="s">
         <v>31</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>20</v>
       </c>
-      <c r="H6" t="s">
-        <v>31</v>
-      </c>
       <c r="I6" t="s">
         <v>31</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6">
         <v>2</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>20</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>5.8058999999999999E-2</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>0.5</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>4.9182999999999998E-2</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>5.0830599999999997</v>
       </c>
-      <c r="W6" t="s">
+      <c r="X6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>35</v>
       </c>
       <c r="B7" s="1">
         <v>44317</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D7" t="s">
         <v>38</v>
       </c>
-      <c r="D7" t="s">
-        <v>31</v>
-      </c>
       <c r="E7" t="s">
         <v>31</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7">
         <v>7</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>179</v>
       </c>
-      <c r="H7" t="s">
-        <v>31</v>
-      </c>
       <c r="I7" t="s">
         <v>31</v>
       </c>
-      <c r="J7">
+      <c r="J7" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7">
         <v>14</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>171</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>0.40039599999999997</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>0.47765400000000002</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>0.197579</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>1.154744</v>
       </c>
-      <c r="W7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>35</v>
       </c>
       <c r="B8" s="1">
         <v>44958</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" t="s">
         <v>39</v>
       </c>
-      <c r="D8" t="s">
-        <v>31</v>
-      </c>
       <c r="E8" t="s">
         <v>31</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8">
         <v>2</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>17</v>
       </c>
-      <c r="H8" t="s">
-        <v>31</v>
-      </c>
       <c r="I8" t="s">
         <v>31</v>
       </c>
-      <c r="J8">
+      <c r="J8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8">
         <v>3</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>14</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>0.115594</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>0.54901999999999995</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>0.10613400000000001</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>2.8400099999999999</v>
       </c>
-      <c r="W8" t="s">
+      <c r="X8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>35</v>
       </c>
       <c r="B9" s="1">
         <v>44958</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" t="s">
         <v>40</v>
       </c>
-      <c r="D9" t="s">
-        <v>31</v>
-      </c>
       <c r="E9" t="s">
         <v>31</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9">
         <v>10</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>69</v>
       </c>
-      <c r="H9" t="s">
-        <v>31</v>
-      </c>
       <c r="I9" t="s">
         <v>31</v>
       </c>
-      <c r="J9">
+      <c r="J9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9">
         <v>8</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>67</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>0.415265</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>1.213768</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>0.51014700000000002</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>2.8878629999999998</v>
       </c>
-      <c r="W9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>35</v>
       </c>
       <c r="B10" s="1">
         <v>44958</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" t="s">
         <v>41</v>
       </c>
-      <c r="D10" t="s">
-        <v>31</v>
-      </c>
       <c r="E10" t="s">
         <v>31</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10">
         <v>5</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>257</v>
       </c>
-      <c r="H10" t="s">
-        <v>31</v>
-      </c>
       <c r="I10" t="s">
         <v>31</v>
       </c>
-      <c r="J10">
+      <c r="J10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10">
         <v>1</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>254</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>6.8178000000000002E-2</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>4.9416339999999996</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>0.58139600000000002</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>42.001891000000001</v>
       </c>
-      <c r="W10" t="s">
+      <c r="X10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>35</v>
       </c>
       <c r="B11" s="1">
         <v>44958</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" t="s">
         <v>42</v>
       </c>
-      <c r="D11" t="s">
-        <v>31</v>
-      </c>
       <c r="E11" t="s">
         <v>31</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11">
         <v>14</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>231</v>
       </c>
-      <c r="H11" t="s">
-        <v>31</v>
-      </c>
       <c r="I11" t="s">
         <v>31</v>
       </c>
-      <c r="J11">
+      <c r="J11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11">
         <v>19</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>240</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>0.70235199999999998</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>0.76554999999999995</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>0.39319599999999999</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>1.4905200000000001</v>
       </c>
-      <c r="W11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>35</v>
       </c>
       <c r="B12" s="1">
         <v>44317</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" t="s">
         <v>43</v>
       </c>
-      <c r="D12" t="s">
-        <v>31</v>
-      </c>
       <c r="E12" t="s">
         <v>31</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12">
         <v>25</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>228</v>
       </c>
-      <c r="H12" t="s">
-        <v>31</v>
-      </c>
       <c r="I12" t="s">
         <v>31</v>
       </c>
-      <c r="J12">
+      <c r="J12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12">
         <v>12</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>105</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>0.74170499999999995</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>0.95943000000000001</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>0.50169799999999998</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>1.834781</v>
       </c>
-      <c r="W12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>35</v>
       </c>
       <c r="B13" s="1">
         <v>44958</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" t="s">
         <v>44</v>
       </c>
-      <c r="D13" t="s">
-        <v>31</v>
-      </c>
       <c r="E13" t="s">
         <v>31</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13">
         <v>2</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>40</v>
       </c>
-      <c r="H13" t="s">
-        <v>31</v>
-      </c>
       <c r="I13" t="s">
         <v>31</v>
       </c>
-      <c r="J13">
+      <c r="J13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13">
         <v>10</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>39</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>0.147929</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>0.19500000000000001</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>4.5617999999999999E-2</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>0.83355599999999996</v>
       </c>
-      <c r="W13" t="s">
+      <c r="X13" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>35</v>
       </c>
       <c r="B14" s="1">
         <v>44958</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" t="s">
         <v>45</v>
       </c>
-      <c r="D14" t="s">
-        <v>31</v>
-      </c>
       <c r="E14" t="s">
         <v>31</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14">
         <v>8</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>36</v>
       </c>
-      <c r="H14" t="s">
-        <v>31</v>
-      </c>
       <c r="I14" t="s">
         <v>31</v>
       </c>
-      <c r="J14">
+      <c r="J14" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14">
         <v>18</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>71</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>0.58537700000000004</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>0.87654299999999996</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>0.42244700000000002</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>1.818754</v>
       </c>
-      <c r="W14" t="s">
+      <c r="X14" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="1">
         <v>44958</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" t="s">
         <v>46</v>
       </c>
-      <c r="D15" t="s">
-        <v>31</v>
-      </c>
       <c r="E15" t="s">
         <v>31</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15">
         <v>352</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>1074</v>
       </c>
-      <c r="H15" t="s">
-        <v>31</v>
-      </c>
       <c r="I15" t="s">
         <v>31</v>
       </c>
-      <c r="J15">
+      <c r="J15" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15">
         <v>300</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>904</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>18.837778</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>0.98760999999999999</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>0.87063699999999999</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>1.1202989999999999</v>
       </c>
-      <c r="W15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>35</v>
       </c>
       <c r="B16" s="1">
         <v>44317</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" t="s">
         <v>47</v>
       </c>
-      <c r="D16" t="s">
-        <v>31</v>
-      </c>
       <c r="E16" t="s">
         <v>31</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16">
         <v>8</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>51</v>
       </c>
-      <c r="H16" t="s">
-        <v>31</v>
-      </c>
       <c r="I16" t="s">
         <v>31</v>
       </c>
-      <c r="J16">
+      <c r="J16" t="s">
+        <v>31</v>
+      </c>
+      <c r="K16">
         <v>12</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>50</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>0.48129300000000003</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>0.65359500000000004</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>0.29219099999999998</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>1.462008</v>
       </c>
-      <c r="W16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>35</v>
       </c>
       <c r="B17" s="1">
         <v>44958</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" t="s">
         <v>48</v>
       </c>
-      <c r="D17" t="s">
-        <v>31</v>
-      </c>
       <c r="E17" t="s">
         <v>31</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17">
         <v>141</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>614</v>
       </c>
-      <c r="H17" t="s">
-        <v>31</v>
-      </c>
       <c r="I17" t="s">
         <v>31</v>
       </c>
-      <c r="J17">
+      <c r="J17" t="s">
+        <v>31</v>
+      </c>
+      <c r="K17">
         <v>63</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>307</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>4.4525050000000004</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>1.119048</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>0.85979899999999998</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>1.456466</v>
       </c>
-      <c r="W17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>35</v>
       </c>
       <c r="B18" s="1">
         <v>44958</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" t="s">
         <v>49</v>
       </c>
-      <c r="D18" t="s">
-        <v>31</v>
-      </c>
       <c r="E18" t="s">
         <v>31</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18">
         <v>29</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>320</v>
       </c>
-      <c r="H18" t="s">
-        <v>31</v>
-      </c>
       <c r="I18" t="s">
         <v>31</v>
       </c>
-      <c r="J18">
+      <c r="J18" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18">
         <v>14</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>163</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>0.83953800000000001</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>1.055134</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>0.57369300000000001</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>1.9406000000000001</v>
       </c>
-      <c r="W18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>35</v>
       </c>
       <c r="B19" s="1">
         <v>44958</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" t="s">
         <v>50</v>
       </c>
-      <c r="D19" t="s">
-        <v>31</v>
-      </c>
       <c r="E19" t="s">
         <v>31</v>
       </c>
-      <c r="F19">
+      <c r="F19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19">
         <v>6</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>43</v>
       </c>
-      <c r="H19" t="s">
-        <v>31</v>
-      </c>
       <c r="I19" t="s">
         <v>31</v>
       </c>
-      <c r="J19">
+      <c r="J19" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19">
         <v>11</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>43</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>0.38482899999999998</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>0.54545500000000002</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>0.221667</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>1.3421940000000001</v>
       </c>
-      <c r="W19" t="s">
+      <c r="X19" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>35</v>
       </c>
       <c r="B20" s="1">
         <v>44317</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" t="s">
         <v>51</v>
       </c>
-      <c r="D20" t="s">
-        <v>31</v>
-      </c>
       <c r="E20" t="s">
         <v>31</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20">
         <v>1399</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>5795</v>
       </c>
-      <c r="H20" t="s">
-        <v>31</v>
-      </c>
       <c r="I20" t="s">
         <v>31</v>
       </c>
-      <c r="J20">
+      <c r="J20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K20">
         <v>1408</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>5763</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>64.652202000000003</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>0.98812100000000003</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>0.92651099999999997</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>1.053828</v>
       </c>
-      <c r="W20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>35</v>
       </c>
       <c r="B21" s="1">
         <v>44958</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" t="s">
         <v>52</v>
       </c>
-      <c r="D21" t="s">
-        <v>31</v>
-      </c>
       <c r="E21" t="s">
         <v>31</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="s">
+        <v>31</v>
+      </c>
+      <c r="G21">
         <v>8</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>53</v>
       </c>
-      <c r="H21" t="s">
-        <v>31</v>
-      </c>
       <c r="I21" t="s">
         <v>31</v>
       </c>
-      <c r="J21">
+      <c r="J21" t="s">
+        <v>31</v>
+      </c>
+      <c r="K21">
         <v>14</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>52</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>0.51285800000000004</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>0.56064700000000001</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>0.25703399999999998</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>1.222893</v>
       </c>
-      <c r="W21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>35</v>
       </c>
       <c r="B22" s="1">
         <v>44958</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" t="s">
         <v>53</v>
       </c>
-      <c r="D22" t="s">
-        <v>31</v>
-      </c>
       <c r="E22" t="s">
         <v>31</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22">
         <v>59</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>462</v>
       </c>
-      <c r="H22" t="s">
-        <v>31</v>
-      </c>
       <c r="I22" t="s">
         <v>31</v>
       </c>
-      <c r="J22">
+      <c r="J22" t="s">
+        <v>31</v>
+      </c>
+      <c r="K22">
         <v>71</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>462</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>3.0239199999999999</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>0.830986</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>0.60324500000000003</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>1.1447039999999999</v>
       </c>
-      <c r="W22" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>35</v>
       </c>
       <c r="B23" s="1">
         <v>44317</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" t="s">
         <v>54</v>
       </c>
-      <c r="D23" t="s">
-        <v>31</v>
-      </c>
       <c r="E23" t="s">
         <v>31</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23">
         <v>10</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>40</v>
       </c>
-      <c r="H23" t="s">
-        <v>31</v>
-      </c>
       <c r="I23" t="s">
         <v>31</v>
       </c>
-      <c r="J23">
+      <c r="J23" t="s">
+        <v>31</v>
+      </c>
+      <c r="K23">
         <v>14</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>40</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>0.66848399999999997</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>0.71428599999999998</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>0.360792</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>1.4141220000000001</v>
       </c>
-      <c r="W23" t="s">
+      <c r="X23" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>35</v>
       </c>
       <c r="B24" s="1">
         <v>44958</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24" t="s">
         <v>55</v>
       </c>
-      <c r="D24" t="s">
-        <v>31</v>
-      </c>
       <c r="E24" t="s">
         <v>31</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="s">
+        <v>31</v>
+      </c>
+      <c r="G24">
         <v>18</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>80</v>
       </c>
-      <c r="H24" t="s">
-        <v>31</v>
-      </c>
       <c r="I24" t="s">
         <v>31</v>
       </c>
-      <c r="J24">
+      <c r="J24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24">
         <v>13</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>80</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>0.755104</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>1.3846149999999999</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>0.72823499999999997</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>2.6326100000000001</v>
       </c>
-      <c r="W24" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="1">
         <v>44958</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" t="s">
         <v>56</v>
       </c>
-      <c r="D25" t="s">
-        <v>31</v>
-      </c>
       <c r="E25" t="s">
         <v>31</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="s">
+        <v>31</v>
+      </c>
+      <c r="G25">
         <v>11</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>52</v>
       </c>
-      <c r="H25" t="s">
-        <v>31</v>
-      </c>
       <c r="I25" t="s">
         <v>31</v>
       </c>
-      <c r="J25">
+      <c r="J25" t="s">
+        <v>31</v>
+      </c>
+      <c r="K25">
         <v>13</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>51</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>0.62933399999999995</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>0.82988200000000001</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>0.41048899999999999</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <v>1.677764</v>
       </c>
-      <c r="W25" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B26" s="1">
         <v>44378</v>
       </c>
-      <c r="C26" t="s">
-        <v>62</v>
+      <c r="C26" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="E26" t="s">
         <v>31</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="s">
+        <v>31</v>
+      </c>
+      <c r="G26">
         <v>5</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>36</v>
       </c>
-      <c r="H26" t="s">
-        <v>31</v>
-      </c>
       <c r="I26" t="s">
         <v>31</v>
       </c>
-      <c r="J26">
+      <c r="J26" t="s">
+        <v>31</v>
+      </c>
+      <c r="K26">
         <v>6</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>37</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>79.463014000000001</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>0.85648100000000005</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>0.286661</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>2.5589870000000001</v>
       </c>
-      <c r="W26" t="s">
+      <c r="X26" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B27" s="1">
         <v>44378</v>
       </c>
-      <c r="C27" t="s">
-        <v>63</v>
+      <c r="C27" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="E27" t="s">
         <v>31</v>
       </c>
-      <c r="F27">
-        <v>0</v>
+      <c r="F27" t="s">
+        <v>31</v>
       </c>
       <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
         <v>55</v>
       </c>
-      <c r="H27" t="s">
-        <v>31</v>
-      </c>
       <c r="I27" t="s">
         <v>31</v>
       </c>
-      <c r="J27">
+      <c r="J27" t="s">
+        <v>31</v>
+      </c>
+      <c r="K27">
         <v>3</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>57</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>20.536985999999999</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>0.14795900000000001</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>7.8189999999999996E-3</v>
       </c>
-      <c r="O27">
+      <c r="P27">
         <v>2.7997480000000001</v>
       </c>
-      <c r="W27" t="s">
+      <c r="X27" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B28" s="1">
         <v>44713</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D28" t="s">
+        <v>63</v>
+      </c>
+      <c r="E28" t="s">
+        <v>31</v>
+      </c>
+      <c r="F28" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>30</v>
+      </c>
+      <c r="I28" t="s">
+        <v>31</v>
+      </c>
+      <c r="J28" t="s">
+        <v>31</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>15</v>
+      </c>
+      <c r="M28" t="s">
+        <v>31</v>
+      </c>
+      <c r="N28" t="s">
+        <v>31</v>
+      </c>
+      <c r="O28" t="s">
+        <v>31</v>
+      </c>
+      <c r="P28" t="s">
+        <v>31</v>
+      </c>
+      <c r="X28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>64</v>
-      </c>
-      <c r="D28" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" t="s">
-        <v>31</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28">
-        <v>30</v>
-      </c>
-      <c r="H28" t="s">
-        <v>31</v>
-      </c>
-      <c r="I28" t="s">
-        <v>31</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>15</v>
-      </c>
-      <c r="L28" t="s">
-        <v>31</v>
-      </c>
-      <c r="M28" t="s">
-        <v>31</v>
-      </c>
-      <c r="N28" t="s">
-        <v>31</v>
-      </c>
-      <c r="O28" t="s">
-        <v>31</v>
-      </c>
-      <c r="W28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>66</v>
       </c>
       <c r="B29" s="1">
         <v>44287</v>
       </c>
-      <c r="C29" t="s">
-        <v>67</v>
+      <c r="C29" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="E29" t="s">
         <v>31</v>
@@ -2171,45 +2314,45 @@
       <c r="F29" t="s">
         <v>31</v>
       </c>
-      <c r="G29">
+      <c r="G29" t="s">
+        <v>31</v>
+      </c>
+      <c r="H29">
         <v>88</v>
       </c>
-      <c r="H29" t="s">
-        <v>31</v>
-      </c>
       <c r="I29" t="s">
         <v>31</v>
       </c>
       <c r="J29" t="s">
         <v>31</v>
       </c>
-      <c r="K29">
+      <c r="K29" t="s">
+        <v>31</v>
+      </c>
+      <c r="L29">
         <v>126</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>10.661391</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>0.89996399999999999</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>0.62785500000000005</v>
       </c>
-      <c r="O29">
+      <c r="P29">
         <v>1.2900039999999999</v>
       </c>
-      <c r="P29" t="s">
-        <v>22</v>
-      </c>
       <c r="Q29" t="s">
         <v>22</v>
       </c>
       <c r="R29" t="s">
+        <v>22</v>
+      </c>
+      <c r="S29" t="s">
         <v>24</v>
       </c>
-      <c r="S29" t="s">
-        <v>22</v>
-      </c>
       <c r="T29" t="s">
         <v>22</v>
       </c>
@@ -2217,21 +2360,24 @@
         <v>22</v>
       </c>
       <c r="V29" t="s">
+        <v>22</v>
+      </c>
+      <c r="W29" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B30" s="1">
         <v>44287</v>
       </c>
-      <c r="C30" t="s">
-        <v>68</v>
+      <c r="C30" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="D30" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="E30" t="s">
         <v>31</v>
@@ -2239,36 +2385,36 @@
       <c r="F30" t="s">
         <v>31</v>
       </c>
-      <c r="G30">
+      <c r="G30" t="s">
+        <v>31</v>
+      </c>
+      <c r="H30">
         <v>107</v>
       </c>
-      <c r="H30" t="s">
-        <v>31</v>
-      </c>
       <c r="I30" t="s">
         <v>31</v>
       </c>
       <c r="J30" t="s">
         <v>31</v>
       </c>
-      <c r="K30">
+      <c r="K30" t="s">
+        <v>31</v>
+      </c>
+      <c r="L30">
         <v>98</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>8.1972780000000007</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>0.59001899999999996</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>0.39117299999999999</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>0.88994499999999999</v>
       </c>
-      <c r="P30" t="s">
-        <v>22</v>
-      </c>
       <c r="Q30" t="s">
         <v>22</v>
       </c>
@@ -2285,21 +2431,24 @@
         <v>22</v>
       </c>
       <c r="V30" t="s">
+        <v>22</v>
+      </c>
+      <c r="W30" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B31" s="1">
         <v>44287</v>
       </c>
-      <c r="C31" t="s">
-        <v>69</v>
+      <c r="C31" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="D31" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="E31" t="s">
         <v>31</v>
@@ -2307,36 +2456,36 @@
       <c r="F31" t="s">
         <v>31</v>
       </c>
-      <c r="G31">
+      <c r="G31" t="s">
+        <v>31</v>
+      </c>
+      <c r="H31">
         <v>299</v>
       </c>
-      <c r="H31" t="s">
-        <v>31</v>
-      </c>
       <c r="I31" t="s">
         <v>31</v>
       </c>
       <c r="J31" t="s">
         <v>31</v>
       </c>
-      <c r="K31">
+      <c r="K31" t="s">
+        <v>31</v>
+      </c>
+      <c r="L31">
         <v>300</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>31.268568999999999</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>0.689975</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>0.56010000000000004</v>
       </c>
-      <c r="O31">
+      <c r="P31">
         <v>0.84996499999999997</v>
       </c>
-      <c r="P31" t="s">
-        <v>22</v>
-      </c>
       <c r="Q31" t="s">
         <v>22</v>
       </c>
@@ -2353,21 +2502,24 @@
         <v>22</v>
       </c>
       <c r="V31" t="s">
+        <v>22</v>
+      </c>
+      <c r="W31" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B32" s="1">
         <v>44287</v>
       </c>
-      <c r="C32" t="s">
-        <v>70</v>
+      <c r="C32" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="D32" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="E32" t="s">
         <v>31</v>
@@ -2375,45 +2527,45 @@
       <c r="F32" t="s">
         <v>31</v>
       </c>
-      <c r="G32">
+      <c r="G32" t="s">
+        <v>31</v>
+      </c>
+      <c r="H32">
         <v>154</v>
       </c>
-      <c r="H32" t="s">
-        <v>31</v>
-      </c>
       <c r="I32" t="s">
         <v>31</v>
       </c>
       <c r="J32" t="s">
         <v>31</v>
       </c>
-      <c r="K32">
+      <c r="K32" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32">
         <v>151</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>20.924423000000001</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>0.62002199999999996</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>0.47999900000000001</v>
       </c>
-      <c r="O32">
+      <c r="P32">
         <v>0.80089200000000005</v>
       </c>
-      <c r="P32" t="s">
-        <v>22</v>
-      </c>
       <c r="Q32" t="s">
         <v>22</v>
       </c>
       <c r="R32" t="s">
+        <v>22</v>
+      </c>
+      <c r="S32" t="s">
         <v>24</v>
       </c>
-      <c r="S32" t="s">
-        <v>22</v>
-      </c>
       <c r="T32" t="s">
         <v>22</v>
       </c>
@@ -2421,21 +2573,24 @@
         <v>22</v>
       </c>
       <c r="V32" t="s">
+        <v>22</v>
+      </c>
+      <c r="W32" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B33" s="1">
         <v>44287</v>
       </c>
-      <c r="C33" t="s">
-        <v>71</v>
+      <c r="C33" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="D33" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="E33" t="s">
         <v>31</v>
@@ -2443,67 +2598,70 @@
       <c r="F33" t="s">
         <v>31</v>
       </c>
-      <c r="G33">
+      <c r="G33" t="s">
+        <v>31</v>
+      </c>
+      <c r="H33">
         <v>118</v>
       </c>
-      <c r="H33" t="s">
-        <v>31</v>
-      </c>
       <c r="I33" t="s">
         <v>31</v>
       </c>
       <c r="J33" t="s">
         <v>31</v>
       </c>
-      <c r="K33">
+      <c r="K33" t="s">
+        <v>31</v>
+      </c>
+      <c r="L33">
         <v>107</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>14.174234999999999</v>
       </c>
-      <c r="M33">
+      <c r="N33">
         <v>0.76002800000000004</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>0.55642100000000005</v>
       </c>
-      <c r="O33">
+      <c r="P33">
         <v>1.0381400000000001</v>
       </c>
-      <c r="P33" t="s">
-        <v>22</v>
-      </c>
       <c r="Q33" t="s">
         <v>22</v>
       </c>
       <c r="R33" t="s">
+        <v>22</v>
+      </c>
+      <c r="S33" t="s">
         <v>24</v>
       </c>
-      <c r="S33" t="s">
-        <v>22</v>
-      </c>
       <c r="T33" t="s">
+        <v>22</v>
+      </c>
+      <c r="U33" t="s">
         <v>24</v>
       </c>
-      <c r="U33" t="s">
-        <v>22</v>
-      </c>
       <c r="V33" t="s">
+        <v>22</v>
+      </c>
+      <c r="W33" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B34" s="1">
         <v>44287</v>
       </c>
-      <c r="C34" t="s">
-        <v>72</v>
+      <c r="C34" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="D34" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="E34" t="s">
         <v>31</v>
@@ -2511,44 +2669,44 @@
       <c r="F34" t="s">
         <v>31</v>
       </c>
-      <c r="G34">
+      <c r="G34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H34">
         <v>283</v>
       </c>
-      <c r="H34" t="s">
-        <v>31</v>
-      </c>
       <c r="I34" t="s">
         <v>31</v>
       </c>
       <c r="J34" t="s">
         <v>31</v>
       </c>
-      <c r="K34">
+      <c r="K34" t="s">
+        <v>31</v>
+      </c>
+      <c r="L34">
         <v>280</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>14.774103999999999</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>0.57001100000000005</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>0.420016</v>
       </c>
-      <c r="O34">
+      <c r="P34">
         <v>0.77357100000000001</v>
-      </c>
-      <c r="P34" t="s">
-        <v>23</v>
       </c>
       <c r="Q34" t="s">
         <v>23</v>
       </c>
       <c r="R34" t="s">
+        <v>23</v>
+      </c>
+      <c r="S34" t="s">
         <v>24</v>
-      </c>
-      <c r="S34" t="s">
-        <v>23</v>
       </c>
       <c r="T34" t="s">
         <v>23</v>
@@ -2557,707 +2715,4037 @@
         <v>23</v>
       </c>
       <c r="V34" t="s">
+        <v>23</v>
+      </c>
+      <c r="W34" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B35" s="1">
         <v>44927</v>
       </c>
-      <c r="C35" t="s">
-        <v>75</v>
+      <c r="C35" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="D35" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="E35" t="s">
         <v>31</v>
       </c>
-      <c r="F35">
+      <c r="F35" t="s">
+        <v>31</v>
+      </c>
+      <c r="G35">
         <v>59</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>541</v>
       </c>
-      <c r="H35" t="s">
-        <v>31</v>
-      </c>
       <c r="I35" t="s">
         <v>31</v>
       </c>
-      <c r="J35">
+      <c r="J35" t="s">
+        <v>31</v>
+      </c>
+      <c r="K35">
         <v>77</v>
       </c>
-      <c r="K35">
+      <c r="L35">
         <v>521</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>18.349443999999998</v>
       </c>
-      <c r="M35">
+      <c r="N35">
         <v>0.73790699999999998</v>
       </c>
-      <c r="N35">
+      <c r="O35">
         <v>0.53741000000000005</v>
       </c>
-      <c r="O35">
+      <c r="P35">
         <v>1.0132049999999999</v>
       </c>
-      <c r="W35" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X35" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B36" s="1">
         <v>44927</v>
       </c>
-      <c r="C36" t="s">
-        <v>76</v>
+      <c r="C36" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="D36" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="E36" t="s">
         <v>31</v>
       </c>
-      <c r="F36">
+      <c r="F36" t="s">
+        <v>31</v>
+      </c>
+      <c r="G36">
         <v>3</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>193</v>
       </c>
-      <c r="H36" t="s">
-        <v>31</v>
-      </c>
       <c r="I36" t="s">
         <v>31</v>
       </c>
-      <c r="J36">
+      <c r="J36" t="s">
+        <v>31</v>
+      </c>
+      <c r="K36">
         <v>4</v>
       </c>
-      <c r="K36">
+      <c r="L36">
         <v>200</v>
       </c>
-      <c r="L36">
+      <c r="M36">
         <v>0.83777900000000005</v>
       </c>
-      <c r="M36">
+      <c r="N36">
         <v>0.77720199999999995</v>
       </c>
-      <c r="N36">
+      <c r="O36">
         <v>0.17624500000000001</v>
       </c>
-      <c r="O36">
+      <c r="P36">
         <v>3.4272939999999998</v>
       </c>
-      <c r="W36" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B37" s="1">
         <v>44927</v>
       </c>
-      <c r="C37" t="s">
-        <v>77</v>
+      <c r="C37" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="D37" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="E37" t="s">
         <v>31</v>
       </c>
-      <c r="F37">
+      <c r="F37" t="s">
+        <v>31</v>
+      </c>
+      <c r="G37">
         <v>285</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>2743</v>
       </c>
-      <c r="H37" t="s">
-        <v>31</v>
-      </c>
       <c r="I37" t="s">
         <v>31</v>
       </c>
-      <c r="J37">
+      <c r="J37" t="s">
+        <v>31</v>
+      </c>
+      <c r="K37">
         <v>289</v>
       </c>
-      <c r="K37">
+      <c r="L37">
         <v>2708</v>
       </c>
-      <c r="L37">
+      <c r="M37">
         <v>77.011066</v>
       </c>
-      <c r="M37">
+      <c r="N37">
         <v>0.973576</v>
       </c>
-      <c r="N37">
+      <c r="O37">
         <v>0.833982</v>
       </c>
-      <c r="O37">
+      <c r="P37">
         <v>1.136536</v>
       </c>
-      <c r="W37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X37" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B38" s="1">
         <v>44927</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D38" t="s">
+        <v>76</v>
+      </c>
+      <c r="E38" t="s">
+        <v>31</v>
+      </c>
+      <c r="F38" t="s">
+        <v>31</v>
+      </c>
+      <c r="G38">
+        <v>22</v>
+      </c>
+      <c r="H38">
+        <v>158</v>
+      </c>
+      <c r="I38" t="s">
+        <v>31</v>
+      </c>
+      <c r="J38" t="s">
+        <v>31</v>
+      </c>
+      <c r="K38">
+        <v>10</v>
+      </c>
+      <c r="L38">
         <v>78</v>
       </c>
-      <c r="D38" t="s">
-        <v>31</v>
-      </c>
-      <c r="E38" t="s">
-        <v>31</v>
-      </c>
-      <c r="F38">
-        <v>22</v>
-      </c>
-      <c r="G38">
-        <v>158</v>
-      </c>
-      <c r="H38" t="s">
-        <v>31</v>
-      </c>
-      <c r="I38" t="s">
-        <v>31</v>
-      </c>
-      <c r="J38">
-        <v>10</v>
-      </c>
-      <c r="K38">
-        <v>78</v>
-      </c>
-      <c r="L38">
+      <c r="M38">
         <v>3.8017099999999999</v>
       </c>
-      <c r="M38">
+      <c r="N38">
         <v>1.086076</v>
       </c>
-      <c r="N38">
+      <c r="O38">
         <v>0.541188</v>
       </c>
-      <c r="O38">
+      <c r="P38">
         <v>2.1795770000000001</v>
       </c>
-      <c r="W38" t="s">
+      <c r="X38" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B39" s="1">
         <v>44866</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D39" t="s">
+        <v>85</v>
+      </c>
+      <c r="E39" t="s">
+        <v>31</v>
+      </c>
+      <c r="F39" t="s">
+        <v>31</v>
+      </c>
+      <c r="G39">
+        <v>37</v>
+      </c>
+      <c r="H39">
+        <v>141</v>
+      </c>
+      <c r="I39" t="s">
+        <v>31</v>
+      </c>
+      <c r="J39" t="s">
+        <v>31</v>
+      </c>
+      <c r="K39">
+        <v>17</v>
+      </c>
+      <c r="L39">
+        <v>52</v>
+      </c>
+      <c r="M39">
+        <v>2.4689999999999999</v>
+      </c>
+      <c r="N39">
+        <v>0.80266999999999999</v>
+      </c>
+      <c r="O39">
+        <v>0.49757499999999999</v>
+      </c>
+      <c r="P39">
+        <v>1.2948379999999999</v>
+      </c>
+      <c r="X39" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>88</v>
-      </c>
-      <c r="D39" t="s">
-        <v>31</v>
-      </c>
-      <c r="E39" t="s">
-        <v>31</v>
-      </c>
-      <c r="F39">
-        <v>37</v>
-      </c>
-      <c r="G39">
-        <v>141</v>
-      </c>
-      <c r="H39" t="s">
-        <v>31</v>
-      </c>
-      <c r="I39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J39">
-        <v>17</v>
-      </c>
-      <c r="K39">
-        <v>52</v>
-      </c>
-      <c r="L39">
-        <v>2.4689999999999999</v>
-      </c>
-      <c r="M39">
-        <v>0.80266999999999999</v>
-      </c>
-      <c r="N39">
-        <v>0.49757499999999999</v>
-      </c>
-      <c r="O39">
-        <v>1.2948379999999999</v>
-      </c>
-      <c r="W39" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>79</v>
       </c>
       <c r="B40" s="1">
         <v>44866</v>
       </c>
-      <c r="C40" t="s">
-        <v>89</v>
+      <c r="C40" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="D40" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="E40" t="s">
         <v>31</v>
       </c>
-      <c r="F40">
+      <c r="F40" t="s">
+        <v>31</v>
+      </c>
+      <c r="G40">
         <v>41</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>137</v>
       </c>
-      <c r="H40" t="s">
-        <v>31</v>
-      </c>
       <c r="I40" t="s">
         <v>31</v>
       </c>
-      <c r="J40">
+      <c r="J40" t="s">
+        <v>31</v>
+      </c>
+      <c r="K40">
         <v>16</v>
       </c>
-      <c r="K40">
+      <c r="L40">
         <v>49</v>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>2.483384</v>
       </c>
-      <c r="M40">
+      <c r="N40">
         <v>0.91651499999999997</v>
       </c>
-      <c r="N40">
+      <c r="O40">
         <v>0.568936</v>
       </c>
-      <c r="O40">
+      <c r="P40">
         <v>1.4764390000000001</v>
       </c>
-      <c r="W40" t="s">
+      <c r="X40" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B41" s="1">
         <v>44866</v>
       </c>
-      <c r="C41" t="s">
-        <v>80</v>
+      <c r="C41" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="D41" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="E41" t="s">
         <v>31</v>
       </c>
-      <c r="F41">
+      <c r="F41" t="s">
+        <v>31</v>
+      </c>
+      <c r="G41">
         <v>7</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>35</v>
       </c>
-      <c r="H41" t="s">
-        <v>31</v>
-      </c>
       <c r="I41" t="s">
         <v>31</v>
       </c>
-      <c r="J41">
+      <c r="J41" t="s">
+        <v>31</v>
+      </c>
+      <c r="K41">
         <v>5</v>
       </c>
-      <c r="K41">
+      <c r="L41">
         <v>29</v>
       </c>
-      <c r="L41">
+      <c r="M41">
         <v>0.52527599999999997</v>
       </c>
-      <c r="M41">
+      <c r="N41">
         <v>1.1599999999999999</v>
       </c>
-      <c r="N41">
+      <c r="O41">
         <v>0.41134199999999999</v>
       </c>
-      <c r="O41">
+      <c r="P41">
         <v>3.2712439999999998</v>
       </c>
-      <c r="W41" t="s">
+      <c r="X41" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B42" s="1">
         <v>44866</v>
       </c>
-      <c r="C42" t="s">
-        <v>81</v>
+      <c r="C42" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="D42" t="s">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="E42" t="s">
         <v>31</v>
       </c>
-      <c r="F42">
+      <c r="F42" t="s">
+        <v>31</v>
+      </c>
+      <c r="G42">
         <v>11</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>76</v>
       </c>
-      <c r="H42" t="s">
-        <v>31</v>
-      </c>
       <c r="I42" t="s">
         <v>31</v>
       </c>
-      <c r="J42">
+      <c r="J42" t="s">
+        <v>31</v>
+      </c>
+      <c r="K42">
         <v>20</v>
       </c>
-      <c r="K42">
+      <c r="L42">
         <v>73</v>
       </c>
-      <c r="L42">
+      <c r="M42">
         <v>1.288648</v>
       </c>
-      <c r="M42">
+      <c r="N42">
         <v>0.52828900000000001</v>
       </c>
-      <c r="N42">
+      <c r="O42">
         <v>0.27252500000000002</v>
       </c>
-      <c r="O42">
+      <c r="P42">
         <v>1.024087</v>
       </c>
-      <c r="W42" t="s">
+      <c r="X42" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B43" s="1">
         <v>44866</v>
       </c>
-      <c r="C43" t="s">
-        <v>82</v>
+      <c r="C43" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="D43" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="E43" t="s">
         <v>31</v>
       </c>
-      <c r="F43">
+      <c r="F43" t="s">
+        <v>31</v>
+      </c>
+      <c r="G43">
         <v>482</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>2104</v>
       </c>
-      <c r="H43" t="s">
-        <v>31</v>
-      </c>
       <c r="I43" t="s">
         <v>31</v>
       </c>
-      <c r="J43">
+      <c r="J43" t="s">
+        <v>31</v>
+      </c>
+      <c r="K43">
         <v>1110</v>
       </c>
-      <c r="K43">
+      <c r="L43">
         <v>4321</v>
       </c>
-      <c r="L43">
+      <c r="M43">
         <v>64.778155999999996</v>
       </c>
-      <c r="M43">
+      <c r="N43">
         <v>0.89178999999999997</v>
       </c>
-      <c r="N43">
+      <c r="O43">
         <v>0.81230199999999997</v>
       </c>
-      <c r="O43">
+      <c r="P43">
         <v>0.97905600000000004</v>
       </c>
-      <c r="W43" t="s">
+      <c r="X43" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B44" s="1">
         <v>44866</v>
       </c>
-      <c r="C44" t="s">
-        <v>83</v>
+      <c r="C44" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="D44" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="E44" t="s">
         <v>31</v>
       </c>
-      <c r="F44">
+      <c r="F44" t="s">
+        <v>31</v>
+      </c>
+      <c r="G44">
         <v>16</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <v>25</v>
       </c>
-      <c r="H44" t="s">
-        <v>31</v>
-      </c>
       <c r="I44" t="s">
         <v>31</v>
       </c>
-      <c r="J44">
+      <c r="J44" t="s">
+        <v>31</v>
+      </c>
+      <c r="K44">
         <v>15</v>
       </c>
-      <c r="K44">
+      <c r="L44">
         <v>25</v>
       </c>
-      <c r="L44">
+      <c r="M44">
         <v>2.9892940000000001</v>
       </c>
-      <c r="M44">
+      <c r="N44">
         <v>1.066667</v>
       </c>
-      <c r="N44">
+      <c r="O44">
         <v>0.69069599999999998</v>
       </c>
-      <c r="O44">
+      <c r="P44">
         <v>1.6472910000000001</v>
       </c>
-      <c r="W44" t="s">
+      <c r="X44" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B45" s="1">
         <v>44866</v>
       </c>
-      <c r="C45" t="s">
-        <v>84</v>
+      <c r="C45" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="D45" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="E45" t="s">
         <v>31</v>
       </c>
-      <c r="F45">
+      <c r="F45" t="s">
+        <v>31</v>
+      </c>
+      <c r="G45">
         <v>79</v>
       </c>
-      <c r="G45">
+      <c r="H45">
         <v>209</v>
       </c>
-      <c r="H45" t="s">
-        <v>31</v>
-      </c>
       <c r="I45" t="s">
         <v>31</v>
       </c>
-      <c r="J45">
+      <c r="J45" t="s">
+        <v>31</v>
+      </c>
+      <c r="K45">
         <v>80</v>
       </c>
-      <c r="K45">
+      <c r="L45">
         <v>207</v>
       </c>
-      <c r="L45">
+      <c r="M45">
         <v>9.4561679999999999</v>
       </c>
-      <c r="M45">
+      <c r="N45">
         <v>0.97804999999999997</v>
       </c>
-      <c r="N45">
+      <c r="O45">
         <v>0.76602300000000001</v>
       </c>
-      <c r="O45">
+      <c r="P45">
         <v>1.248764</v>
       </c>
-      <c r="W45" t="s">
+      <c r="X45" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B46" s="1">
         <v>44866</v>
       </c>
-      <c r="C46" t="s">
-        <v>85</v>
+      <c r="C46" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="D46" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="E46" t="s">
         <v>31</v>
       </c>
-      <c r="F46">
+      <c r="F46" t="s">
+        <v>31</v>
+      </c>
+      <c r="G46">
         <v>6</v>
       </c>
-      <c r="G46">
+      <c r="H46">
         <v>16</v>
       </c>
-      <c r="H46" t="s">
-        <v>31</v>
-      </c>
       <c r="I46" t="s">
         <v>31</v>
       </c>
-      <c r="J46">
+      <c r="J46" t="s">
+        <v>31</v>
+      </c>
+      <c r="K46">
         <v>2</v>
       </c>
-      <c r="K46">
+      <c r="L46">
         <v>14</v>
       </c>
-      <c r="L46">
+      <c r="M46">
         <v>0.27588299999999999</v>
       </c>
-      <c r="M46">
+      <c r="N46">
         <v>2.625</v>
       </c>
-      <c r="N46">
+      <c r="O46">
         <v>0.62783699999999998</v>
       </c>
-      <c r="O46">
+      <c r="P46">
         <v>10.97519</v>
       </c>
-      <c r="W46" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X46" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B47" s="1">
         <v>44866</v>
       </c>
-      <c r="C47" t="s">
-        <v>86</v>
+      <c r="C47" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="D47" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="E47" t="s">
         <v>31</v>
       </c>
-      <c r="F47">
-        <v>0</v>
+      <c r="F47" t="s">
+        <v>31</v>
       </c>
       <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
         <v>43</v>
       </c>
-      <c r="H47" t="s">
-        <v>31</v>
-      </c>
       <c r="I47" t="s">
         <v>31</v>
       </c>
-      <c r="J47">
+      <c r="J47" t="s">
+        <v>31</v>
+      </c>
+      <c r="K47">
         <v>1</v>
       </c>
-      <c r="K47">
+      <c r="L47">
         <v>43</v>
       </c>
-      <c r="L47">
+      <c r="M47">
         <v>5.6071000000000003E-2</v>
       </c>
-      <c r="M47">
+      <c r="N47">
         <v>0.33333299999999999</v>
       </c>
-      <c r="N47">
+      <c r="O47">
         <v>1.3956E-2</v>
       </c>
-      <c r="O47">
+      <c r="P47">
         <v>7.9613639999999997</v>
       </c>
-      <c r="W47" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X47" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B48" s="1">
         <v>44866</v>
       </c>
-      <c r="C48" t="s">
-        <v>87</v>
+      <c r="C48" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="D48" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="E48" t="s">
         <v>31</v>
       </c>
-      <c r="F48">
+      <c r="F48" t="s">
+        <v>31</v>
+      </c>
+      <c r="G48">
         <v>85</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>151</v>
       </c>
-      <c r="H48" t="s">
-        <v>31</v>
-      </c>
       <c r="I48" t="s">
         <v>31</v>
       </c>
-      <c r="J48">
+      <c r="J48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K48">
         <v>91</v>
       </c>
-      <c r="K48">
+      <c r="L48">
         <v>148</v>
       </c>
-      <c r="L48">
+      <c r="M48">
         <v>15.678119000000001</v>
       </c>
-      <c r="M48">
+      <c r="N48">
         <v>0.91550799999999999</v>
       </c>
-      <c r="N48">
+      <c r="O48">
         <v>0.75726400000000005</v>
       </c>
-      <c r="O48">
+      <c r="P48">
         <v>1.1068199999999999</v>
       </c>
-      <c r="W48" t="s">
+      <c r="X48" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" s="1">
+        <v>44256</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49">
+        <v>-4.3</v>
+      </c>
+      <c r="F49">
+        <v>2.9459</v>
+      </c>
+      <c r="G49" t="s">
+        <v>31</v>
+      </c>
+      <c r="H49">
+        <v>30</v>
+      </c>
+      <c r="I49">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="J49">
+        <v>3.4815</v>
+      </c>
+      <c r="K49" t="s">
+        <v>31</v>
+      </c>
+      <c r="L49">
+        <v>30</v>
+      </c>
+      <c r="M49">
+        <v>8.3433449999999993</v>
+      </c>
+      <c r="N49">
+        <v>-2.1</v>
+      </c>
+      <c r="O49">
+        <v>-3.7319640000000001</v>
+      </c>
+      <c r="P49">
+        <v>-0.46803600000000001</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>22</v>
+      </c>
+      <c r="R49" t="s">
+        <v>22</v>
+      </c>
+      <c r="S49" t="s">
+        <v>22</v>
+      </c>
+      <c r="T49" t="s">
+        <v>22</v>
+      </c>
+      <c r="U49" t="s">
+        <v>24</v>
+      </c>
+      <c r="V49" t="s">
+        <v>23</v>
+      </c>
+      <c r="W49" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" s="1">
+        <v>44256</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50">
+        <v>-4.54</v>
+      </c>
+      <c r="F50">
+        <v>2.7504</v>
+      </c>
+      <c r="G50" t="s">
+        <v>31</v>
+      </c>
+      <c r="H50">
+        <v>143</v>
+      </c>
+      <c r="I50">
+        <v>-1.34</v>
+      </c>
+      <c r="J50">
+        <v>2.7677999999999998</v>
+      </c>
+      <c r="K50" t="s">
+        <v>31</v>
+      </c>
+      <c r="L50">
+        <v>133</v>
+      </c>
+      <c r="M50">
+        <v>52.348607000000001</v>
+      </c>
+      <c r="N50">
+        <v>-3.2</v>
+      </c>
+      <c r="O50">
+        <v>-3.8515199999999998</v>
+      </c>
+      <c r="P50">
+        <v>-2.5484800000000001</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>22</v>
+      </c>
+      <c r="R50" t="s">
+        <v>22</v>
+      </c>
+      <c r="S50" t="s">
+        <v>22</v>
+      </c>
+      <c r="T50" t="s">
+        <v>22</v>
+      </c>
+      <c r="U50" t="s">
+        <v>23</v>
+      </c>
+      <c r="V50" t="s">
+        <v>23</v>
+      </c>
+      <c r="W50" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" s="1">
+        <v>44256</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D51" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51">
+        <v>-4.32</v>
+      </c>
+      <c r="F51">
+        <v>3.2633999999999999</v>
+      </c>
+      <c r="G51" t="s">
+        <v>31</v>
+      </c>
+      <c r="H51">
+        <v>295</v>
+      </c>
+      <c r="I51">
+        <v>-1.39</v>
+      </c>
+      <c r="J51">
+        <v>4.1220999999999997</v>
+      </c>
+      <c r="K51" t="s">
+        <v>31</v>
+      </c>
+      <c r="L51">
+        <v>153</v>
+      </c>
+      <c r="M51">
+        <v>39.308047999999999</v>
+      </c>
+      <c r="N51">
+        <v>-2.93</v>
+      </c>
+      <c r="O51">
+        <v>-3.6818650000000002</v>
+      </c>
+      <c r="P51">
+        <v>-2.1781350000000002</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>22</v>
+      </c>
+      <c r="R51" t="s">
+        <v>22</v>
+      </c>
+      <c r="S51" t="s">
+        <v>22</v>
+      </c>
+      <c r="T51" t="s">
+        <v>22</v>
+      </c>
+      <c r="U51" t="s">
+        <v>24</v>
+      </c>
+      <c r="V51" t="s">
+        <v>23</v>
+      </c>
+      <c r="W51" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" s="1">
+        <v>44256</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D52" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" t="s">
+        <v>31</v>
+      </c>
+      <c r="F52" t="s">
+        <v>31</v>
+      </c>
+      <c r="G52">
+        <v>2</v>
+      </c>
+      <c r="H52">
+        <v>30</v>
+      </c>
+      <c r="I52" t="s">
+        <v>31</v>
+      </c>
+      <c r="J52" t="s">
+        <v>31</v>
+      </c>
+      <c r="K52">
+        <v>4</v>
+      </c>
+      <c r="L52">
+        <v>30</v>
+      </c>
+      <c r="M52">
+        <v>8.8845960000000002</v>
+      </c>
+      <c r="N52">
+        <v>0.5</v>
+      </c>
+      <c r="O52">
+        <v>9.8931000000000005E-2</v>
+      </c>
+      <c r="P52">
+        <v>2.5270109999999999</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>22</v>
+      </c>
+      <c r="R52" t="s">
+        <v>22</v>
+      </c>
+      <c r="S52" t="s">
+        <v>22</v>
+      </c>
+      <c r="T52" t="s">
+        <v>22</v>
+      </c>
+      <c r="U52" t="s">
+        <v>24</v>
+      </c>
+      <c r="V52" t="s">
+        <v>23</v>
+      </c>
+      <c r="W52" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" s="1">
+        <v>44256</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D53" t="s">
+        <v>12</v>
+      </c>
+      <c r="E53" t="s">
+        <v>31</v>
+      </c>
+      <c r="F53" t="s">
+        <v>31</v>
+      </c>
+      <c r="G53">
+        <v>6</v>
+      </c>
+      <c r="H53">
+        <v>143</v>
+      </c>
+      <c r="I53" t="s">
+        <v>31</v>
+      </c>
+      <c r="J53" t="s">
+        <v>31</v>
+      </c>
+      <c r="K53">
+        <v>19</v>
+      </c>
+      <c r="L53">
+        <v>132</v>
+      </c>
+      <c r="M53">
+        <v>43.889902999999997</v>
+      </c>
+      <c r="N53">
+        <v>0.29149799999999998</v>
+      </c>
+      <c r="O53">
+        <v>0.120086</v>
+      </c>
+      <c r="P53">
+        <v>0.70758600000000005</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>22</v>
+      </c>
+      <c r="R53" t="s">
+        <v>22</v>
+      </c>
+      <c r="S53" t="s">
+        <v>22</v>
+      </c>
+      <c r="T53" t="s">
+        <v>22</v>
+      </c>
+      <c r="U53" t="s">
+        <v>23</v>
+      </c>
+      <c r="V53" t="s">
+        <v>23</v>
+      </c>
+      <c r="W53" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" s="1">
+        <v>44256</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D54" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" t="s">
+        <v>31</v>
+      </c>
+      <c r="F54" t="s">
+        <v>31</v>
+      </c>
+      <c r="G54">
+        <v>20</v>
+      </c>
+      <c r="H54">
+        <v>297</v>
+      </c>
+      <c r="I54" t="s">
+        <v>31</v>
+      </c>
+      <c r="J54" t="s">
+        <v>31</v>
+      </c>
+      <c r="K54">
+        <v>16</v>
+      </c>
+      <c r="L54">
+        <v>150</v>
+      </c>
+      <c r="M54">
+        <v>47.225501999999999</v>
+      </c>
+      <c r="N54">
+        <v>0.63131300000000001</v>
+      </c>
+      <c r="O54">
+        <v>0.33711000000000002</v>
+      </c>
+      <c r="P54">
+        <v>1.182272</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>22</v>
+      </c>
+      <c r="R54" t="s">
+        <v>22</v>
+      </c>
+      <c r="S54" t="s">
+        <v>22</v>
+      </c>
+      <c r="T54" t="s">
+        <v>22</v>
+      </c>
+      <c r="U54" t="s">
+        <v>24</v>
+      </c>
+      <c r="V54" t="s">
+        <v>23</v>
+      </c>
+      <c r="W54" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" s="1">
+        <v>44256</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D55" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" t="s">
+        <v>31</v>
+      </c>
+      <c r="F55" t="s">
+        <v>31</v>
+      </c>
+      <c r="G55">
+        <v>3</v>
+      </c>
+      <c r="H55">
+        <v>143</v>
+      </c>
+      <c r="I55" t="s">
+        <v>31</v>
+      </c>
+      <c r="J55" t="s">
+        <v>31</v>
+      </c>
+      <c r="K55">
+        <v>10</v>
+      </c>
+      <c r="L55">
+        <v>133</v>
+      </c>
+      <c r="M55">
+        <v>55.659208</v>
+      </c>
+      <c r="N55">
+        <v>0.27902100000000002</v>
+      </c>
+      <c r="O55">
+        <v>7.8481999999999996E-2</v>
+      </c>
+      <c r="P55">
+        <v>0.99198299999999995</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>22</v>
+      </c>
+      <c r="R55" t="s">
+        <v>22</v>
+      </c>
+      <c r="S55" t="s">
+        <v>22</v>
+      </c>
+      <c r="T55" t="s">
+        <v>22</v>
+      </c>
+      <c r="U55" t="s">
+        <v>23</v>
+      </c>
+      <c r="V55" t="s">
+        <v>23</v>
+      </c>
+      <c r="W55" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" s="1">
+        <v>44256</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D56" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" t="s">
+        <v>31</v>
+      </c>
+      <c r="F56" t="s">
+        <v>31</v>
+      </c>
+      <c r="G56">
+        <v>2</v>
+      </c>
+      <c r="H56">
+        <v>295</v>
+      </c>
+      <c r="I56" t="s">
+        <v>31</v>
+      </c>
+      <c r="J56" t="s">
+        <v>31</v>
+      </c>
+      <c r="K56">
+        <v>12</v>
+      </c>
+      <c r="L56">
+        <v>154</v>
+      </c>
+      <c r="M56">
+        <v>44.340792</v>
+      </c>
+      <c r="N56">
+        <v>8.7006E-2</v>
+      </c>
+      <c r="O56">
+        <v>1.9723000000000001E-2</v>
+      </c>
+      <c r="P56">
+        <v>0.383824</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>22</v>
+      </c>
+      <c r="R56" t="s">
+        <v>22</v>
+      </c>
+      <c r="S56" t="s">
+        <v>22</v>
+      </c>
+      <c r="T56" t="s">
+        <v>22</v>
+      </c>
+      <c r="U56" t="s">
+        <v>24</v>
+      </c>
+      <c r="V56" t="s">
+        <v>23</v>
+      </c>
+      <c r="W56" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" s="1">
+        <v>44256</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D57" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" t="s">
+        <v>31</v>
+      </c>
+      <c r="F57" t="s">
+        <v>31</v>
+      </c>
+      <c r="G57">
+        <v>14</v>
+      </c>
+      <c r="H57">
+        <v>30</v>
+      </c>
+      <c r="I57" t="s">
+        <v>31</v>
+      </c>
+      <c r="J57" t="s">
+        <v>31</v>
+      </c>
+      <c r="K57">
+        <v>10</v>
+      </c>
+      <c r="L57">
+        <v>30</v>
+      </c>
+      <c r="M57">
+        <v>19.019812999999999</v>
+      </c>
+      <c r="N57">
+        <v>1.4</v>
+      </c>
+      <c r="O57">
+        <v>0.74236899999999995</v>
+      </c>
+      <c r="P57">
+        <v>2.6401949999999998</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>22</v>
+      </c>
+      <c r="R57" t="s">
+        <v>22</v>
+      </c>
+      <c r="S57" t="s">
+        <v>22</v>
+      </c>
+      <c r="T57" t="s">
+        <v>22</v>
+      </c>
+      <c r="U57" t="s">
+        <v>24</v>
+      </c>
+      <c r="V57" t="s">
+        <v>23</v>
+      </c>
+      <c r="W57" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" s="1">
+        <v>44256</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D58" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" t="s">
+        <v>31</v>
+      </c>
+      <c r="F58" t="s">
+        <v>31</v>
+      </c>
+      <c r="G58">
+        <v>19</v>
+      </c>
+      <c r="H58">
+        <v>143</v>
+      </c>
+      <c r="I58" t="s">
+        <v>31</v>
+      </c>
+      <c r="J58" t="s">
+        <v>31</v>
+      </c>
+      <c r="K58">
+        <v>20</v>
+      </c>
+      <c r="L58">
+        <v>133</v>
+      </c>
+      <c r="M58">
+        <v>22.611858000000002</v>
+      </c>
+      <c r="N58">
+        <v>0.88356599999999996</v>
+      </c>
+      <c r="O58">
+        <v>0.49381000000000003</v>
+      </c>
+      <c r="P58">
+        <v>1.5809500000000001</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>22</v>
+      </c>
+      <c r="R58" t="s">
+        <v>22</v>
+      </c>
+      <c r="S58" t="s">
+        <v>22</v>
+      </c>
+      <c r="T58" t="s">
+        <v>22</v>
+      </c>
+      <c r="U58" t="s">
+        <v>23</v>
+      </c>
+      <c r="V58" t="s">
+        <v>23</v>
+      </c>
+      <c r="W58" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" s="1">
+        <v>44256</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D59" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" t="s">
+        <v>31</v>
+      </c>
+      <c r="F59" t="s">
+        <v>31</v>
+      </c>
+      <c r="G59">
+        <v>61</v>
+      </c>
+      <c r="H59">
+        <v>297</v>
+      </c>
+      <c r="I59" t="s">
+        <v>31</v>
+      </c>
+      <c r="J59" t="s">
+        <v>31</v>
+      </c>
+      <c r="K59">
+        <v>36</v>
+      </c>
+      <c r="L59">
+        <v>150</v>
+      </c>
+      <c r="M59">
+        <v>58.36833</v>
+      </c>
+      <c r="N59">
+        <v>0.85577999999999999</v>
+      </c>
+      <c r="O59">
+        <v>0.59578699999999996</v>
+      </c>
+      <c r="P59">
+        <v>1.22923</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>22</v>
+      </c>
+      <c r="R59" t="s">
+        <v>22</v>
+      </c>
+      <c r="S59" t="s">
+        <v>22</v>
+      </c>
+      <c r="T59" t="s">
+        <v>22</v>
+      </c>
+      <c r="U59" t="s">
+        <v>24</v>
+      </c>
+      <c r="V59" t="s">
+        <v>23</v>
+      </c>
+      <c r="W59" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>35</v>
+      </c>
+      <c r="B60" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D60" t="s">
+        <v>36</v>
+      </c>
+      <c r="E60" t="s">
+        <v>31</v>
+      </c>
+      <c r="F60" t="s">
+        <v>31</v>
+      </c>
+      <c r="G60">
+        <v>44</v>
+      </c>
+      <c r="H60">
+        <v>235</v>
+      </c>
+      <c r="I60" t="s">
+        <v>31</v>
+      </c>
+      <c r="J60" t="s">
+        <v>31</v>
+      </c>
+      <c r="K60">
+        <v>41</v>
+      </c>
+      <c r="L60">
+        <v>229</v>
+      </c>
+      <c r="M60">
+        <v>3.0132330000000001</v>
+      </c>
+      <c r="N60">
+        <v>1.045771</v>
+      </c>
+      <c r="O60">
+        <v>0.71191599999999999</v>
+      </c>
+      <c r="P60">
+        <v>1.5361880000000001</v>
+      </c>
+      <c r="X60" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>35</v>
+      </c>
+      <c r="B61" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D61" t="s">
+        <v>41</v>
+      </c>
+      <c r="E61" t="s">
+        <v>31</v>
+      </c>
+      <c r="F61" t="s">
+        <v>31</v>
+      </c>
+      <c r="G61">
+        <v>8</v>
+      </c>
+      <c r="H61">
+        <v>257</v>
+      </c>
+      <c r="I61" t="s">
+        <v>31</v>
+      </c>
+      <c r="J61" t="s">
+        <v>31</v>
+      </c>
+      <c r="K61">
+        <v>3</v>
+      </c>
+      <c r="L61">
+        <v>254</v>
+      </c>
+      <c r="M61">
+        <v>0.26425199999999999</v>
+      </c>
+      <c r="N61">
+        <v>2.6355379999999999</v>
+      </c>
+      <c r="O61">
+        <v>0.70720499999999997</v>
+      </c>
+      <c r="P61">
+        <v>9.821847</v>
+      </c>
+      <c r="X61" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>35</v>
+      </c>
+      <c r="B62" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D62" t="s">
+        <v>43</v>
+      </c>
+      <c r="E62" t="s">
+        <v>31</v>
+      </c>
+      <c r="F62" t="s">
+        <v>31</v>
+      </c>
+      <c r="G62">
+        <v>44</v>
+      </c>
+      <c r="H62">
+        <v>228</v>
+      </c>
+      <c r="I62" t="s">
+        <v>31</v>
+      </c>
+      <c r="J62" t="s">
+        <v>31</v>
+      </c>
+      <c r="K62">
+        <v>22</v>
+      </c>
+      <c r="L62">
+        <v>105</v>
+      </c>
+      <c r="M62">
+        <v>2.154855</v>
+      </c>
+      <c r="N62">
+        <v>0.92105300000000001</v>
+      </c>
+      <c r="O62">
+        <v>0.583426</v>
+      </c>
+      <c r="P62">
+        <v>1.454064</v>
+      </c>
+      <c r="X62" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>35</v>
+      </c>
+      <c r="B63" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D63" t="s">
+        <v>46</v>
+      </c>
+      <c r="E63" t="s">
+        <v>31</v>
+      </c>
+      <c r="F63" t="s">
+        <v>31</v>
+      </c>
+      <c r="G63">
+        <v>347</v>
+      </c>
+      <c r="H63">
+        <v>701</v>
+      </c>
+      <c r="I63" t="s">
+        <v>31</v>
+      </c>
+      <c r="J63" t="s">
+        <v>31</v>
+      </c>
+      <c r="K63">
+        <v>275</v>
+      </c>
+      <c r="L63">
+        <v>606</v>
+      </c>
+      <c r="M63">
+        <v>26.219619999999999</v>
+      </c>
+      <c r="N63">
+        <v>1.090816</v>
+      </c>
+      <c r="O63">
+        <v>0.97233599999999998</v>
+      </c>
+      <c r="P63">
+        <v>1.223733</v>
+      </c>
+      <c r="X63" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>35</v>
+      </c>
+      <c r="B64" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D64" t="s">
+        <v>48</v>
+      </c>
+      <c r="E64" t="s">
+        <v>31</v>
+      </c>
+      <c r="F64" t="s">
+        <v>31</v>
+      </c>
+      <c r="G64">
+        <v>199</v>
+      </c>
+      <c r="H64">
+        <v>614</v>
+      </c>
+      <c r="I64" t="s">
+        <v>31</v>
+      </c>
+      <c r="J64" t="s">
+        <v>31</v>
+      </c>
+      <c r="K64">
+        <v>86</v>
+      </c>
+      <c r="L64">
+        <v>307</v>
+      </c>
+      <c r="M64">
+        <v>9.2676479999999994</v>
+      </c>
+      <c r="N64">
+        <v>1.1569769999999999</v>
+      </c>
+      <c r="O64">
+        <v>0.93538299999999996</v>
+      </c>
+      <c r="P64">
+        <v>1.4310659999999999</v>
+      </c>
+      <c r="X64" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>35</v>
+      </c>
+      <c r="B65" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D65" t="s">
+        <v>51</v>
+      </c>
+      <c r="E65" t="s">
+        <v>31</v>
+      </c>
+      <c r="F65" t="s">
+        <v>31</v>
+      </c>
+      <c r="G65">
+        <v>1568</v>
+      </c>
+      <c r="H65">
+        <v>5493</v>
+      </c>
+      <c r="I65" t="s">
+        <v>31</v>
+      </c>
+      <c r="J65" t="s">
+        <v>31</v>
+      </c>
+      <c r="K65">
+        <v>1568</v>
+      </c>
+      <c r="L65">
+        <v>5448</v>
+      </c>
+      <c r="M65">
+        <v>59.080393000000001</v>
+      </c>
+      <c r="N65">
+        <v>0.99180800000000002</v>
+      </c>
+      <c r="O65">
+        <v>0.93486999999999998</v>
+      </c>
+      <c r="P65">
+        <v>1.0522130000000001</v>
+      </c>
+      <c r="X65" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>35</v>
+      </c>
+      <c r="B66" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D66" t="s">
+        <v>43</v>
+      </c>
+      <c r="E66" t="s">
+        <v>31</v>
+      </c>
+      <c r="F66" t="s">
+        <v>31</v>
+      </c>
+      <c r="G66">
+        <v>171</v>
+      </c>
+      <c r="H66">
+        <v>228</v>
+      </c>
+      <c r="I66" t="s">
+        <v>31</v>
+      </c>
+      <c r="J66" t="s">
+        <v>31</v>
+      </c>
+      <c r="K66">
+        <v>80</v>
+      </c>
+      <c r="L66">
+        <v>105</v>
+      </c>
+      <c r="M66">
+        <v>3.500273</v>
+      </c>
+      <c r="N66">
+        <v>0.984375</v>
+      </c>
+      <c r="O66">
+        <v>0.86388100000000001</v>
+      </c>
+      <c r="P66">
+        <v>1.1216759999999999</v>
+      </c>
+      <c r="X66" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>35</v>
+      </c>
+      <c r="B67" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D67" t="s">
+        <v>47</v>
+      </c>
+      <c r="E67" t="s">
+        <v>31</v>
+      </c>
+      <c r="F67" t="s">
+        <v>31</v>
+      </c>
+      <c r="G67">
+        <v>26</v>
+      </c>
+      <c r="H67">
+        <v>51</v>
+      </c>
+      <c r="I67" t="s">
+        <v>31</v>
+      </c>
+      <c r="J67" t="s">
+        <v>31</v>
+      </c>
+      <c r="K67">
+        <v>18</v>
+      </c>
+      <c r="L67">
+        <v>50</v>
+      </c>
+      <c r="M67">
+        <v>0.28551799999999999</v>
+      </c>
+      <c r="N67">
+        <v>1.4161220000000001</v>
+      </c>
+      <c r="O67">
+        <v>0.89650200000000002</v>
+      </c>
+      <c r="P67">
+        <v>2.2369180000000002</v>
+      </c>
+      <c r="X67" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>35</v>
+      </c>
+      <c r="B68" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D68" t="s">
+        <v>49</v>
+      </c>
+      <c r="E68" t="s">
+        <v>31</v>
+      </c>
+      <c r="F68" t="s">
+        <v>31</v>
+      </c>
+      <c r="G68">
+        <v>257</v>
+      </c>
+      <c r="H68">
+        <v>320</v>
+      </c>
+      <c r="I68" t="s">
+        <v>31</v>
+      </c>
+      <c r="J68" t="s">
+        <v>31</v>
+      </c>
+      <c r="K68">
+        <v>130</v>
+      </c>
+      <c r="L68">
+        <v>163</v>
+      </c>
+      <c r="M68">
+        <v>6.6862830000000004</v>
+      </c>
+      <c r="N68">
+        <v>1.0069950000000001</v>
+      </c>
+      <c r="O68">
+        <v>0.91621699999999995</v>
+      </c>
+      <c r="P68">
+        <v>1.106768</v>
+      </c>
+      <c r="X68" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>35</v>
+      </c>
+      <c r="B69" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D69" t="s">
+        <v>50</v>
+      </c>
+      <c r="E69" t="s">
+        <v>31</v>
+      </c>
+      <c r="F69" t="s">
+        <v>31</v>
+      </c>
+      <c r="G69">
+        <v>31</v>
+      </c>
+      <c r="H69">
+        <v>43</v>
+      </c>
+      <c r="I69" t="s">
+        <v>31</v>
+      </c>
+      <c r="J69" t="s">
+        <v>31</v>
+      </c>
+      <c r="K69">
+        <v>28</v>
+      </c>
+      <c r="L69">
+        <v>43</v>
+      </c>
+      <c r="M69">
+        <v>0.72387299999999999</v>
+      </c>
+      <c r="N69">
+        <v>1.107143</v>
+      </c>
+      <c r="O69">
+        <v>0.83082</v>
+      </c>
+      <c r="P69">
+        <v>1.475368</v>
+      </c>
+      <c r="X69" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>35</v>
+      </c>
+      <c r="B70" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D70" t="s">
+        <v>51</v>
+      </c>
+      <c r="E70" t="s">
+        <v>31</v>
+      </c>
+      <c r="F70" t="s">
+        <v>31</v>
+      </c>
+      <c r="G70">
+        <v>3832</v>
+      </c>
+      <c r="H70">
+        <v>5795</v>
+      </c>
+      <c r="I70" t="s">
+        <v>31</v>
+      </c>
+      <c r="J70" t="s">
+        <v>31</v>
+      </c>
+      <c r="K70">
+        <v>3822</v>
+      </c>
+      <c r="L70">
+        <v>5763</v>
+      </c>
+      <c r="M70">
+        <v>88.006018999999995</v>
+      </c>
+      <c r="N70">
+        <v>0.99707999999999997</v>
+      </c>
+      <c r="O70">
+        <v>0.97145099999999995</v>
+      </c>
+      <c r="P70">
+        <v>1.023385</v>
+      </c>
+      <c r="X70" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>35</v>
+      </c>
+      <c r="B71" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D71" t="s">
+        <v>55</v>
+      </c>
+      <c r="E71" t="s">
+        <v>31</v>
+      </c>
+      <c r="F71" t="s">
+        <v>31</v>
+      </c>
+      <c r="G71">
+        <v>44</v>
+      </c>
+      <c r="H71">
+        <v>80</v>
+      </c>
+      <c r="I71" t="s">
+        <v>31</v>
+      </c>
+      <c r="J71" t="s">
+        <v>31</v>
+      </c>
+      <c r="K71">
+        <v>46</v>
+      </c>
+      <c r="L71">
+        <v>80</v>
+      </c>
+      <c r="M71">
+        <v>0.79803299999999999</v>
+      </c>
+      <c r="N71">
+        <v>0.95652199999999998</v>
+      </c>
+      <c r="O71">
+        <v>0.72766799999999998</v>
+      </c>
+      <c r="P71">
+        <v>1.25735</v>
+      </c>
+      <c r="X71" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>35</v>
+      </c>
+      <c r="B72" s="1">
+        <v>44317</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D72" t="s">
+        <v>36</v>
+      </c>
+      <c r="E72" t="s">
+        <v>31</v>
+      </c>
+      <c r="F72" t="s">
+        <v>31</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>227</v>
+      </c>
+      <c r="I72" t="s">
+        <v>31</v>
+      </c>
+      <c r="J72" t="s">
+        <v>31</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>224</v>
+      </c>
+      <c r="X72" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>35</v>
+      </c>
+      <c r="B73" s="1">
+        <v>44317</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D73" t="s">
+        <v>37</v>
+      </c>
+      <c r="E73" t="s">
+        <v>31</v>
+      </c>
+      <c r="F73" t="s">
+        <v>31</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>20</v>
+      </c>
+      <c r="I73" t="s">
+        <v>31</v>
+      </c>
+      <c r="J73" t="s">
+        <v>31</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>20</v>
+      </c>
+      <c r="X73" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>35</v>
+      </c>
+      <c r="B74" s="1">
+        <v>44317</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D74" t="s">
+        <v>43</v>
+      </c>
+      <c r="E74" t="s">
+        <v>31</v>
+      </c>
+      <c r="F74" t="s">
+        <v>31</v>
+      </c>
+      <c r="G74">
+        <v>40</v>
+      </c>
+      <c r="H74">
+        <v>228</v>
+      </c>
+      <c r="I74" t="s">
+        <v>31</v>
+      </c>
+      <c r="J74" t="s">
+        <v>31</v>
+      </c>
+      <c r="K74">
+        <v>21</v>
+      </c>
+      <c r="L74">
+        <v>105</v>
+      </c>
+      <c r="M74">
+        <v>88.5</v>
+      </c>
+      <c r="N74">
+        <v>0.877193</v>
+      </c>
+      <c r="O74">
+        <v>0.54556800000000005</v>
+      </c>
+      <c r="P74">
+        <v>1.4103969999999999</v>
+      </c>
+      <c r="X74" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>35</v>
+      </c>
+      <c r="B75" s="1">
+        <v>44317</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D75" t="s">
+        <v>38</v>
+      </c>
+      <c r="E75" t="s">
+        <v>31</v>
+      </c>
+      <c r="F75" t="s">
+        <v>31</v>
+      </c>
+      <c r="G75">
+        <v>4</v>
+      </c>
+      <c r="H75">
+        <v>38</v>
+      </c>
+      <c r="I75" t="s">
+        <v>31</v>
+      </c>
+      <c r="J75" t="s">
+        <v>31</v>
+      </c>
+      <c r="K75">
+        <v>4</v>
+      </c>
+      <c r="L75">
+        <v>43</v>
+      </c>
+      <c r="M75">
+        <v>11.5</v>
+      </c>
+      <c r="N75">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="O75">
+        <v>0.3</v>
+      </c>
+      <c r="P75">
+        <v>4.22</v>
+      </c>
+      <c r="X75" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>35</v>
+      </c>
+      <c r="B76" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D76" t="s">
+        <v>43</v>
+      </c>
+      <c r="E76" t="s">
+        <v>31</v>
+      </c>
+      <c r="F76" t="s">
+        <v>31</v>
+      </c>
+      <c r="G76">
+        <v>54</v>
+      </c>
+      <c r="H76">
+        <v>228</v>
+      </c>
+      <c r="I76" t="s">
+        <v>31</v>
+      </c>
+      <c r="J76" t="s">
+        <v>31</v>
+      </c>
+      <c r="K76">
+        <v>19</v>
+      </c>
+      <c r="L76">
+        <v>105</v>
+      </c>
+      <c r="M76">
+        <v>14.914524999999999</v>
+      </c>
+      <c r="N76">
+        <v>1.308864</v>
+      </c>
+      <c r="O76">
+        <v>0.81892699999999996</v>
+      </c>
+      <c r="P76">
+        <v>2.0919159999999999</v>
+      </c>
+      <c r="X76" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>35</v>
+      </c>
+      <c r="B77" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D77" t="s">
+        <v>44</v>
+      </c>
+      <c r="E77" t="s">
+        <v>31</v>
+      </c>
+      <c r="F77" t="s">
+        <v>31</v>
+      </c>
+      <c r="G77">
+        <v>12</v>
+      </c>
+      <c r="H77">
+        <v>40</v>
+      </c>
+      <c r="I77" t="s">
+        <v>31</v>
+      </c>
+      <c r="J77" t="s">
+        <v>31</v>
+      </c>
+      <c r="K77">
+        <v>15</v>
+      </c>
+      <c r="L77">
+        <v>39</v>
+      </c>
+      <c r="M77">
+        <v>10.218532</v>
+      </c>
+      <c r="N77">
+        <v>0.78</v>
+      </c>
+      <c r="O77">
+        <v>0.42051899999999998</v>
+      </c>
+      <c r="P77">
+        <v>1.446785</v>
+      </c>
+      <c r="X77" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>35</v>
+      </c>
+      <c r="B78" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D78" t="s">
+        <v>48</v>
+      </c>
+      <c r="E78" t="s">
+        <v>31</v>
+      </c>
+      <c r="F78" t="s">
+        <v>31</v>
+      </c>
+      <c r="G78">
+        <v>205</v>
+      </c>
+      <c r="H78">
+        <v>614</v>
+      </c>
+      <c r="I78" t="s">
+        <v>31</v>
+      </c>
+      <c r="J78" t="s">
+        <v>31</v>
+      </c>
+      <c r="K78">
+        <v>81</v>
+      </c>
+      <c r="L78">
+        <v>307</v>
+      </c>
+      <c r="M78">
+        <v>29.240273999999999</v>
+      </c>
+      <c r="N78">
+        <v>1.2654319999999999</v>
+      </c>
+      <c r="O78">
+        <v>1.017868</v>
+      </c>
+      <c r="P78">
+        <v>1.5732090000000001</v>
+      </c>
+      <c r="X78" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>35</v>
+      </c>
+      <c r="B79" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D79" t="s">
+        <v>49</v>
+      </c>
+      <c r="E79" t="s">
+        <v>31</v>
+      </c>
+      <c r="F79" t="s">
+        <v>31</v>
+      </c>
+      <c r="G79">
+        <v>66</v>
+      </c>
+      <c r="H79">
+        <v>320</v>
+      </c>
+      <c r="I79" t="s">
+        <v>31</v>
+      </c>
+      <c r="J79" t="s">
+        <v>31</v>
+      </c>
+      <c r="K79">
+        <v>34</v>
+      </c>
+      <c r="L79">
+        <v>163</v>
+      </c>
+      <c r="M79">
+        <v>19.607727000000001</v>
+      </c>
+      <c r="N79">
+        <v>0.98878699999999997</v>
+      </c>
+      <c r="O79">
+        <v>0.68417799999999995</v>
+      </c>
+      <c r="P79">
+        <v>1.429014</v>
+      </c>
+      <c r="X79" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>35</v>
+      </c>
+      <c r="B80" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D80" t="s">
+        <v>46</v>
+      </c>
+      <c r="E80" t="s">
+        <v>31</v>
+      </c>
+      <c r="F80" t="s">
+        <v>31</v>
+      </c>
+      <c r="G80">
+        <v>32</v>
+      </c>
+      <c r="H80">
+        <v>1075</v>
+      </c>
+      <c r="I80" t="s">
+        <v>31</v>
+      </c>
+      <c r="J80" t="s">
+        <v>31</v>
+      </c>
+      <c r="K80">
+        <v>12</v>
+      </c>
+      <c r="L80">
+        <v>905</v>
+      </c>
+      <c r="M80">
+        <v>9.301444</v>
+      </c>
+      <c r="N80">
+        <v>2.244961</v>
+      </c>
+      <c r="O80">
+        <v>1.163178</v>
+      </c>
+      <c r="P80">
+        <v>4.3328290000000003</v>
+      </c>
+      <c r="X80" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="81" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>35</v>
+      </c>
+      <c r="B81" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D81" t="s">
+        <v>52</v>
+      </c>
+      <c r="E81" t="s">
+        <v>31</v>
+      </c>
+      <c r="F81" t="s">
+        <v>31</v>
+      </c>
+      <c r="G81">
+        <v>22</v>
+      </c>
+      <c r="H81">
+        <v>53</v>
+      </c>
+      <c r="I81" t="s">
+        <v>31</v>
+      </c>
+      <c r="J81" t="s">
+        <v>31</v>
+      </c>
+      <c r="K81">
+        <v>25</v>
+      </c>
+      <c r="L81">
+        <v>52</v>
+      </c>
+      <c r="M81">
+        <v>16.717497999999999</v>
+      </c>
+      <c r="N81">
+        <v>0.86339600000000005</v>
+      </c>
+      <c r="O81">
+        <v>0.563608</v>
+      </c>
+      <c r="P81">
+        <v>1.322646</v>
+      </c>
+      <c r="X81" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>60</v>
+      </c>
+      <c r="B82" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D82" t="s">
+        <v>63</v>
+      </c>
+      <c r="E82" t="s">
+        <v>31</v>
+      </c>
+      <c r="F82" t="s">
+        <v>31</v>
+      </c>
+      <c r="G82">
+        <v>1</v>
+      </c>
+      <c r="H82">
+        <v>30</v>
+      </c>
+      <c r="I82" t="s">
+        <v>31</v>
+      </c>
+      <c r="J82" t="s">
+        <v>31</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <v>15</v>
+      </c>
+      <c r="M82">
+        <v>100</v>
+      </c>
+      <c r="N82">
+        <v>1.548387</v>
+      </c>
+      <c r="O82">
+        <v>6.6803000000000001E-2</v>
+      </c>
+      <c r="P82">
+        <v>35.889386000000002</v>
+      </c>
+      <c r="X82" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>60</v>
+      </c>
+      <c r="B83" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D83" t="s">
+        <v>99</v>
+      </c>
+      <c r="E83" t="s">
+        <v>31</v>
+      </c>
+      <c r="F83" t="s">
+        <v>31</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>100</v>
+      </c>
+      <c r="I83" t="s">
+        <v>31</v>
+      </c>
+      <c r="J83" t="s">
+        <v>31</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>52</v>
+      </c>
+      <c r="M83" t="s">
+        <v>31</v>
+      </c>
+      <c r="N83" t="s">
+        <v>31</v>
+      </c>
+      <c r="O83" t="s">
+        <v>31</v>
+      </c>
+      <c r="P83" t="s">
+        <v>31</v>
+      </c>
+      <c r="X83" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>60</v>
+      </c>
+      <c r="B84" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D84" t="s">
+        <v>63</v>
+      </c>
+      <c r="E84" t="s">
+        <v>31</v>
+      </c>
+      <c r="F84" t="s">
+        <v>31</v>
+      </c>
+      <c r="G84">
+        <v>13</v>
+      </c>
+      <c r="H84">
+        <v>30</v>
+      </c>
+      <c r="I84" t="s">
+        <v>31</v>
+      </c>
+      <c r="J84" t="s">
+        <v>31</v>
+      </c>
+      <c r="K84">
+        <v>5</v>
+      </c>
+      <c r="L84">
+        <v>15</v>
+      </c>
+      <c r="M84">
+        <v>42.656703999999998</v>
+      </c>
+      <c r="N84">
+        <v>1.3</v>
+      </c>
+      <c r="O84">
+        <v>0.57004500000000002</v>
+      </c>
+      <c r="P84">
+        <v>2.9646789999999998</v>
+      </c>
+      <c r="X84" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>60</v>
+      </c>
+      <c r="B85" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D85" t="s">
+        <v>99</v>
+      </c>
+      <c r="E85" t="s">
+        <v>31</v>
+      </c>
+      <c r="F85" t="s">
+        <v>31</v>
+      </c>
+      <c r="G85">
+        <v>14</v>
+      </c>
+      <c r="H85">
+        <v>100</v>
+      </c>
+      <c r="I85" t="s">
+        <v>31</v>
+      </c>
+      <c r="J85" t="s">
+        <v>31</v>
+      </c>
+      <c r="K85">
+        <v>6</v>
+      </c>
+      <c r="L85">
+        <v>52</v>
+      </c>
+      <c r="M85">
+        <v>36.133265999999999</v>
+      </c>
+      <c r="N85">
+        <v>1.213333</v>
+      </c>
+      <c r="O85">
+        <v>0.49541200000000002</v>
+      </c>
+      <c r="P85">
+        <v>2.9716230000000001</v>
+      </c>
+      <c r="X85" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>60</v>
+      </c>
+      <c r="B86" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D86" t="s">
+        <v>100</v>
+      </c>
+      <c r="E86" t="s">
+        <v>31</v>
+      </c>
+      <c r="F86" t="s">
+        <v>31</v>
+      </c>
+      <c r="G86">
+        <v>7</v>
+      </c>
+      <c r="H86">
+        <v>27</v>
+      </c>
+      <c r="I86" t="s">
+        <v>31</v>
+      </c>
+      <c r="J86" t="s">
+        <v>31</v>
+      </c>
+      <c r="K86">
+        <v>2</v>
+      </c>
+      <c r="L86">
+        <v>4</v>
+      </c>
+      <c r="M86">
+        <v>21.210031000000001</v>
+      </c>
+      <c r="N86">
+        <v>0.51851899999999995</v>
+      </c>
+      <c r="O86">
+        <v>0.16107099999999999</v>
+      </c>
+      <c r="P86">
+        <v>1.6692119999999999</v>
+      </c>
+      <c r="X86" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>60</v>
+      </c>
+      <c r="B87" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D87" t="s">
+        <v>62</v>
+      </c>
+      <c r="E87" t="s">
+        <v>31</v>
+      </c>
+      <c r="F87" t="s">
+        <v>31</v>
+      </c>
+      <c r="G87">
+        <v>13</v>
+      </c>
+      <c r="H87">
+        <v>32</v>
+      </c>
+      <c r="I87" t="s">
+        <v>31</v>
+      </c>
+      <c r="J87" t="s">
+        <v>31</v>
+      </c>
+      <c r="K87">
+        <v>18</v>
+      </c>
+      <c r="L87">
+        <v>44</v>
+      </c>
+      <c r="M87">
+        <v>38.639063999999998</v>
+      </c>
+      <c r="N87">
+        <v>0.99305600000000005</v>
+      </c>
+      <c r="O87">
+        <v>0.573434</v>
+      </c>
+      <c r="P87">
+        <v>1.7197450000000001</v>
+      </c>
+      <c r="X87" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>60</v>
+      </c>
+      <c r="B88" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D88" t="s">
+        <v>99</v>
+      </c>
+      <c r="E88" t="s">
+        <v>31</v>
+      </c>
+      <c r="F88" t="s">
+        <v>31</v>
+      </c>
+      <c r="G88">
+        <v>33</v>
+      </c>
+      <c r="H88">
+        <v>80</v>
+      </c>
+      <c r="I88" t="s">
+        <v>31</v>
+      </c>
+      <c r="J88" t="s">
+        <v>31</v>
+      </c>
+      <c r="K88">
+        <v>14</v>
+      </c>
+      <c r="L88">
+        <v>45</v>
+      </c>
+      <c r="M88">
+        <v>45.265588999999999</v>
+      </c>
+      <c r="N88">
+        <v>1.325893</v>
+      </c>
+      <c r="O88">
+        <v>0.79829799999999995</v>
+      </c>
+      <c r="P88">
+        <v>2.202175</v>
+      </c>
+      <c r="X88" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="89" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>60</v>
+      </c>
+      <c r="B89" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D89" t="s">
+        <v>100</v>
+      </c>
+      <c r="E89" t="s">
+        <v>31</v>
+      </c>
+      <c r="F89" t="s">
+        <v>31</v>
+      </c>
+      <c r="G89">
+        <v>17</v>
+      </c>
+      <c r="H89">
+        <v>27</v>
+      </c>
+      <c r="I89" t="s">
+        <v>31</v>
+      </c>
+      <c r="J89" t="s">
+        <v>31</v>
+      </c>
+      <c r="K89">
+        <v>2</v>
+      </c>
+      <c r="L89">
+        <v>3</v>
+      </c>
+      <c r="M89">
+        <v>16.095347</v>
+      </c>
+      <c r="N89">
+        <v>0.94444399999999995</v>
+      </c>
+      <c r="O89">
+        <v>0.40332899999999999</v>
+      </c>
+      <c r="P89">
+        <v>2.2115320000000001</v>
+      </c>
+      <c r="X89" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>64</v>
+      </c>
+      <c r="B90" s="1">
+        <v>44287</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D90" t="s">
+        <v>65</v>
+      </c>
+      <c r="E90" t="s">
+        <v>31</v>
+      </c>
+      <c r="F90" t="s">
+        <v>31</v>
+      </c>
+      <c r="G90">
+        <v>47</v>
+      </c>
+      <c r="H90">
+        <v>267</v>
+      </c>
+      <c r="I90" t="s">
+        <v>31</v>
+      </c>
+      <c r="J90" t="s">
+        <v>31</v>
+      </c>
+      <c r="K90">
+        <v>133</v>
+      </c>
+      <c r="L90">
+        <v>263</v>
+      </c>
+      <c r="M90">
+        <v>17.866872999999998</v>
+      </c>
+      <c r="N90">
+        <v>0.34808899999999998</v>
+      </c>
+      <c r="O90">
+        <v>0.26158599999999999</v>
+      </c>
+      <c r="P90">
+        <v>0.463198</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>22</v>
+      </c>
+      <c r="R90" t="s">
+        <v>22</v>
+      </c>
+      <c r="S90" t="s">
+        <v>24</v>
+      </c>
+      <c r="T90" t="s">
+        <v>22</v>
+      </c>
+      <c r="U90" t="s">
+        <v>22</v>
+      </c>
+      <c r="V90" t="s">
+        <v>22</v>
+      </c>
+      <c r="W90" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="91" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>64</v>
+      </c>
+      <c r="B91" s="1">
+        <v>44287</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D91" t="s">
+        <v>66</v>
+      </c>
+      <c r="E91" t="s">
+        <v>31</v>
+      </c>
+      <c r="F91" t="s">
+        <v>31</v>
+      </c>
+      <c r="G91">
+        <v>37</v>
+      </c>
+      <c r="H91">
+        <v>277</v>
+      </c>
+      <c r="I91" t="s">
+        <v>31</v>
+      </c>
+      <c r="J91" t="s">
+        <v>31</v>
+      </c>
+      <c r="K91">
+        <v>116</v>
+      </c>
+      <c r="L91">
+        <v>263</v>
+      </c>
+      <c r="M91">
+        <v>15.675273000000001</v>
+      </c>
+      <c r="N91">
+        <v>0.30284499999999998</v>
+      </c>
+      <c r="O91">
+        <v>0.217866</v>
+      </c>
+      <c r="P91">
+        <v>0.42096899999999998</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>22</v>
+      </c>
+      <c r="R91" t="s">
+        <v>22</v>
+      </c>
+      <c r="S91" t="s">
+        <v>22</v>
+      </c>
+      <c r="T91" t="s">
+        <v>22</v>
+      </c>
+      <c r="U91" t="s">
+        <v>22</v>
+      </c>
+      <c r="V91" t="s">
+        <v>22</v>
+      </c>
+      <c r="W91" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="92" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>64</v>
+      </c>
+      <c r="B92" s="1">
+        <v>44287</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D92" t="s">
+        <v>67</v>
+      </c>
+      <c r="E92" t="s">
+        <v>31</v>
+      </c>
+      <c r="F92" t="s">
+        <v>31</v>
+      </c>
+      <c r="G92">
+        <v>100</v>
+      </c>
+      <c r="H92">
+        <v>636</v>
+      </c>
+      <c r="I92" t="s">
+        <v>31</v>
+      </c>
+      <c r="J92" t="s">
+        <v>31</v>
+      </c>
+      <c r="K92">
+        <v>238</v>
+      </c>
+      <c r="L92">
+        <v>615</v>
+      </c>
+      <c r="M92">
+        <v>22.473483999999999</v>
+      </c>
+      <c r="N92">
+        <v>0.40629500000000002</v>
+      </c>
+      <c r="O92">
+        <v>0.33078999999999997</v>
+      </c>
+      <c r="P92">
+        <v>0.499033</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>22</v>
+      </c>
+      <c r="R92" t="s">
+        <v>22</v>
+      </c>
+      <c r="S92" t="s">
+        <v>22</v>
+      </c>
+      <c r="T92" t="s">
+        <v>22</v>
+      </c>
+      <c r="U92" t="s">
+        <v>22</v>
+      </c>
+      <c r="V92" t="s">
+        <v>22</v>
+      </c>
+      <c r="W92" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="93" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>64</v>
+      </c>
+      <c r="B93" s="1">
+        <v>44287</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D93" t="s">
+        <v>68</v>
+      </c>
+      <c r="E93" t="s">
+        <v>31</v>
+      </c>
+      <c r="F93" t="s">
+        <v>31</v>
+      </c>
+      <c r="G93">
+        <v>46</v>
+      </c>
+      <c r="H93">
+        <v>154</v>
+      </c>
+      <c r="I93" t="s">
+        <v>31</v>
+      </c>
+      <c r="J93" t="s">
+        <v>31</v>
+      </c>
+      <c r="K93">
+        <v>77</v>
+      </c>
+      <c r="L93">
+        <v>150</v>
+      </c>
+      <c r="M93">
+        <v>17.753844999999998</v>
+      </c>
+      <c r="N93">
+        <v>0.58188600000000001</v>
+      </c>
+      <c r="O93">
+        <v>0.43635099999999999</v>
+      </c>
+      <c r="P93">
+        <v>0.77596100000000001</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>22</v>
+      </c>
+      <c r="R93" t="s">
+        <v>22</v>
+      </c>
+      <c r="S93" t="s">
+        <v>24</v>
+      </c>
+      <c r="T93" t="s">
+        <v>22</v>
+      </c>
+      <c r="U93" t="s">
+        <v>22</v>
+      </c>
+      <c r="V93" t="s">
+        <v>22</v>
+      </c>
+      <c r="W93" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="94" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>64</v>
+      </c>
+      <c r="B94" s="1">
+        <v>44287</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D94" t="s">
+        <v>69</v>
+      </c>
+      <c r="E94" t="s">
+        <v>31</v>
+      </c>
+      <c r="F94" t="s">
+        <v>31</v>
+      </c>
+      <c r="G94">
+        <v>53</v>
+      </c>
+      <c r="H94">
+        <v>369</v>
+      </c>
+      <c r="I94" t="s">
+        <v>31</v>
+      </c>
+      <c r="J94" t="s">
+        <v>31</v>
+      </c>
+      <c r="K94">
+        <v>116</v>
+      </c>
+      <c r="L94">
+        <v>352</v>
+      </c>
+      <c r="M94">
+        <v>17.6236</v>
+      </c>
+      <c r="N94">
+        <v>0.43584699999999998</v>
+      </c>
+      <c r="O94">
+        <v>0.32603100000000002</v>
+      </c>
+      <c r="P94">
+        <v>0.58265100000000003</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>22</v>
+      </c>
+      <c r="R94" t="s">
+        <v>22</v>
+      </c>
+      <c r="S94" t="s">
+        <v>24</v>
+      </c>
+      <c r="T94" t="s">
+        <v>22</v>
+      </c>
+      <c r="U94" t="s">
+        <v>24</v>
+      </c>
+      <c r="V94" t="s">
+        <v>22</v>
+      </c>
+      <c r="W94" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="95" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>72</v>
+      </c>
+      <c r="B95" s="1">
+        <v>44409</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D95" t="s">
+        <v>73</v>
+      </c>
+      <c r="E95" t="s">
+        <v>31</v>
+      </c>
+      <c r="F95" t="s">
+        <v>31</v>
+      </c>
+      <c r="G95">
+        <v>305</v>
+      </c>
+      <c r="H95">
+        <v>532</v>
+      </c>
+      <c r="I95" t="s">
+        <v>31</v>
+      </c>
+      <c r="J95" t="s">
+        <v>31</v>
+      </c>
+      <c r="K95">
+        <v>323</v>
+      </c>
+      <c r="L95">
+        <v>516</v>
+      </c>
+      <c r="M95">
+        <v>31.016203000000001</v>
+      </c>
+      <c r="N95">
+        <v>0.91587300000000005</v>
+      </c>
+      <c r="O95">
+        <v>0.82945500000000005</v>
+      </c>
+      <c r="P95">
+        <v>1.0112950000000001</v>
+      </c>
+      <c r="X95" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="96" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>72</v>
+      </c>
+      <c r="B96" s="1">
+        <v>44409</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D96" t="s">
+        <v>74</v>
+      </c>
+      <c r="E96" t="s">
+        <v>31</v>
+      </c>
+      <c r="F96" t="s">
+        <v>31</v>
+      </c>
+      <c r="G96">
+        <v>113</v>
+      </c>
+      <c r="H96">
+        <v>193</v>
+      </c>
+      <c r="I96" t="s">
+        <v>31</v>
+      </c>
+      <c r="J96" t="s">
+        <v>31</v>
+      </c>
+      <c r="K96">
+        <v>93</v>
+      </c>
+      <c r="L96">
+        <v>200</v>
+      </c>
+      <c r="M96">
+        <v>20.559826000000001</v>
+      </c>
+      <c r="N96">
+        <v>1.259123</v>
+      </c>
+      <c r="O96">
+        <v>1.040997</v>
+      </c>
+      <c r="P96">
+        <v>1.5229539999999999</v>
+      </c>
+      <c r="X96" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="97" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>72</v>
+      </c>
+      <c r="B97" s="1">
+        <v>44927</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D97" t="s">
+        <v>102</v>
+      </c>
+      <c r="E97" t="s">
+        <v>31</v>
+      </c>
+      <c r="F97" t="s">
+        <v>31</v>
+      </c>
+      <c r="G97">
+        <v>241</v>
+      </c>
+      <c r="H97">
+        <v>406</v>
+      </c>
+      <c r="I97" t="s">
+        <v>31</v>
+      </c>
+      <c r="J97" t="s">
+        <v>31</v>
+      </c>
+      <c r="K97">
+        <v>236</v>
+      </c>
+      <c r="L97">
+        <v>418</v>
+      </c>
+      <c r="M97">
+        <v>28.927900000000001</v>
+      </c>
+      <c r="N97">
+        <v>1.051369</v>
+      </c>
+      <c r="O97">
+        <v>0.93577900000000003</v>
+      </c>
+      <c r="P97">
+        <v>1.181238</v>
+      </c>
+      <c r="X97" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="98" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>72</v>
+      </c>
+      <c r="B98" s="1">
+        <v>44409</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D98" t="s">
+        <v>76</v>
+      </c>
+      <c r="E98" t="s">
+        <v>31</v>
+      </c>
+      <c r="F98" t="s">
+        <v>31</v>
+      </c>
+      <c r="G98">
+        <v>102</v>
+      </c>
+      <c r="H98">
+        <v>155</v>
+      </c>
+      <c r="I98" t="s">
+        <v>31</v>
+      </c>
+      <c r="J98" t="s">
+        <v>31</v>
+      </c>
+      <c r="K98">
+        <v>50</v>
+      </c>
+      <c r="L98">
+        <v>78</v>
+      </c>
+      <c r="M98">
+        <v>19.496071000000001</v>
+      </c>
+      <c r="N98">
+        <v>1.026581</v>
+      </c>
+      <c r="O98">
+        <v>0.83953500000000003</v>
+      </c>
+      <c r="P98">
+        <v>1.2552989999999999</v>
+      </c>
+      <c r="X98" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="99" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>72</v>
+      </c>
+      <c r="B99" s="1">
+        <v>44409</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D99" t="s">
+        <v>73</v>
+      </c>
+      <c r="E99" t="s">
+        <v>31</v>
+      </c>
+      <c r="F99" t="s">
+        <v>31</v>
+      </c>
+      <c r="G99">
+        <v>130</v>
+      </c>
+      <c r="H99">
+        <v>532</v>
+      </c>
+      <c r="I99" t="s">
+        <v>31</v>
+      </c>
+      <c r="J99" t="s">
+        <v>31</v>
+      </c>
+      <c r="K99">
+        <v>163</v>
+      </c>
+      <c r="L99">
+        <v>516</v>
+      </c>
+      <c r="M99">
+        <v>37.366193000000003</v>
+      </c>
+      <c r="N99">
+        <v>0.77356000000000003</v>
+      </c>
+      <c r="O99">
+        <v>0.63581799999999999</v>
+      </c>
+      <c r="P99">
+        <v>0.94114100000000001</v>
+      </c>
+      <c r="X99" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="100" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>72</v>
+      </c>
+      <c r="B100" s="1">
+        <v>44409</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D100" t="s">
+        <v>74</v>
+      </c>
+      <c r="E100" t="s">
+        <v>31</v>
+      </c>
+      <c r="F100" t="s">
+        <v>31</v>
+      </c>
+      <c r="G100">
+        <v>10</v>
+      </c>
+      <c r="H100">
+        <v>193</v>
+      </c>
+      <c r="I100" t="s">
+        <v>31</v>
+      </c>
+      <c r="J100" t="s">
+        <v>31</v>
+      </c>
+      <c r="K100">
+        <v>18</v>
+      </c>
+      <c r="L100">
+        <v>200</v>
+      </c>
+      <c r="M100">
+        <v>9.1363339999999997</v>
+      </c>
+      <c r="N100">
+        <v>0.57570500000000002</v>
+      </c>
+      <c r="O100">
+        <v>0.27268100000000001</v>
+      </c>
+      <c r="P100">
+        <v>1.2154750000000001</v>
+      </c>
+      <c r="X100" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>72</v>
+      </c>
+      <c r="B101" s="1">
+        <v>44927</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D101" t="s">
+        <v>102</v>
+      </c>
+      <c r="E101" t="s">
+        <v>31</v>
+      </c>
+      <c r="F101" t="s">
+        <v>31</v>
+      </c>
+      <c r="G101">
+        <v>135</v>
+      </c>
+      <c r="H101">
+        <v>406</v>
+      </c>
+      <c r="I101" t="s">
+        <v>31</v>
+      </c>
+      <c r="J101" t="s">
+        <v>31</v>
+      </c>
+      <c r="K101">
+        <v>130</v>
+      </c>
+      <c r="L101">
+        <v>418</v>
+      </c>
+      <c r="M101">
+        <v>37.167059000000002</v>
+      </c>
+      <c r="N101">
+        <v>1.0691550000000001</v>
+      </c>
+      <c r="O101">
+        <v>0.87677300000000002</v>
+      </c>
+      <c r="P101">
+        <v>1.30375</v>
+      </c>
+      <c r="X101" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>72</v>
+      </c>
+      <c r="B102" s="1">
+        <v>44409</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D102" t="s">
+        <v>76</v>
+      </c>
+      <c r="E102" t="s">
+        <v>31</v>
+      </c>
+      <c r="F102" t="s">
+        <v>31</v>
+      </c>
+      <c r="G102">
+        <v>28</v>
+      </c>
+      <c r="H102">
+        <v>155</v>
+      </c>
+      <c r="I102" t="s">
+        <v>31</v>
+      </c>
+      <c r="J102" t="s">
+        <v>31</v>
+      </c>
+      <c r="K102">
+        <v>20</v>
+      </c>
+      <c r="L102">
+        <v>78</v>
+      </c>
+      <c r="M102">
+        <v>16.330414999999999</v>
+      </c>
+      <c r="N102">
+        <v>0.70451600000000003</v>
+      </c>
+      <c r="O102">
+        <v>0.425091</v>
+      </c>
+      <c r="P102">
+        <v>1.167616</v>
+      </c>
+      <c r="X102" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>88</v>
+      </c>
+      <c r="B103" s="1">
+        <v>44866</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D103" t="s">
+        <v>105</v>
+      </c>
+      <c r="E103" t="s">
+        <v>31</v>
+      </c>
+      <c r="F103" t="s">
+        <v>31</v>
+      </c>
+      <c r="G103">
+        <v>2</v>
+      </c>
+      <c r="H103">
+        <v>34</v>
+      </c>
+      <c r="I103" t="s">
+        <v>31</v>
+      </c>
+      <c r="J103" t="s">
+        <v>31</v>
+      </c>
+      <c r="K103">
+        <v>12</v>
+      </c>
+      <c r="L103">
+        <v>28</v>
+      </c>
+      <c r="M103">
+        <v>26.489611</v>
+      </c>
+      <c r="N103">
+        <v>0.13725499999999999</v>
+      </c>
+      <c r="O103">
+        <v>3.3479000000000002E-2</v>
+      </c>
+      <c r="P103">
+        <v>0.56270299999999995</v>
+      </c>
+      <c r="X103" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="104" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>88</v>
+      </c>
+      <c r="B104" s="1">
+        <v>44866</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D104" t="s">
+        <v>81</v>
+      </c>
+      <c r="E104" t="s">
+        <v>31</v>
+      </c>
+      <c r="F104" t="s">
+        <v>31</v>
+      </c>
+      <c r="G104">
+        <v>80</v>
+      </c>
+      <c r="H104">
+        <v>194</v>
+      </c>
+      <c r="I104" t="s">
+        <v>31</v>
+      </c>
+      <c r="J104" t="s">
+        <v>31</v>
+      </c>
+      <c r="K104">
+        <v>82</v>
+      </c>
+      <c r="L104">
+        <v>199</v>
+      </c>
+      <c r="M104">
+        <v>42.929988999999999</v>
+      </c>
+      <c r="N104">
+        <v>1.0007539999999999</v>
+      </c>
+      <c r="O104">
+        <v>0.790269</v>
+      </c>
+      <c r="P104">
+        <v>1.2673019999999999</v>
+      </c>
+      <c r="X104" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="105" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>88</v>
+      </c>
+      <c r="B105" s="1">
+        <v>44866</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D105" t="s">
+        <v>82</v>
+      </c>
+      <c r="E105" t="s">
+        <v>31</v>
+      </c>
+      <c r="F105" t="s">
+        <v>31</v>
+      </c>
+      <c r="G105">
+        <v>7</v>
+      </c>
+      <c r="H105">
+        <v>16</v>
+      </c>
+      <c r="I105" t="s">
+        <v>31</v>
+      </c>
+      <c r="J105" t="s">
+        <v>31</v>
+      </c>
+      <c r="K105">
+        <v>3</v>
+      </c>
+      <c r="L105">
+        <v>14</v>
+      </c>
+      <c r="M105">
+        <v>30.580400000000001</v>
+      </c>
+      <c r="N105">
+        <v>2.0416669999999999</v>
+      </c>
+      <c r="O105">
+        <v>0.64864200000000005</v>
+      </c>
+      <c r="P105">
+        <v>6.4263529999999998</v>
+      </c>
+      <c r="X105" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -3269,19 +6757,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E6B89F4-E48E-4E03-B88F-4C83697BDFFF}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.08984375" customWidth="1"/>
+    <col min="5" max="5" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -3289,33 +6779,39 @@
         <v>33</v>
       </c>
       <c r="C1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1" t="s">
         <v>25</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>26</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>27</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>28</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>15</v>
       </c>
       <c r="B2" s="1">
         <v>44256</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
+      <c r="C2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -3326,166 +6822,707 @@
       <c r="G2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="1">
+        <v>44256</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1">
+        <v>44256</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="1">
+        <v>44256</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1">
+        <v>44256</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="1">
+        <v>44317</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="1">
+        <v>44317</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="1">
-        <v>44958</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="B13" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="1">
-        <v>44317</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="1">
+      <c r="B14" s="1">
+        <v>44378</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" s="2">
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="1">
         <v>44713</v>
       </c>
-      <c r="C5">
+      <c r="C15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2</v>
+      </c>
+      <c r="E15">
         <v>1</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="1">
-        <v>44378</v>
-      </c>
-      <c r="C6">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2</v>
+      </c>
+      <c r="E16">
         <v>1</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7" s="1">
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="1">
         <v>44287</v>
       </c>
-      <c r="C7">
+      <c r="C18" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="2">
         <v>1</v>
       </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="1">
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="1">
+        <v>44287</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="1">
         <v>44927</v>
       </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
+      <c r="C20" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="2">
+        <v>2</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" s="1">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="1">
+        <v>44927</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" s="2">
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="1">
+        <v>44927</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" s="2">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="1">
+        <v>44409</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" s="2">
+        <v>2</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="1">
+        <v>44409</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D24" s="2">
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>88</v>
+      </c>
+      <c r="B25" s="1">
         <v>44866</v>
       </c>
-      <c r="C9">
+      <c r="C25" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="2">
+        <v>2</v>
+      </c>
+      <c r="E25">
         <v>1</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B26" s="1">
+        <v>44866</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D26" s="2">
+        <v>2</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Datasets/primary_info.xlsx
+++ b/Datasets/primary_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniofleicester-my.sharepoint.com/personal/crn4_leicester_ac_uk/Documents/PhD/WP2/3. Create tool/Datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="175" documentId="13_ncr:1_{009773F8-B678-42EB-90F1-9F0C232CDCBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{822D7B83-ECDF-49B6-A4B0-022AF6B2BE2D}"/>
+  <xr:revisionPtr revIDLastSave="420" documentId="13_ncr:1_{009773F8-B678-42EB-90F1-9F0C232CDCBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{907FD90A-E196-465D-9806-713BC011015B}"/>
   <bookViews>
-    <workbookView xWindow="-4290" yWindow="2370" windowWidth="8535" windowHeight="4530" xr2:uid="{E19E56DC-86BE-4713-A769-C66B74D62B61}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{E19E56DC-86BE-4713-A769-C66B74D62B61}"/>
   </bookViews>
   <sheets>
     <sheet name="Studies" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="145">
   <si>
     <t>Study</t>
   </si>
@@ -356,6 +356,123 @@
   </si>
   <si>
     <t>Edalatifard 2020</t>
+  </si>
+  <si>
+    <t>Oral anticoagulation</t>
+  </si>
+  <si>
+    <t>Mortality6</t>
+  </si>
+  <si>
+    <t>Mortality12</t>
+  </si>
+  <si>
+    <t>Major bleeding</t>
+  </si>
+  <si>
+    <t>Minor bleeding</t>
+  </si>
+  <si>
+    <t>Chahinian 1989</t>
+  </si>
+  <si>
+    <t>Maurer 1997</t>
+  </si>
+  <si>
+    <t>Zacharski 1984</t>
+  </si>
+  <si>
+    <t>Levine 1994</t>
+  </si>
+  <si>
+    <t>Stanford 1979</t>
+  </si>
+  <si>
+    <t>Inhaled corticosteroids COVID-19</t>
+  </si>
+  <si>
+    <t>Hospital or death</t>
+  </si>
+  <si>
+    <t>Symptom resolution</t>
+  </si>
+  <si>
+    <t>Clemency 2021</t>
+  </si>
+  <si>
+    <t>Ramakrishnan 2021</t>
+  </si>
+  <si>
+    <t>Yu 2021</t>
+  </si>
+  <si>
+    <t>Janus kinase inhibitors COVID-19</t>
+  </si>
+  <si>
+    <t>Mortality28</t>
+  </si>
+  <si>
+    <t>Mortality60</t>
+  </si>
+  <si>
+    <t>Infection</t>
+  </si>
+  <si>
+    <t>Cao 2020</t>
+  </si>
+  <si>
+    <t>Ely 2022</t>
+  </si>
+  <si>
+    <t>Guimarães 2021</t>
+  </si>
+  <si>
+    <t>Horby 2022</t>
+  </si>
+  <si>
+    <t>Kalil 2021</t>
+  </si>
+  <si>
+    <t>Marconi 2021</t>
+  </si>
+  <si>
+    <t>Colchicine COVID-19</t>
+  </si>
+  <si>
+    <t>Deftereos 2020</t>
+  </si>
+  <si>
+    <t>Fluvoxamine COVID-19</t>
+  </si>
+  <si>
+    <t>Lenze 2020</t>
+  </si>
+  <si>
+    <t>TOGETHER 2021</t>
+  </si>
+  <si>
+    <t>Antibiotics COVID-19</t>
+  </si>
+  <si>
+    <t>Arrhythmias</t>
+  </si>
+  <si>
+    <t>Cavalcanti 2020</t>
+  </si>
+  <si>
+    <t>Sekhavati 2020</t>
+  </si>
+  <si>
+    <t>Furtado 2020</t>
+  </si>
+  <si>
+    <t>RECOVERY 2021</t>
+  </si>
+  <si>
+    <t>CJWT629A12301</t>
+  </si>
+  <si>
+    <t>NCT04335552</t>
   </si>
 </sst>
 </file>
@@ -715,25 +832,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FF7956F-2BD5-4B54-899A-FD221CF1CF1D}">
-  <dimension ref="A1:X105"/>
+  <dimension ref="A1:X178"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.54296875" customWidth="1"/>
-    <col min="8" max="8" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.6328125" customWidth="1"/>
-    <col min="12" max="12" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.6328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.1796875" customWidth="1"/>
+    <col min="6" max="7" width="14.54296875" customWidth="1"/>
+    <col min="8" max="8" width="13.6328125" customWidth="1"/>
+    <col min="9" max="9" width="12.1796875" customWidth="1"/>
+    <col min="10" max="11" width="9.6328125" customWidth="1"/>
+    <col min="12" max="12" width="8.7265625" customWidth="1"/>
+    <col min="13" max="13" width="6.7265625" customWidth="1"/>
+    <col min="14" max="14" width="5.6328125" customWidth="1"/>
+    <col min="15" max="15" width="6.7265625" customWidth="1"/>
+    <col min="16" max="16" width="6.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.35">
@@ -6745,6 +6860,4145 @@
         <v>6.4263529999999998</v>
       </c>
       <c r="X105" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="106" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>106</v>
+      </c>
+      <c r="B106" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D106" t="s">
+        <v>111</v>
+      </c>
+      <c r="E106" t="s">
+        <v>31</v>
+      </c>
+      <c r="F106" t="s">
+        <v>31</v>
+      </c>
+      <c r="G106">
+        <v>28</v>
+      </c>
+      <c r="H106">
+        <v>100</v>
+      </c>
+      <c r="I106" t="s">
+        <v>31</v>
+      </c>
+      <c r="J106" t="s">
+        <v>31</v>
+      </c>
+      <c r="K106">
+        <v>33</v>
+      </c>
+      <c r="L106">
+        <v>84</v>
+      </c>
+      <c r="M106">
+        <v>20.657496999999999</v>
+      </c>
+      <c r="N106">
+        <v>0.712727</v>
+      </c>
+      <c r="O106">
+        <v>0.472221</v>
+      </c>
+      <c r="P106">
+        <v>1.075725</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>22</v>
+      </c>
+      <c r="R106" t="s">
+        <v>24</v>
+      </c>
+      <c r="S106" t="s">
+        <v>24</v>
+      </c>
+      <c r="T106" t="s">
+        <v>22</v>
+      </c>
+      <c r="U106" t="s">
+        <v>22</v>
+      </c>
+      <c r="V106" t="s">
+        <v>22</v>
+      </c>
+      <c r="W106" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="107" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>106</v>
+      </c>
+      <c r="B107" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D107" t="s">
+        <v>112</v>
+      </c>
+      <c r="E107" t="s">
+        <v>31</v>
+      </c>
+      <c r="F107" t="s">
+        <v>31</v>
+      </c>
+      <c r="G107">
+        <v>12</v>
+      </c>
+      <c r="H107">
+        <v>176</v>
+      </c>
+      <c r="I107" t="s">
+        <v>31</v>
+      </c>
+      <c r="J107" t="s">
+        <v>31</v>
+      </c>
+      <c r="K107">
+        <v>12</v>
+      </c>
+      <c r="L107">
+        <v>168</v>
+      </c>
+      <c r="M107">
+        <v>6.12784</v>
+      </c>
+      <c r="N107">
+        <v>0.95454499999999998</v>
+      </c>
+      <c r="O107">
+        <v>0.44120799999999999</v>
+      </c>
+      <c r="P107">
+        <v>2.065143</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>22</v>
+      </c>
+      <c r="R107" t="s">
+        <v>22</v>
+      </c>
+      <c r="S107" t="s">
+        <v>24</v>
+      </c>
+      <c r="T107" t="s">
+        <v>22</v>
+      </c>
+      <c r="U107" t="s">
+        <v>22</v>
+      </c>
+      <c r="V107" t="s">
+        <v>22</v>
+      </c>
+      <c r="W107" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="108" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>106</v>
+      </c>
+      <c r="B108" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D108" t="s">
+        <v>113</v>
+      </c>
+      <c r="E108" t="s">
+        <v>31</v>
+      </c>
+      <c r="F108" t="s">
+        <v>31</v>
+      </c>
+      <c r="G108">
+        <v>100</v>
+      </c>
+      <c r="H108">
+        <v>210</v>
+      </c>
+      <c r="I108" t="s">
+        <v>31</v>
+      </c>
+      <c r="J108" t="s">
+        <v>31</v>
+      </c>
+      <c r="K108">
+        <v>99</v>
+      </c>
+      <c r="L108">
+        <v>208</v>
+      </c>
+      <c r="M108">
+        <v>73.214663000000002</v>
+      </c>
+      <c r="N108">
+        <v>1.000481</v>
+      </c>
+      <c r="O108">
+        <v>0.81819399999999998</v>
+      </c>
+      <c r="P108">
+        <v>1.2233799999999999</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>22</v>
+      </c>
+      <c r="R108" t="s">
+        <v>24</v>
+      </c>
+      <c r="S108" t="s">
+        <v>24</v>
+      </c>
+      <c r="T108" t="s">
+        <v>22</v>
+      </c>
+      <c r="U108" t="s">
+        <v>22</v>
+      </c>
+      <c r="V108" t="s">
+        <v>22</v>
+      </c>
+      <c r="W108" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="109" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>106</v>
+      </c>
+      <c r="B109" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D109" t="s">
+        <v>111</v>
+      </c>
+      <c r="E109" t="s">
+        <v>31</v>
+      </c>
+      <c r="F109" t="s">
+        <v>31</v>
+      </c>
+      <c r="G109">
+        <v>74</v>
+      </c>
+      <c r="H109">
+        <v>100</v>
+      </c>
+      <c r="I109" t="s">
+        <v>31</v>
+      </c>
+      <c r="J109" t="s">
+        <v>31</v>
+      </c>
+      <c r="K109">
+        <v>68</v>
+      </c>
+      <c r="L109">
+        <v>84</v>
+      </c>
+      <c r="M109">
+        <v>30.195846</v>
+      </c>
+      <c r="N109">
+        <v>0.91411799999999999</v>
+      </c>
+      <c r="O109">
+        <v>0.78227899999999995</v>
+      </c>
+      <c r="P109">
+        <v>1.0681750000000001</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>22</v>
+      </c>
+      <c r="R109" t="s">
+        <v>24</v>
+      </c>
+      <c r="S109" t="s">
+        <v>24</v>
+      </c>
+      <c r="T109" t="s">
+        <v>22</v>
+      </c>
+      <c r="U109" t="s">
+        <v>22</v>
+      </c>
+      <c r="V109" t="s">
+        <v>22</v>
+      </c>
+      <c r="W109" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="110" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>106</v>
+      </c>
+      <c r="B110" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D110" t="s">
+        <v>114</v>
+      </c>
+      <c r="E110" t="s">
+        <v>31</v>
+      </c>
+      <c r="F110" t="s">
+        <v>31</v>
+      </c>
+      <c r="G110">
+        <v>87</v>
+      </c>
+      <c r="H110">
+        <v>152</v>
+      </c>
+      <c r="I110" t="s">
+        <v>31</v>
+      </c>
+      <c r="J110" t="s">
+        <v>31</v>
+      </c>
+      <c r="K110">
+        <v>99</v>
+      </c>
+      <c r="L110">
+        <v>159</v>
+      </c>
+      <c r="M110">
+        <v>21.848922999999999</v>
+      </c>
+      <c r="N110">
+        <v>0.91925800000000002</v>
+      </c>
+      <c r="O110">
+        <v>0.765455</v>
+      </c>
+      <c r="P110">
+        <v>1.103966</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>22</v>
+      </c>
+      <c r="R110" t="s">
+        <v>24</v>
+      </c>
+      <c r="S110" t="s">
+        <v>22</v>
+      </c>
+      <c r="T110" t="s">
+        <v>22</v>
+      </c>
+      <c r="U110" t="s">
+        <v>22</v>
+      </c>
+      <c r="V110" t="s">
+        <v>22</v>
+      </c>
+      <c r="W110" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="111" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>106</v>
+      </c>
+      <c r="B111" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D111" t="s">
+        <v>112</v>
+      </c>
+      <c r="E111" t="s">
+        <v>31</v>
+      </c>
+      <c r="F111" t="s">
+        <v>31</v>
+      </c>
+      <c r="G111">
+        <v>47</v>
+      </c>
+      <c r="H111">
+        <v>176</v>
+      </c>
+      <c r="I111" t="s">
+        <v>31</v>
+      </c>
+      <c r="J111" t="s">
+        <v>31</v>
+      </c>
+      <c r="K111">
+        <v>48</v>
+      </c>
+      <c r="L111">
+        <v>168</v>
+      </c>
+      <c r="M111">
+        <v>6.2566410000000001</v>
+      </c>
+      <c r="N111">
+        <v>0.93465900000000002</v>
+      </c>
+      <c r="O111">
+        <v>0.663829</v>
+      </c>
+      <c r="P111">
+        <v>1.315982</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>22</v>
+      </c>
+      <c r="R111" t="s">
+        <v>22</v>
+      </c>
+      <c r="S111" t="s">
+        <v>24</v>
+      </c>
+      <c r="T111" t="s">
+        <v>22</v>
+      </c>
+      <c r="U111" t="s">
+        <v>22</v>
+      </c>
+      <c r="V111" t="s">
+        <v>22</v>
+      </c>
+      <c r="W111" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="112" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>106</v>
+      </c>
+      <c r="B112" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D112" t="s">
+        <v>115</v>
+      </c>
+      <c r="E112" t="s">
+        <v>31</v>
+      </c>
+      <c r="F112" t="s">
+        <v>31</v>
+      </c>
+      <c r="G112">
+        <v>9</v>
+      </c>
+      <c r="H112">
+        <v>12</v>
+      </c>
+      <c r="I112" t="s">
+        <v>31</v>
+      </c>
+      <c r="J112" t="s">
+        <v>31</v>
+      </c>
+      <c r="K112">
+        <v>6</v>
+      </c>
+      <c r="L112">
+        <v>12</v>
+      </c>
+      <c r="M112">
+        <v>1.716081</v>
+      </c>
+      <c r="N112">
+        <v>1.5</v>
+      </c>
+      <c r="O112">
+        <v>0.78047200000000005</v>
+      </c>
+      <c r="P112">
+        <v>2.88287</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>22</v>
+      </c>
+      <c r="R112" t="s">
+        <v>24</v>
+      </c>
+      <c r="S112" t="s">
+        <v>24</v>
+      </c>
+      <c r="T112" t="s">
+        <v>22</v>
+      </c>
+      <c r="U112" t="s">
+        <v>22</v>
+      </c>
+      <c r="V112" t="s">
+        <v>23</v>
+      </c>
+      <c r="W112" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="113" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>106</v>
+      </c>
+      <c r="B113" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D113" t="s">
+        <v>113</v>
+      </c>
+      <c r="E113" t="s">
+        <v>31</v>
+      </c>
+      <c r="F113" t="s">
+        <v>31</v>
+      </c>
+      <c r="G113">
+        <v>138</v>
+      </c>
+      <c r="H113">
+        <v>210</v>
+      </c>
+      <c r="I113" t="s">
+        <v>31</v>
+      </c>
+      <c r="J113" t="s">
+        <v>31</v>
+      </c>
+      <c r="K113">
+        <v>141</v>
+      </c>
+      <c r="L113">
+        <v>208</v>
+      </c>
+      <c r="M113">
+        <v>39.982508000000003</v>
+      </c>
+      <c r="N113">
+        <v>0.96940199999999999</v>
+      </c>
+      <c r="O113">
+        <v>0.84668500000000002</v>
+      </c>
+      <c r="P113">
+        <v>1.1099060000000001</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>22</v>
+      </c>
+      <c r="R113" t="s">
+        <v>24</v>
+      </c>
+      <c r="S113" t="s">
+        <v>24</v>
+      </c>
+      <c r="T113" t="s">
+        <v>22</v>
+      </c>
+      <c r="U113" t="s">
+        <v>22</v>
+      </c>
+      <c r="V113" t="s">
+        <v>22</v>
+      </c>
+      <c r="W113" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="114" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>106</v>
+      </c>
+      <c r="B114" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D114" t="s">
+        <v>111</v>
+      </c>
+      <c r="E114" t="s">
+        <v>31</v>
+      </c>
+      <c r="F114" t="s">
+        <v>31</v>
+      </c>
+      <c r="G114">
+        <v>7</v>
+      </c>
+      <c r="H114">
+        <v>100</v>
+      </c>
+      <c r="I114" t="s">
+        <v>31</v>
+      </c>
+      <c r="J114" t="s">
+        <v>31</v>
+      </c>
+      <c r="K114">
+        <v>0</v>
+      </c>
+      <c r="L114">
+        <v>84</v>
+      </c>
+      <c r="M114">
+        <v>2.5079790000000002</v>
+      </c>
+      <c r="N114">
+        <v>12.623761999999999</v>
+      </c>
+      <c r="O114">
+        <v>0.73157499999999998</v>
+      </c>
+      <c r="P114">
+        <v>217.83064899999999</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>22</v>
+      </c>
+      <c r="R114" t="s">
+        <v>24</v>
+      </c>
+      <c r="S114" t="s">
+        <v>24</v>
+      </c>
+      <c r="T114" t="s">
+        <v>22</v>
+      </c>
+      <c r="U114" t="s">
+        <v>22</v>
+      </c>
+      <c r="V114" t="s">
+        <v>22</v>
+      </c>
+      <c r="W114" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="115" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>106</v>
+      </c>
+      <c r="B115" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D115" t="s">
+        <v>114</v>
+      </c>
+      <c r="E115" t="s">
+        <v>31</v>
+      </c>
+      <c r="F115" t="s">
+        <v>31</v>
+      </c>
+      <c r="G115">
+        <v>1</v>
+      </c>
+      <c r="H115">
+        <v>152</v>
+      </c>
+      <c r="I115" t="s">
+        <v>31</v>
+      </c>
+      <c r="J115" t="s">
+        <v>31</v>
+      </c>
+      <c r="K115">
+        <v>2</v>
+      </c>
+      <c r="L115">
+        <v>159</v>
+      </c>
+      <c r="M115">
+        <v>3.5399250000000002</v>
+      </c>
+      <c r="N115">
+        <v>0.52302599999999999</v>
+      </c>
+      <c r="O115">
+        <v>4.7918000000000002E-2</v>
+      </c>
+      <c r="P115">
+        <v>5.7088270000000003</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>22</v>
+      </c>
+      <c r="R115" t="s">
+        <v>24</v>
+      </c>
+      <c r="S115" t="s">
+        <v>22</v>
+      </c>
+      <c r="T115" t="s">
+        <v>22</v>
+      </c>
+      <c r="U115" t="s">
+        <v>22</v>
+      </c>
+      <c r="V115" t="s">
+        <v>22</v>
+      </c>
+      <c r="W115" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="116" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>106</v>
+      </c>
+      <c r="B116" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D116" t="s">
+        <v>112</v>
+      </c>
+      <c r="E116" t="s">
+        <v>31</v>
+      </c>
+      <c r="F116" t="s">
+        <v>31</v>
+      </c>
+      <c r="G116">
+        <v>12</v>
+      </c>
+      <c r="H116">
+        <v>176</v>
+      </c>
+      <c r="I116" t="s">
+        <v>31</v>
+      </c>
+      <c r="J116" t="s">
+        <v>31</v>
+      </c>
+      <c r="K116">
+        <v>3</v>
+      </c>
+      <c r="L116">
+        <v>168</v>
+      </c>
+      <c r="M116">
+        <v>12.330959</v>
+      </c>
+      <c r="N116">
+        <v>3.8181820000000002</v>
+      </c>
+      <c r="O116">
+        <v>1.0968150000000001</v>
+      </c>
+      <c r="P116">
+        <v>13.291672999999999</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>22</v>
+      </c>
+      <c r="R116" t="s">
+        <v>22</v>
+      </c>
+      <c r="S116" t="s">
+        <v>24</v>
+      </c>
+      <c r="T116" t="s">
+        <v>22</v>
+      </c>
+      <c r="U116" t="s">
+        <v>22</v>
+      </c>
+      <c r="V116" t="s">
+        <v>22</v>
+      </c>
+      <c r="W116" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="117" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>106</v>
+      </c>
+      <c r="B117" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D117" t="s">
+        <v>115</v>
+      </c>
+      <c r="E117" t="s">
+        <v>31</v>
+      </c>
+      <c r="F117" t="s">
+        <v>31</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>12</v>
+      </c>
+      <c r="I117" t="s">
+        <v>31</v>
+      </c>
+      <c r="J117" t="s">
+        <v>31</v>
+      </c>
+      <c r="K117">
+        <v>0</v>
+      </c>
+      <c r="L117">
+        <v>12</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>22</v>
+      </c>
+      <c r="R117" t="s">
+        <v>24</v>
+      </c>
+      <c r="S117" t="s">
+        <v>24</v>
+      </c>
+      <c r="T117" t="s">
+        <v>22</v>
+      </c>
+      <c r="U117" t="s">
+        <v>22</v>
+      </c>
+      <c r="V117" t="s">
+        <v>23</v>
+      </c>
+      <c r="W117" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="118" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>106</v>
+      </c>
+      <c r="B118" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D118" t="s">
+        <v>113</v>
+      </c>
+      <c r="E118" t="s">
+        <v>31</v>
+      </c>
+      <c r="F118" t="s">
+        <v>31</v>
+      </c>
+      <c r="G118">
+        <v>88</v>
+      </c>
+      <c r="H118">
+        <v>210</v>
+      </c>
+      <c r="I118" t="s">
+        <v>31</v>
+      </c>
+      <c r="J118" t="s">
+        <v>31</v>
+      </c>
+      <c r="K118">
+        <v>30</v>
+      </c>
+      <c r="L118">
+        <v>208</v>
+      </c>
+      <c r="M118">
+        <v>81.621136000000007</v>
+      </c>
+      <c r="N118">
+        <v>2.9053969999999998</v>
+      </c>
+      <c r="O118">
+        <v>2.0121980000000002</v>
+      </c>
+      <c r="P118">
+        <v>4.1950789999999998</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>22</v>
+      </c>
+      <c r="R118" t="s">
+        <v>24</v>
+      </c>
+      <c r="S118" t="s">
+        <v>24</v>
+      </c>
+      <c r="T118" t="s">
+        <v>22</v>
+      </c>
+      <c r="U118" t="s">
+        <v>22</v>
+      </c>
+      <c r="V118" t="s">
+        <v>22</v>
+      </c>
+      <c r="W118" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="119" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>106</v>
+      </c>
+      <c r="B119" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D119" t="s">
+        <v>111</v>
+      </c>
+      <c r="E119" t="s">
+        <v>31</v>
+      </c>
+      <c r="F119" t="s">
+        <v>31</v>
+      </c>
+      <c r="G119">
+        <v>29</v>
+      </c>
+      <c r="H119">
+        <v>100</v>
+      </c>
+      <c r="I119" t="s">
+        <v>31</v>
+      </c>
+      <c r="J119" t="s">
+        <v>31</v>
+      </c>
+      <c r="K119">
+        <v>3</v>
+      </c>
+      <c r="L119">
+        <v>84</v>
+      </c>
+      <c r="M119">
+        <v>17.379131999999998</v>
+      </c>
+      <c r="N119">
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="O119">
+        <v>2.5640610000000001</v>
+      </c>
+      <c r="P119">
+        <v>25.714829000000002</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>22</v>
+      </c>
+      <c r="R119" t="s">
+        <v>24</v>
+      </c>
+      <c r="S119" t="s">
+        <v>24</v>
+      </c>
+      <c r="T119" t="s">
+        <v>22</v>
+      </c>
+      <c r="U119" t="s">
+        <v>22</v>
+      </c>
+      <c r="V119" t="s">
+        <v>22</v>
+      </c>
+      <c r="W119" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="120" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>106</v>
+      </c>
+      <c r="B120" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D120" t="s">
+        <v>114</v>
+      </c>
+      <c r="E120" t="s">
+        <v>31</v>
+      </c>
+      <c r="F120" t="s">
+        <v>31</v>
+      </c>
+      <c r="G120">
+        <v>7</v>
+      </c>
+      <c r="H120">
+        <v>152</v>
+      </c>
+      <c r="I120" t="s">
+        <v>31</v>
+      </c>
+      <c r="J120" t="s">
+        <v>31</v>
+      </c>
+      <c r="K120">
+        <v>3</v>
+      </c>
+      <c r="L120">
+        <v>159</v>
+      </c>
+      <c r="M120">
+        <v>13.55283</v>
+      </c>
+      <c r="N120">
+        <v>2.4407890000000001</v>
+      </c>
+      <c r="O120">
+        <v>0.64288999999999996</v>
+      </c>
+      <c r="P120">
+        <v>9.2666830000000004</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>22</v>
+      </c>
+      <c r="R120" t="s">
+        <v>24</v>
+      </c>
+      <c r="S120" t="s">
+        <v>22</v>
+      </c>
+      <c r="T120" t="s">
+        <v>22</v>
+      </c>
+      <c r="U120" t="s">
+        <v>22</v>
+      </c>
+      <c r="V120" t="s">
+        <v>22</v>
+      </c>
+      <c r="W120" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="121" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>106</v>
+      </c>
+      <c r="B121" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D121" t="s">
+        <v>112</v>
+      </c>
+      <c r="E121" t="s">
+        <v>31</v>
+      </c>
+      <c r="F121" t="s">
+        <v>31</v>
+      </c>
+      <c r="G121">
+        <v>73</v>
+      </c>
+      <c r="H121">
+        <v>176</v>
+      </c>
+      <c r="I121" t="s">
+        <v>31</v>
+      </c>
+      <c r="J121" t="s">
+        <v>31</v>
+      </c>
+      <c r="K121">
+        <v>27</v>
+      </c>
+      <c r="L121">
+        <v>168</v>
+      </c>
+      <c r="M121">
+        <v>66.269703000000007</v>
+      </c>
+      <c r="N121">
+        <v>2.5808080000000002</v>
+      </c>
+      <c r="O121">
+        <v>1.751614</v>
+      </c>
+      <c r="P121">
+        <v>3.8025340000000001</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>22</v>
+      </c>
+      <c r="R121" t="s">
+        <v>22</v>
+      </c>
+      <c r="S121" t="s">
+        <v>24</v>
+      </c>
+      <c r="T121" t="s">
+        <v>22</v>
+      </c>
+      <c r="U121" t="s">
+        <v>22</v>
+      </c>
+      <c r="V121" t="s">
+        <v>22</v>
+      </c>
+      <c r="W121" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="122" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>106</v>
+      </c>
+      <c r="B122" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D122" t="s">
+        <v>115</v>
+      </c>
+      <c r="E122" t="s">
+        <v>31</v>
+      </c>
+      <c r="F122" t="s">
+        <v>31</v>
+      </c>
+      <c r="G122">
+        <v>1</v>
+      </c>
+      <c r="H122">
+        <v>12</v>
+      </c>
+      <c r="I122" t="s">
+        <v>31</v>
+      </c>
+      <c r="J122" t="s">
+        <v>31</v>
+      </c>
+      <c r="K122">
+        <v>0</v>
+      </c>
+      <c r="L122">
+        <v>12</v>
+      </c>
+      <c r="M122">
+        <v>2.7983349999999998</v>
+      </c>
+      <c r="N122">
+        <v>3</v>
+      </c>
+      <c r="O122">
+        <v>0.134217</v>
+      </c>
+      <c r="P122">
+        <v>67.055683999999999</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>22</v>
+      </c>
+      <c r="R122" t="s">
+        <v>24</v>
+      </c>
+      <c r="S122" t="s">
+        <v>24</v>
+      </c>
+      <c r="T122" t="s">
+        <v>22</v>
+      </c>
+      <c r="U122" t="s">
+        <v>22</v>
+      </c>
+      <c r="V122" t="s">
+        <v>23</v>
+      </c>
+      <c r="W122" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="123" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>116</v>
+      </c>
+      <c r="B123" s="1">
+        <v>44621</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D123" t="s">
+        <v>119</v>
+      </c>
+      <c r="E123" t="s">
+        <v>31</v>
+      </c>
+      <c r="F123" t="s">
+        <v>31</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>197</v>
+      </c>
+      <c r="I123" t="s">
+        <v>31</v>
+      </c>
+      <c r="J123" t="s">
+        <v>31</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+      <c r="L123">
+        <v>203</v>
+      </c>
+      <c r="X123" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="124" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>116</v>
+      </c>
+      <c r="B124" s="1">
+        <v>44621</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D124" t="s">
+        <v>120</v>
+      </c>
+      <c r="E124" t="s">
+        <v>31</v>
+      </c>
+      <c r="F124" t="s">
+        <v>31</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>73</v>
+      </c>
+      <c r="I124" t="s">
+        <v>31</v>
+      </c>
+      <c r="J124" t="s">
+        <v>31</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="L124">
+        <v>73</v>
+      </c>
+      <c r="X124" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="125" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>116</v>
+      </c>
+      <c r="B125" s="1">
+        <v>44621</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D125" t="s">
+        <v>121</v>
+      </c>
+      <c r="E125" t="s">
+        <v>31</v>
+      </c>
+      <c r="F125" t="s">
+        <v>31</v>
+      </c>
+      <c r="G125">
+        <v>6</v>
+      </c>
+      <c r="H125">
+        <v>787</v>
+      </c>
+      <c r="I125" t="s">
+        <v>31</v>
+      </c>
+      <c r="J125" t="s">
+        <v>31</v>
+      </c>
+      <c r="K125">
+        <v>10</v>
+      </c>
+      <c r="L125">
+        <v>799</v>
+      </c>
+      <c r="M125">
+        <v>100</v>
+      </c>
+      <c r="N125">
+        <v>0.60914900000000005</v>
+      </c>
+      <c r="O125">
+        <v>0.22245799999999999</v>
+      </c>
+      <c r="P125">
+        <v>1.6680079999999999</v>
+      </c>
+      <c r="X125" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="126" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>116</v>
+      </c>
+      <c r="B126" s="1">
+        <v>44621</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D126" t="s">
+        <v>119</v>
+      </c>
+      <c r="E126" t="s">
+        <v>31</v>
+      </c>
+      <c r="F126" t="s">
+        <v>31</v>
+      </c>
+      <c r="G126">
+        <v>3</v>
+      </c>
+      <c r="H126">
+        <v>197</v>
+      </c>
+      <c r="I126" t="s">
+        <v>31</v>
+      </c>
+      <c r="J126" t="s">
+        <v>31</v>
+      </c>
+      <c r="K126">
+        <v>7</v>
+      </c>
+      <c r="L126">
+        <v>203</v>
+      </c>
+      <c r="M126">
+        <v>6.0650500000000003</v>
+      </c>
+      <c r="N126">
+        <v>0.44162400000000002</v>
+      </c>
+      <c r="O126">
+        <v>0.115843</v>
+      </c>
+      <c r="P126">
+        <v>1.6835899999999999</v>
+      </c>
+      <c r="X126" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="127" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>116</v>
+      </c>
+      <c r="B127" s="1">
+        <v>44621</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D127" t="s">
+        <v>121</v>
+      </c>
+      <c r="E127" t="s">
+        <v>31</v>
+      </c>
+      <c r="F127" t="s">
+        <v>31</v>
+      </c>
+      <c r="G127">
+        <v>52</v>
+      </c>
+      <c r="H127">
+        <v>787</v>
+      </c>
+      <c r="I127" t="s">
+        <v>31</v>
+      </c>
+      <c r="J127" t="s">
+        <v>31</v>
+      </c>
+      <c r="K127">
+        <v>75</v>
+      </c>
+      <c r="L127">
+        <v>838</v>
+      </c>
+      <c r="M127">
+        <v>93.934950000000001</v>
+      </c>
+      <c r="N127">
+        <v>0.738263</v>
+      </c>
+      <c r="O127">
+        <v>0.52545200000000003</v>
+      </c>
+      <c r="P127">
+        <v>1.0372650000000001</v>
+      </c>
+      <c r="X127" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="128" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>116</v>
+      </c>
+      <c r="B128" s="1">
+        <v>44621</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D128" t="s">
+        <v>119</v>
+      </c>
+      <c r="E128" t="s">
+        <v>31</v>
+      </c>
+      <c r="F128" t="s">
+        <v>31</v>
+      </c>
+      <c r="G128">
+        <v>81</v>
+      </c>
+      <c r="H128">
+        <v>197</v>
+      </c>
+      <c r="I128" t="s">
+        <v>31</v>
+      </c>
+      <c r="J128" t="s">
+        <v>31</v>
+      </c>
+      <c r="K128">
+        <v>76</v>
+      </c>
+      <c r="L128">
+        <v>203</v>
+      </c>
+      <c r="M128">
+        <v>12.460062000000001</v>
+      </c>
+      <c r="N128">
+        <v>1.0982499999999999</v>
+      </c>
+      <c r="O128">
+        <v>0.86044500000000002</v>
+      </c>
+      <c r="P128">
+        <v>1.4017790000000001</v>
+      </c>
+      <c r="X128" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="129" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>116</v>
+      </c>
+      <c r="B129" s="1">
+        <v>44621</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D129" t="s">
+        <v>121</v>
+      </c>
+      <c r="E129" t="s">
+        <v>31</v>
+      </c>
+      <c r="F129" t="s">
+        <v>31</v>
+      </c>
+      <c r="G129">
+        <v>462</v>
+      </c>
+      <c r="H129">
+        <v>787</v>
+      </c>
+      <c r="I129" t="s">
+        <v>31</v>
+      </c>
+      <c r="J129" t="s">
+        <v>31</v>
+      </c>
+      <c r="K129">
+        <v>390</v>
+      </c>
+      <c r="L129">
+        <v>799</v>
+      </c>
+      <c r="M129">
+        <v>87.539938000000006</v>
+      </c>
+      <c r="N129">
+        <v>1.2026779999999999</v>
+      </c>
+      <c r="O129">
+        <v>1.0968990000000001</v>
+      </c>
+      <c r="P129">
+        <v>1.3186580000000001</v>
+      </c>
+      <c r="X129" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="130" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>122</v>
+      </c>
+      <c r="B130" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D130" t="s">
+        <v>126</v>
+      </c>
+      <c r="E130" t="s">
+        <v>31</v>
+      </c>
+      <c r="F130" t="s">
+        <v>31</v>
+      </c>
+      <c r="G130">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>20</v>
+      </c>
+      <c r="I130" t="s">
+        <v>31</v>
+      </c>
+      <c r="J130" t="s">
+        <v>31</v>
+      </c>
+      <c r="K130">
+        <v>3</v>
+      </c>
+      <c r="L130">
+        <v>21</v>
+      </c>
+      <c r="M130">
+        <v>0.65271900000000005</v>
+      </c>
+      <c r="N130">
+        <v>0.14965999999999999</v>
+      </c>
+      <c r="O130">
+        <v>8.2159999999999993E-3</v>
+      </c>
+      <c r="P130">
+        <v>2.7260119999999999</v>
+      </c>
+      <c r="X130" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="131" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>122</v>
+      </c>
+      <c r="B131" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D131" t="s">
+        <v>127</v>
+      </c>
+      <c r="E131" t="s">
+        <v>31</v>
+      </c>
+      <c r="F131" t="s">
+        <v>31</v>
+      </c>
+      <c r="G131">
+        <v>20</v>
+      </c>
+      <c r="H131">
+        <v>51</v>
+      </c>
+      <c r="I131" t="s">
+        <v>31</v>
+      </c>
+      <c r="J131" t="s">
+        <v>31</v>
+      </c>
+      <c r="K131">
+        <v>29</v>
+      </c>
+      <c r="L131">
+        <v>50</v>
+      </c>
+      <c r="M131">
+        <v>18.213861000000001</v>
+      </c>
+      <c r="N131">
+        <v>0.67613299999999998</v>
+      </c>
+      <c r="O131">
+        <v>0.44639099999999998</v>
+      </c>
+      <c r="P131">
+        <v>1.0241130000000001</v>
+      </c>
+      <c r="X131" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="132" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>122</v>
+      </c>
+      <c r="B132" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D132" t="s">
+        <v>128</v>
+      </c>
+      <c r="E132" t="s">
+        <v>31</v>
+      </c>
+      <c r="F132" t="s">
+        <v>31</v>
+      </c>
+      <c r="G132">
+        <v>4</v>
+      </c>
+      <c r="H132">
+        <v>144</v>
+      </c>
+      <c r="I132" t="s">
+        <v>31</v>
+      </c>
+      <c r="J132" t="s">
+        <v>31</v>
+      </c>
+      <c r="K132">
+        <v>8</v>
+      </c>
+      <c r="L132">
+        <v>145</v>
+      </c>
+      <c r="M132">
+        <v>3.670655</v>
+      </c>
+      <c r="N132">
+        <v>0.50347200000000003</v>
+      </c>
+      <c r="O132">
+        <v>0.15503600000000001</v>
+      </c>
+      <c r="P132">
+        <v>1.6350009999999999</v>
+      </c>
+      <c r="X132" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="133" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>122</v>
+      </c>
+      <c r="B133" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D133" t="s">
+        <v>129</v>
+      </c>
+      <c r="E133" t="s">
+        <v>31</v>
+      </c>
+      <c r="F133" t="s">
+        <v>31</v>
+      </c>
+      <c r="G133">
+        <v>513</v>
+      </c>
+      <c r="H133">
+        <v>4148</v>
+      </c>
+      <c r="I133" t="s">
+        <v>31</v>
+      </c>
+      <c r="J133" t="s">
+        <v>31</v>
+      </c>
+      <c r="K133">
+        <v>546</v>
+      </c>
+      <c r="L133">
+        <v>4008</v>
+      </c>
+      <c r="M133">
+        <v>38.018566</v>
+      </c>
+      <c r="N133">
+        <v>0.90784900000000002</v>
+      </c>
+      <c r="O133">
+        <v>0.81131299999999995</v>
+      </c>
+      <c r="P133">
+        <v>1.0158720000000001</v>
+      </c>
+      <c r="X133" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="134" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>122</v>
+      </c>
+      <c r="B134" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D134" t="s">
+        <v>130</v>
+      </c>
+      <c r="E134" t="s">
+        <v>31</v>
+      </c>
+      <c r="F134" t="s">
+        <v>31</v>
+      </c>
+      <c r="G134">
+        <v>24</v>
+      </c>
+      <c r="H134">
+        <v>515</v>
+      </c>
+      <c r="I134" t="s">
+        <v>31</v>
+      </c>
+      <c r="J134" t="s">
+        <v>31</v>
+      </c>
+      <c r="K134">
+        <v>37</v>
+      </c>
+      <c r="L134">
+        <v>518</v>
+      </c>
+      <c r="M134">
+        <v>14.572654999999999</v>
+      </c>
+      <c r="N134">
+        <v>0.65242699999999998</v>
+      </c>
+      <c r="O134">
+        <v>0.39611000000000002</v>
+      </c>
+      <c r="P134">
+        <v>1.0746039999999999</v>
+      </c>
+      <c r="X134" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="135" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>122</v>
+      </c>
+      <c r="B135" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D135" t="s">
+        <v>131</v>
+      </c>
+      <c r="E135" t="s">
+        <v>31</v>
+      </c>
+      <c r="F135" t="s">
+        <v>31</v>
+      </c>
+      <c r="G135">
+        <v>62</v>
+      </c>
+      <c r="H135">
+        <v>764</v>
+      </c>
+      <c r="I135" t="s">
+        <v>31</v>
+      </c>
+      <c r="J135" t="s">
+        <v>31</v>
+      </c>
+      <c r="K135">
+        <v>100</v>
+      </c>
+      <c r="L135">
+        <v>761</v>
+      </c>
+      <c r="M135">
+        <v>24.871544</v>
+      </c>
+      <c r="N135">
+        <v>0.61756500000000003</v>
+      </c>
+      <c r="O135">
+        <v>0.45727699999999999</v>
+      </c>
+      <c r="P135">
+        <v>0.83403899999999997</v>
+      </c>
+      <c r="X135" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="136" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>122</v>
+      </c>
+      <c r="B136" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D136" t="s">
+        <v>127</v>
+      </c>
+      <c r="E136" t="s">
+        <v>31</v>
+      </c>
+      <c r="F136" t="s">
+        <v>31</v>
+      </c>
+      <c r="G136">
+        <v>23</v>
+      </c>
+      <c r="H136">
+        <v>51</v>
+      </c>
+      <c r="I136" t="s">
+        <v>31</v>
+      </c>
+      <c r="J136" t="s">
+        <v>31</v>
+      </c>
+      <c r="K136">
+        <v>31</v>
+      </c>
+      <c r="L136">
+        <v>50</v>
+      </c>
+      <c r="M136">
+        <v>34.053386000000003</v>
+      </c>
+      <c r="N136">
+        <v>0.72738800000000003</v>
+      </c>
+      <c r="O136">
+        <v>0.50115699999999996</v>
+      </c>
+      <c r="P136">
+        <v>1.0557430000000001</v>
+      </c>
+      <c r="X136" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="137" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>122</v>
+      </c>
+      <c r="B137" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D137" t="s">
+        <v>131</v>
+      </c>
+      <c r="E137" t="s">
+        <v>31</v>
+      </c>
+      <c r="F137" t="s">
+        <v>31</v>
+      </c>
+      <c r="G137">
+        <v>79</v>
+      </c>
+      <c r="H137">
+        <v>764</v>
+      </c>
+      <c r="I137" t="s">
+        <v>31</v>
+      </c>
+      <c r="J137" t="s">
+        <v>31</v>
+      </c>
+      <c r="K137">
+        <v>116</v>
+      </c>
+      <c r="L137">
+        <v>761</v>
+      </c>
+      <c r="M137">
+        <v>65.946613999999997</v>
+      </c>
+      <c r="N137">
+        <v>0.67835999999999996</v>
+      </c>
+      <c r="O137">
+        <v>0.51903600000000005</v>
+      </c>
+      <c r="P137">
+        <v>0.88659100000000002</v>
+      </c>
+      <c r="X137" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="138" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>122</v>
+      </c>
+      <c r="B138" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D138" t="s">
+        <v>127</v>
+      </c>
+      <c r="E138" t="s">
+        <v>31</v>
+      </c>
+      <c r="F138" t="s">
+        <v>31</v>
+      </c>
+      <c r="G138">
+        <v>44</v>
+      </c>
+      <c r="H138">
+        <v>50</v>
+      </c>
+      <c r="I138" t="s">
+        <v>31</v>
+      </c>
+      <c r="J138" t="s">
+        <v>31</v>
+      </c>
+      <c r="K138">
+        <v>47</v>
+      </c>
+      <c r="L138">
+        <v>49</v>
+      </c>
+      <c r="M138">
+        <v>45.973539000000002</v>
+      </c>
+      <c r="N138">
+        <v>0.91744700000000001</v>
+      </c>
+      <c r="O138">
+        <v>0.81571700000000003</v>
+      </c>
+      <c r="P138">
+        <v>1.0318639999999999</v>
+      </c>
+      <c r="X138" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="139" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>122</v>
+      </c>
+      <c r="B139" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D139" t="s">
+        <v>128</v>
+      </c>
+      <c r="E139" t="s">
+        <v>31</v>
+      </c>
+      <c r="F139" t="s">
+        <v>31</v>
+      </c>
+      <c r="G139">
+        <v>37</v>
+      </c>
+      <c r="H139">
+        <v>142</v>
+      </c>
+      <c r="I139" t="s">
+        <v>31</v>
+      </c>
+      <c r="J139" t="s">
+        <v>31</v>
+      </c>
+      <c r="K139">
+        <v>32</v>
+      </c>
+      <c r="L139">
+        <v>142</v>
+      </c>
+      <c r="M139">
+        <v>5.8476809999999997</v>
+      </c>
+      <c r="N139">
+        <v>1.15625</v>
+      </c>
+      <c r="O139">
+        <v>0.76579399999999997</v>
+      </c>
+      <c r="P139">
+        <v>1.7457879999999999</v>
+      </c>
+      <c r="X139" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="140" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>122</v>
+      </c>
+      <c r="B140" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D140" t="s">
+        <v>131</v>
+      </c>
+      <c r="E140" t="s">
+        <v>31</v>
+      </c>
+      <c r="F140" t="s">
+        <v>31</v>
+      </c>
+      <c r="G140">
+        <v>334</v>
+      </c>
+      <c r="H140">
+        <v>750</v>
+      </c>
+      <c r="I140" t="s">
+        <v>31</v>
+      </c>
+      <c r="J140" t="s">
+        <v>31</v>
+      </c>
+      <c r="K140">
+        <v>334</v>
+      </c>
+      <c r="L140">
+        <v>752</v>
+      </c>
+      <c r="M140">
+        <v>48.178780000000003</v>
+      </c>
+      <c r="N140">
+        <v>1.002667</v>
+      </c>
+      <c r="O140">
+        <v>0.89551899999999995</v>
+      </c>
+      <c r="P140">
+        <v>1.122635</v>
+      </c>
+      <c r="X140" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="141" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>122</v>
+      </c>
+      <c r="B141" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D141" t="s">
+        <v>127</v>
+      </c>
+      <c r="E141" t="s">
+        <v>31</v>
+      </c>
+      <c r="F141" t="s">
+        <v>31</v>
+      </c>
+      <c r="G141">
+        <v>25</v>
+      </c>
+      <c r="H141">
+        <v>50</v>
+      </c>
+      <c r="I141" t="s">
+        <v>31</v>
+      </c>
+      <c r="J141" t="s">
+        <v>31</v>
+      </c>
+      <c r="K141">
+        <v>35</v>
+      </c>
+      <c r="L141">
+        <v>49</v>
+      </c>
+      <c r="M141">
+        <v>20.328666999999999</v>
+      </c>
+      <c r="N141">
+        <v>0.7</v>
+      </c>
+      <c r="O141">
+        <v>0.50379099999999999</v>
+      </c>
+      <c r="P141">
+        <v>0.97262599999999999</v>
+      </c>
+      <c r="X141" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="142" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>122</v>
+      </c>
+      <c r="B142" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D142" t="s">
+        <v>128</v>
+      </c>
+      <c r="E142" t="s">
+        <v>31</v>
+      </c>
+      <c r="F142" t="s">
+        <v>31</v>
+      </c>
+      <c r="G142">
+        <v>20</v>
+      </c>
+      <c r="H142">
+        <v>142</v>
+      </c>
+      <c r="I142" t="s">
+        <v>31</v>
+      </c>
+      <c r="J142" t="s">
+        <v>31</v>
+      </c>
+      <c r="K142">
+        <v>17</v>
+      </c>
+      <c r="L142">
+        <v>142</v>
+      </c>
+      <c r="M142">
+        <v>6.043145</v>
+      </c>
+      <c r="N142">
+        <v>1.176471</v>
+      </c>
+      <c r="O142">
+        <v>0.64355200000000001</v>
+      </c>
+      <c r="P142">
+        <v>2.150693</v>
+      </c>
+      <c r="X142" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="143" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>122</v>
+      </c>
+      <c r="B143" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D143" t="s">
+        <v>130</v>
+      </c>
+      <c r="E143" t="s">
+        <v>31</v>
+      </c>
+      <c r="F143" t="s">
+        <v>31</v>
+      </c>
+      <c r="G143">
+        <v>81</v>
+      </c>
+      <c r="H143">
+        <v>507</v>
+      </c>
+      <c r="I143" t="s">
+        <v>31</v>
+      </c>
+      <c r="J143" t="s">
+        <v>31</v>
+      </c>
+      <c r="K143">
+        <v>107</v>
+      </c>
+      <c r="L143">
+        <v>509</v>
+      </c>
+      <c r="M143">
+        <v>32.246654999999997</v>
+      </c>
+      <c r="N143">
+        <v>0.759996</v>
+      </c>
+      <c r="O143">
+        <v>0.585318</v>
+      </c>
+      <c r="P143">
+        <v>0.98680199999999996</v>
+      </c>
+      <c r="X143" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="144" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>122</v>
+      </c>
+      <c r="B144" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D144" t="s">
+        <v>131</v>
+      </c>
+      <c r="E144" t="s">
+        <v>31</v>
+      </c>
+      <c r="F144" t="s">
+        <v>31</v>
+      </c>
+      <c r="G144">
+        <v>110</v>
+      </c>
+      <c r="H144">
+        <v>750</v>
+      </c>
+      <c r="I144" t="s">
+        <v>31</v>
+      </c>
+      <c r="J144" t="s">
+        <v>31</v>
+      </c>
+      <c r="K144">
+        <v>135</v>
+      </c>
+      <c r="L144">
+        <v>752</v>
+      </c>
+      <c r="M144">
+        <v>41.381534000000002</v>
+      </c>
+      <c r="N144">
+        <v>0.81698800000000005</v>
+      </c>
+      <c r="O144">
+        <v>0.64877600000000002</v>
+      </c>
+      <c r="P144">
+        <v>1.028813</v>
+      </c>
+      <c r="X144" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="145" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>122</v>
+      </c>
+      <c r="B145" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D145" t="s">
+        <v>127</v>
+      </c>
+      <c r="E145" t="s">
+        <v>31</v>
+      </c>
+      <c r="F145" t="s">
+        <v>31</v>
+      </c>
+      <c r="G145">
+        <v>35</v>
+      </c>
+      <c r="H145">
+        <v>50</v>
+      </c>
+      <c r="I145" t="s">
+        <v>31</v>
+      </c>
+      <c r="J145" t="s">
+        <v>31</v>
+      </c>
+      <c r="K145">
+        <v>35</v>
+      </c>
+      <c r="L145">
+        <v>49</v>
+      </c>
+      <c r="M145">
+        <v>16.772051999999999</v>
+      </c>
+      <c r="N145">
+        <v>0.98</v>
+      </c>
+      <c r="O145">
+        <v>0.76052299999999995</v>
+      </c>
+      <c r="P145">
+        <v>1.262815</v>
+      </c>
+      <c r="X145" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="146" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>122</v>
+      </c>
+      <c r="B146" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D146" t="s">
+        <v>128</v>
+      </c>
+      <c r="E146" t="s">
+        <v>31</v>
+      </c>
+      <c r="F146" t="s">
+        <v>31</v>
+      </c>
+      <c r="G146">
+        <v>7</v>
+      </c>
+      <c r="H146">
+        <v>142</v>
+      </c>
+      <c r="I146" t="s">
+        <v>31</v>
+      </c>
+      <c r="J146" t="s">
+        <v>31</v>
+      </c>
+      <c r="K146">
+        <v>8</v>
+      </c>
+      <c r="L146">
+        <v>142</v>
+      </c>
+      <c r="M146">
+        <v>1.1060099999999999</v>
+      </c>
+      <c r="N146">
+        <v>0.875</v>
+      </c>
+      <c r="O146">
+        <v>0.32599299999999998</v>
+      </c>
+      <c r="P146">
+        <v>2.348595</v>
+      </c>
+      <c r="X146" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="147" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>122</v>
+      </c>
+      <c r="B147" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D147" t="s">
+        <v>129</v>
+      </c>
+      <c r="E147" t="s">
+        <v>31</v>
+      </c>
+      <c r="F147" t="s">
+        <v>31</v>
+      </c>
+      <c r="G147">
+        <v>403</v>
+      </c>
+      <c r="H147">
+        <v>4148</v>
+      </c>
+      <c r="I147" t="s">
+        <v>31</v>
+      </c>
+      <c r="J147" t="s">
+        <v>31</v>
+      </c>
+      <c r="K147">
+        <v>393</v>
+      </c>
+      <c r="L147">
+        <v>4008</v>
+      </c>
+      <c r="M147">
+        <v>61.886274999999998</v>
+      </c>
+      <c r="N147">
+        <v>0.99083500000000002</v>
+      </c>
+      <c r="O147">
+        <v>0.86831499999999995</v>
+      </c>
+      <c r="P147">
+        <v>1.1306430000000001</v>
+      </c>
+      <c r="X147" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="148" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>122</v>
+      </c>
+      <c r="B148" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D148" t="s">
+        <v>131</v>
+      </c>
+      <c r="E148" t="s">
+        <v>31</v>
+      </c>
+      <c r="F148" t="s">
+        <v>31</v>
+      </c>
+      <c r="G148">
+        <v>119</v>
+      </c>
+      <c r="H148">
+        <v>750</v>
+      </c>
+      <c r="I148" t="s">
+        <v>31</v>
+      </c>
+      <c r="J148" t="s">
+        <v>31</v>
+      </c>
+      <c r="K148">
+        <v>123</v>
+      </c>
+      <c r="L148">
+        <v>752</v>
+      </c>
+      <c r="M148">
+        <v>20.235662999999999</v>
+      </c>
+      <c r="N148">
+        <v>0.97006000000000003</v>
+      </c>
+      <c r="O148">
+        <v>0.77010599999999996</v>
+      </c>
+      <c r="P148">
+        <v>1.22193</v>
+      </c>
+      <c r="X148" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="149" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>132</v>
+      </c>
+      <c r="B149" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D149" t="s">
+        <v>133</v>
+      </c>
+      <c r="E149" t="s">
+        <v>31</v>
+      </c>
+      <c r="F149" t="s">
+        <v>31</v>
+      </c>
+      <c r="G149">
+        <v>1</v>
+      </c>
+      <c r="H149">
+        <v>55</v>
+      </c>
+      <c r="I149" t="s">
+        <v>31</v>
+      </c>
+      <c r="J149" t="s">
+        <v>31</v>
+      </c>
+      <c r="K149">
+        <v>4</v>
+      </c>
+      <c r="L149">
+        <v>50</v>
+      </c>
+      <c r="M149">
+        <v>0.35464499999999999</v>
+      </c>
+      <c r="N149">
+        <v>0.227273</v>
+      </c>
+      <c r="O149">
+        <v>2.6273999999999999E-2</v>
+      </c>
+      <c r="P149">
+        <v>1.9659489999999999</v>
+      </c>
+      <c r="X149" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="150" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>132</v>
+      </c>
+      <c r="B150" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D150" t="s">
+        <v>79</v>
+      </c>
+      <c r="E150" t="s">
+        <v>31</v>
+      </c>
+      <c r="F150" t="s">
+        <v>31</v>
+      </c>
+      <c r="G150">
+        <v>1173</v>
+      </c>
+      <c r="H150">
+        <v>5610</v>
+      </c>
+      <c r="I150" t="s">
+        <v>31</v>
+      </c>
+      <c r="J150" t="s">
+        <v>31</v>
+      </c>
+      <c r="K150">
+        <v>1190</v>
+      </c>
+      <c r="L150">
+        <v>5730</v>
+      </c>
+      <c r="M150">
+        <v>99.645354999999995</v>
+      </c>
+      <c r="N150">
+        <v>1.006799</v>
+      </c>
+      <c r="O150">
+        <v>0.93709299999999995</v>
+      </c>
+      <c r="P150">
+        <v>1.08169</v>
+      </c>
+      <c r="X150" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="151" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>132</v>
+      </c>
+      <c r="B151" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D151" t="s">
+        <v>133</v>
+      </c>
+      <c r="E151" t="s">
+        <v>31</v>
+      </c>
+      <c r="F151" t="s">
+        <v>31</v>
+      </c>
+      <c r="G151">
+        <v>1</v>
+      </c>
+      <c r="H151">
+        <v>55</v>
+      </c>
+      <c r="I151" t="s">
+        <v>31</v>
+      </c>
+      <c r="J151" t="s">
+        <v>31</v>
+      </c>
+      <c r="K151">
+        <v>6</v>
+      </c>
+      <c r="L151">
+        <v>50</v>
+      </c>
+      <c r="M151">
+        <v>0.47136600000000001</v>
+      </c>
+      <c r="N151">
+        <v>0.15151500000000001</v>
+      </c>
+      <c r="O151">
+        <v>1.8890000000000001E-2</v>
+      </c>
+      <c r="P151">
+        <v>1.2153149999999999</v>
+      </c>
+      <c r="X151" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="152" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>132</v>
+      </c>
+      <c r="B152" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D152" t="s">
+        <v>79</v>
+      </c>
+      <c r="E152" t="s">
+        <v>31</v>
+      </c>
+      <c r="F152" t="s">
+        <v>31</v>
+      </c>
+      <c r="G152">
+        <v>1344</v>
+      </c>
+      <c r="H152">
+        <v>5342</v>
+      </c>
+      <c r="I152" t="s">
+        <v>31</v>
+      </c>
+      <c r="J152" t="s">
+        <v>31</v>
+      </c>
+      <c r="K152">
+        <v>1343</v>
+      </c>
+      <c r="L152">
+        <v>5469</v>
+      </c>
+      <c r="M152">
+        <v>99.528633999999997</v>
+      </c>
+      <c r="N152">
+        <v>1.0245359999999999</v>
+      </c>
+      <c r="O152">
+        <v>0.95952999999999999</v>
+      </c>
+      <c r="P152">
+        <v>1.093947</v>
+      </c>
+      <c r="X152" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="153" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>134</v>
+      </c>
+      <c r="B153" s="1">
+        <v>44805</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D153" t="s">
+        <v>135</v>
+      </c>
+      <c r="E153" t="s">
+        <v>31</v>
+      </c>
+      <c r="F153" t="s">
+        <v>31</v>
+      </c>
+      <c r="G153">
+        <v>0</v>
+      </c>
+      <c r="H153">
+        <v>80</v>
+      </c>
+      <c r="I153" t="s">
+        <v>31</v>
+      </c>
+      <c r="J153" t="s">
+        <v>31</v>
+      </c>
+      <c r="K153">
+        <v>0</v>
+      </c>
+      <c r="L153">
+        <v>72</v>
+      </c>
+      <c r="M153" t="s">
+        <v>31</v>
+      </c>
+      <c r="N153" t="s">
+        <v>31</v>
+      </c>
+      <c r="O153" t="s">
+        <v>31</v>
+      </c>
+      <c r="P153" t="s">
+        <v>31</v>
+      </c>
+      <c r="X153" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="154" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>134</v>
+      </c>
+      <c r="B154" s="1">
+        <v>44805</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D154" t="s">
+        <v>136</v>
+      </c>
+      <c r="E154" t="s">
+        <v>31</v>
+      </c>
+      <c r="F154" t="s">
+        <v>31</v>
+      </c>
+      <c r="G154">
+        <v>17</v>
+      </c>
+      <c r="H154">
+        <v>741</v>
+      </c>
+      <c r="I154" t="s">
+        <v>31</v>
+      </c>
+      <c r="J154" t="s">
+        <v>31</v>
+      </c>
+      <c r="K154">
+        <v>25</v>
+      </c>
+      <c r="L154">
+        <v>756</v>
+      </c>
+      <c r="M154">
+        <v>100</v>
+      </c>
+      <c r="N154">
+        <v>0.69376499999999997</v>
+      </c>
+      <c r="O154">
+        <v>0.377807</v>
+      </c>
+      <c r="P154">
+        <v>1.2739590000000001</v>
+      </c>
+      <c r="X154" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="155" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>134</v>
+      </c>
+      <c r="B155" s="1">
+        <v>44805</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D155" t="s">
+        <v>135</v>
+      </c>
+      <c r="E155" t="s">
+        <v>31</v>
+      </c>
+      <c r="F155" t="s">
+        <v>31</v>
+      </c>
+      <c r="G155">
+        <v>1</v>
+      </c>
+      <c r="H155">
+        <v>80</v>
+      </c>
+      <c r="I155" t="s">
+        <v>31</v>
+      </c>
+      <c r="J155" t="s">
+        <v>31</v>
+      </c>
+      <c r="K155">
+        <v>5</v>
+      </c>
+      <c r="L155">
+        <v>72</v>
+      </c>
+      <c r="M155">
+        <v>23.493390000000002</v>
+      </c>
+      <c r="N155">
+        <v>0.18</v>
+      </c>
+      <c r="O155">
+        <v>2.1534999999999999E-2</v>
+      </c>
+      <c r="P155">
+        <v>1.504553</v>
+      </c>
+      <c r="X155" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="156" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>134</v>
+      </c>
+      <c r="B156" s="1">
+        <v>44805</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D156" t="s">
+        <v>136</v>
+      </c>
+      <c r="E156" t="s">
+        <v>31</v>
+      </c>
+      <c r="F156" t="s">
+        <v>31</v>
+      </c>
+      <c r="G156">
+        <v>76</v>
+      </c>
+      <c r="H156">
+        <v>741</v>
+      </c>
+      <c r="I156" t="s">
+        <v>31</v>
+      </c>
+      <c r="J156" t="s">
+        <v>31</v>
+      </c>
+      <c r="K156">
+        <v>99</v>
+      </c>
+      <c r="L156">
+        <v>756</v>
+      </c>
+      <c r="M156">
+        <v>76.506609999999995</v>
+      </c>
+      <c r="N156">
+        <v>0.78321700000000005</v>
+      </c>
+      <c r="O156">
+        <v>0.59122300000000005</v>
+      </c>
+      <c r="P156">
+        <v>1.0375589999999999</v>
+      </c>
+      <c r="X156" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="157" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>134</v>
+      </c>
+      <c r="B157" s="1">
+        <v>44805</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D157" t="s">
+        <v>135</v>
+      </c>
+      <c r="E157" t="s">
+        <v>31</v>
+      </c>
+      <c r="F157" t="s">
+        <v>31</v>
+      </c>
+      <c r="G157">
+        <v>1</v>
+      </c>
+      <c r="H157">
+        <v>80</v>
+      </c>
+      <c r="I157" t="s">
+        <v>31</v>
+      </c>
+      <c r="J157" t="s">
+        <v>31</v>
+      </c>
+      <c r="K157">
+        <v>5</v>
+      </c>
+      <c r="L157">
+        <v>72</v>
+      </c>
+      <c r="M157">
+        <v>25.015528</v>
+      </c>
+      <c r="N157">
+        <v>0.18</v>
+      </c>
+      <c r="O157">
+        <v>2.1534999999999999E-2</v>
+      </c>
+      <c r="P157">
+        <v>1.504553</v>
+      </c>
+      <c r="X157" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="158" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>134</v>
+      </c>
+      <c r="B158" s="1">
+        <v>44805</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D158" t="s">
+        <v>136</v>
+      </c>
+      <c r="E158" t="s">
+        <v>31</v>
+      </c>
+      <c r="F158" t="s">
+        <v>31</v>
+      </c>
+      <c r="G158">
+        <v>77</v>
+      </c>
+      <c r="H158">
+        <v>741</v>
+      </c>
+      <c r="I158" t="s">
+        <v>31</v>
+      </c>
+      <c r="J158" t="s">
+        <v>31</v>
+      </c>
+      <c r="K158">
+        <v>96</v>
+      </c>
+      <c r="L158">
+        <v>756</v>
+      </c>
+      <c r="M158">
+        <v>74.984471999999997</v>
+      </c>
+      <c r="N158">
+        <v>0.81832000000000005</v>
+      </c>
+      <c r="O158">
+        <v>0.61711199999999999</v>
+      </c>
+      <c r="P158">
+        <v>1.085132</v>
+      </c>
+      <c r="X158" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="159" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>134</v>
+      </c>
+      <c r="B159" s="1">
+        <v>44805</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D159" t="s">
+        <v>135</v>
+      </c>
+      <c r="E159" t="s">
+        <v>31</v>
+      </c>
+      <c r="F159" t="s">
+        <v>31</v>
+      </c>
+      <c r="G159">
+        <v>11</v>
+      </c>
+      <c r="H159">
+        <v>80</v>
+      </c>
+      <c r="I159" t="s">
+        <v>31</v>
+      </c>
+      <c r="J159" t="s">
+        <v>31</v>
+      </c>
+      <c r="K159">
+        <v>6</v>
+      </c>
+      <c r="L159">
+        <v>72</v>
+      </c>
+      <c r="M159">
+        <v>7.619008</v>
+      </c>
+      <c r="N159">
+        <v>1.65</v>
+      </c>
+      <c r="O159">
+        <v>0.64299899999999999</v>
+      </c>
+      <c r="P159">
+        <v>4.2340679999999997</v>
+      </c>
+      <c r="X159" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="160" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>134</v>
+      </c>
+      <c r="B160" s="1">
+        <v>44805</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D160" t="s">
+        <v>136</v>
+      </c>
+      <c r="E160" t="s">
+        <v>31</v>
+      </c>
+      <c r="F160" t="s">
+        <v>31</v>
+      </c>
+      <c r="G160">
+        <v>92</v>
+      </c>
+      <c r="H160">
+        <v>741</v>
+      </c>
+      <c r="I160" t="s">
+        <v>31</v>
+      </c>
+      <c r="J160" t="s">
+        <v>31</v>
+      </c>
+      <c r="K160">
+        <v>92</v>
+      </c>
+      <c r="L160">
+        <v>756</v>
+      </c>
+      <c r="M160">
+        <v>92.380992000000006</v>
+      </c>
+      <c r="N160">
+        <v>1.020243</v>
+      </c>
+      <c r="O160">
+        <v>0.77833600000000003</v>
+      </c>
+      <c r="P160">
+        <v>1.337334</v>
+      </c>
+      <c r="X160" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="161" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>137</v>
+      </c>
+      <c r="B161" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D161" t="s">
+        <v>139</v>
+      </c>
+      <c r="E161" t="s">
+        <v>31</v>
+      </c>
+      <c r="F161" t="s">
+        <v>31</v>
+      </c>
+      <c r="G161">
+        <v>5</v>
+      </c>
+      <c r="H161">
+        <v>172</v>
+      </c>
+      <c r="I161" t="s">
+        <v>31</v>
+      </c>
+      <c r="J161" t="s">
+        <v>31</v>
+      </c>
+      <c r="K161">
+        <v>7</v>
+      </c>
+      <c r="L161">
+        <v>159</v>
+      </c>
+      <c r="M161">
+        <v>0.54324799999999995</v>
+      </c>
+      <c r="N161">
+        <v>0.66029899999999997</v>
+      </c>
+      <c r="O161">
+        <v>0.213897</v>
+      </c>
+      <c r="P161">
+        <v>2.038341</v>
+      </c>
+      <c r="X161" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="162" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>137</v>
+      </c>
+      <c r="B162" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D162" t="s">
+        <v>140</v>
+      </c>
+      <c r="E162" t="s">
+        <v>31</v>
+      </c>
+      <c r="F162" t="s">
+        <v>31</v>
+      </c>
+      <c r="G162">
+        <v>0</v>
+      </c>
+      <c r="H162">
+        <v>56</v>
+      </c>
+      <c r="I162" t="s">
+        <v>31</v>
+      </c>
+      <c r="J162" t="s">
+        <v>31</v>
+      </c>
+      <c r="K162">
+        <v>1</v>
+      </c>
+      <c r="L162">
+        <v>55</v>
+      </c>
+      <c r="M162">
+        <v>6.8287E-2</v>
+      </c>
+      <c r="N162">
+        <v>0.32748500000000003</v>
+      </c>
+      <c r="O162">
+        <v>1.3627999999999999E-2</v>
+      </c>
+      <c r="P162">
+        <v>7.8693879999999998</v>
+      </c>
+      <c r="X162" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="163" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>137</v>
+      </c>
+      <c r="B163" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D163" t="s">
+        <v>141</v>
+      </c>
+      <c r="E163" t="s">
+        <v>31</v>
+      </c>
+      <c r="F163" t="s">
+        <v>31</v>
+      </c>
+      <c r="G163">
+        <v>90</v>
+      </c>
+      <c r="H163">
+        <v>212</v>
+      </c>
+      <c r="I163" t="s">
+        <v>31</v>
+      </c>
+      <c r="J163" t="s">
+        <v>31</v>
+      </c>
+      <c r="K163">
+        <v>73</v>
+      </c>
+      <c r="L163">
+        <v>183</v>
+      </c>
+      <c r="M163">
+        <v>12.283155000000001</v>
+      </c>
+      <c r="N163">
+        <v>1.064228</v>
+      </c>
+      <c r="O163">
+        <v>0.83962300000000001</v>
+      </c>
+      <c r="P163">
+        <v>1.3489180000000001</v>
+      </c>
+      <c r="X163" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="164" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>137</v>
+      </c>
+      <c r="B164" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D164" t="s">
+        <v>142</v>
+      </c>
+      <c r="E164" t="s">
+        <v>31</v>
+      </c>
+      <c r="F164" t="s">
+        <v>31</v>
+      </c>
+      <c r="G164">
+        <v>561</v>
+      </c>
+      <c r="H164">
+        <v>2582</v>
+      </c>
+      <c r="I164" t="s">
+        <v>31</v>
+      </c>
+      <c r="J164" t="s">
+        <v>31</v>
+      </c>
+      <c r="K164">
+        <v>1162</v>
+      </c>
+      <c r="L164">
+        <v>5181</v>
+      </c>
+      <c r="M164">
+        <v>87.105310000000003</v>
+      </c>
+      <c r="N164">
+        <v>0.96875500000000003</v>
+      </c>
+      <c r="O164">
+        <v>0.88624599999999998</v>
+      </c>
+      <c r="P164">
+        <v>1.0589470000000001</v>
+      </c>
+      <c r="X164" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="165" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>137</v>
+      </c>
+      <c r="B165" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D165" t="s">
+        <v>143</v>
+      </c>
+      <c r="E165" t="s">
+        <v>31</v>
+      </c>
+      <c r="F165" t="s">
+        <v>31</v>
+      </c>
+      <c r="G165">
+        <v>7</v>
+      </c>
+      <c r="H165">
+        <v>7</v>
+      </c>
+      <c r="I165" t="s">
+        <v>31</v>
+      </c>
+      <c r="J165" t="s">
+        <v>31</v>
+      </c>
+      <c r="K165">
+        <v>7</v>
+      </c>
+      <c r="L165">
+        <v>7</v>
+      </c>
+      <c r="M165">
+        <v>20.535216999999999</v>
+      </c>
+      <c r="N165">
+        <v>1</v>
+      </c>
+      <c r="O165">
+        <v>0.77644400000000002</v>
+      </c>
+      <c r="P165">
+        <v>1.287922</v>
+      </c>
+      <c r="X165" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="166" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>137</v>
+      </c>
+      <c r="B166" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D166" t="s">
+        <v>141</v>
+      </c>
+      <c r="E166" t="s">
+        <v>31</v>
+      </c>
+      <c r="F166" t="s">
+        <v>31</v>
+      </c>
+      <c r="G166">
+        <v>69</v>
+      </c>
+      <c r="H166">
+        <v>212</v>
+      </c>
+      <c r="I166" t="s">
+        <v>31</v>
+      </c>
+      <c r="J166" t="s">
+        <v>31</v>
+      </c>
+      <c r="K166">
+        <v>76</v>
+      </c>
+      <c r="L166">
+        <v>183</v>
+      </c>
+      <c r="M166">
+        <v>19.897371</v>
+      </c>
+      <c r="N166">
+        <v>0.78370200000000001</v>
+      </c>
+      <c r="O166">
+        <v>0.60484800000000005</v>
+      </c>
+      <c r="P166">
+        <v>1.015442</v>
+      </c>
+      <c r="X166" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="167" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>137</v>
+      </c>
+      <c r="B167" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D167" t="s">
+        <v>142</v>
+      </c>
+      <c r="E167" t="s">
+        <v>31</v>
+      </c>
+      <c r="F167" t="s">
+        <v>31</v>
+      </c>
+      <c r="G167">
+        <v>1788</v>
+      </c>
+      <c r="H167">
+        <v>2582</v>
+      </c>
+      <c r="I167" t="s">
+        <v>31</v>
+      </c>
+      <c r="J167" t="s">
+        <v>31</v>
+      </c>
+      <c r="K167">
+        <v>3525</v>
+      </c>
+      <c r="L167">
+        <v>5181</v>
+      </c>
+      <c r="M167">
+        <v>59.567411</v>
+      </c>
+      <c r="N167">
+        <v>1.017808</v>
+      </c>
+      <c r="O167">
+        <v>0.985985</v>
+      </c>
+      <c r="P167">
+        <v>1.050657</v>
+      </c>
+      <c r="X167" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="168" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>137</v>
+      </c>
+      <c r="B168" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D168" t="s">
+        <v>143</v>
+      </c>
+      <c r="E168" t="s">
+        <v>31</v>
+      </c>
+      <c r="F168" t="s">
+        <v>31</v>
+      </c>
+      <c r="G168">
+        <v>0</v>
+      </c>
+      <c r="H168">
+        <v>7</v>
+      </c>
+      <c r="I168" t="s">
+        <v>31</v>
+      </c>
+      <c r="J168" t="s">
+        <v>31</v>
+      </c>
+      <c r="K168">
+        <v>1</v>
+      </c>
+      <c r="L168">
+        <v>7</v>
+      </c>
+      <c r="M168">
+        <v>0.55913400000000002</v>
+      </c>
+      <c r="N168">
+        <v>0.33333299999999999</v>
+      </c>
+      <c r="O168">
+        <v>1.5835999999999999E-2</v>
+      </c>
+      <c r="P168">
+        <v>7.0165769999999998</v>
+      </c>
+      <c r="X168" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="169" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>137</v>
+      </c>
+      <c r="B169" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D169" t="s">
+        <v>139</v>
+      </c>
+      <c r="E169" t="s">
+        <v>31</v>
+      </c>
+      <c r="F169" t="s">
+        <v>31</v>
+      </c>
+      <c r="G169">
+        <v>3</v>
+      </c>
+      <c r="H169">
+        <v>172</v>
+      </c>
+      <c r="I169" t="s">
+        <v>31</v>
+      </c>
+      <c r="J169" t="s">
+        <v>31</v>
+      </c>
+      <c r="K169">
+        <v>2</v>
+      </c>
+      <c r="L169">
+        <v>159</v>
+      </c>
+      <c r="M169">
+        <v>1.6453869999999999</v>
+      </c>
+      <c r="N169">
+        <v>1.386628</v>
+      </c>
+      <c r="O169">
+        <v>0.23474</v>
+      </c>
+      <c r="P169">
+        <v>8.1909379999999992</v>
+      </c>
+      <c r="X169" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="170" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>137</v>
+      </c>
+      <c r="B170" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D170" t="s">
+        <v>144</v>
+      </c>
+      <c r="E170" t="s">
+        <v>31</v>
+      </c>
+      <c r="F170" t="s">
+        <v>31</v>
+      </c>
+      <c r="G170">
+        <v>1</v>
+      </c>
+      <c r="H170">
+        <v>5</v>
+      </c>
+      <c r="I170" t="s">
+        <v>31</v>
+      </c>
+      <c r="J170" t="s">
+        <v>31</v>
+      </c>
+      <c r="K170">
+        <v>1</v>
+      </c>
+      <c r="L170">
+        <v>5</v>
+      </c>
+      <c r="M170">
+        <v>0.844526</v>
+      </c>
+      <c r="N170">
+        <v>1</v>
+      </c>
+      <c r="O170">
+        <v>8.3811999999999998E-2</v>
+      </c>
+      <c r="P170">
+        <v>11.931478</v>
+      </c>
+      <c r="X170" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="171" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>137</v>
+      </c>
+      <c r="B171" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D171" t="s">
+        <v>141</v>
+      </c>
+      <c r="E171" t="s">
+        <v>31</v>
+      </c>
+      <c r="F171" t="s">
+        <v>31</v>
+      </c>
+      <c r="G171">
+        <v>102</v>
+      </c>
+      <c r="H171">
+        <v>241</v>
+      </c>
+      <c r="I171" t="s">
+        <v>31</v>
+      </c>
+      <c r="J171" t="s">
+        <v>31</v>
+      </c>
+      <c r="K171">
+        <v>75</v>
+      </c>
+      <c r="L171">
+        <v>198</v>
+      </c>
+      <c r="M171">
+        <v>96.950952000000001</v>
+      </c>
+      <c r="N171">
+        <v>1.1173439999999999</v>
+      </c>
+      <c r="O171">
+        <v>0.88653700000000002</v>
+      </c>
+      <c r="P171">
+        <v>1.4082410000000001</v>
+      </c>
+      <c r="X171" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="172" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>137</v>
+      </c>
+      <c r="B172" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D172" t="s">
+        <v>143</v>
+      </c>
+      <c r="E172" t="s">
+        <v>31</v>
+      </c>
+      <c r="F172" t="s">
+        <v>31</v>
+      </c>
+      <c r="G172">
+        <v>5</v>
+      </c>
+      <c r="H172">
+        <v>7</v>
+      </c>
+      <c r="I172" t="s">
+        <v>31</v>
+      </c>
+      <c r="J172" t="s">
+        <v>31</v>
+      </c>
+      <c r="K172">
+        <v>4</v>
+      </c>
+      <c r="L172">
+        <v>7</v>
+      </c>
+      <c r="M172">
+        <v>11.465146000000001</v>
+      </c>
+      <c r="N172">
+        <v>1.25</v>
+      </c>
+      <c r="O172">
+        <v>0.56480600000000003</v>
+      </c>
+      <c r="P172">
+        <v>2.766435</v>
+      </c>
+      <c r="X172" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="173" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>137</v>
+      </c>
+      <c r="B173" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D173" t="s">
+        <v>139</v>
+      </c>
+      <c r="E173" t="s">
+        <v>31</v>
+      </c>
+      <c r="F173" t="s">
+        <v>31</v>
+      </c>
+      <c r="G173">
+        <v>68</v>
+      </c>
+      <c r="H173">
+        <v>172</v>
+      </c>
+      <c r="I173" t="s">
+        <v>31</v>
+      </c>
+      <c r="J173" t="s">
+        <v>31</v>
+      </c>
+      <c r="K173">
+        <v>53</v>
+      </c>
+      <c r="L173">
+        <v>159</v>
+      </c>
+      <c r="M173">
+        <v>87.727614000000003</v>
+      </c>
+      <c r="N173">
+        <v>1.1860470000000001</v>
+      </c>
+      <c r="O173">
+        <v>0.88997300000000001</v>
+      </c>
+      <c r="P173">
+        <v>1.5806180000000001</v>
+      </c>
+      <c r="X173" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="174" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>137</v>
+      </c>
+      <c r="B174" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D174" t="s">
+        <v>144</v>
+      </c>
+      <c r="E174" t="s">
+        <v>31</v>
+      </c>
+      <c r="F174" t="s">
+        <v>31</v>
+      </c>
+      <c r="G174">
+        <v>1</v>
+      </c>
+      <c r="H174">
+        <v>5</v>
+      </c>
+      <c r="I174" t="s">
+        <v>31</v>
+      </c>
+      <c r="J174" t="s">
+        <v>31</v>
+      </c>
+      <c r="K174">
+        <v>0</v>
+      </c>
+      <c r="L174">
+        <v>5</v>
+      </c>
+      <c r="M174">
+        <v>0.80723999999999996</v>
+      </c>
+      <c r="N174">
+        <v>3</v>
+      </c>
+      <c r="O174">
+        <v>0.15027599999999999</v>
+      </c>
+      <c r="P174">
+        <v>59.889831000000001</v>
+      </c>
+      <c r="X174" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="175" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>137</v>
+      </c>
+      <c r="B175" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D175" t="s">
+        <v>139</v>
+      </c>
+      <c r="E175" t="s">
+        <v>31</v>
+      </c>
+      <c r="F175" t="s">
+        <v>31</v>
+      </c>
+      <c r="G175">
+        <v>1</v>
+      </c>
+      <c r="H175">
+        <v>172</v>
+      </c>
+      <c r="I175" t="s">
+        <v>31</v>
+      </c>
+      <c r="J175" t="s">
+        <v>31</v>
+      </c>
+      <c r="K175">
+        <v>2</v>
+      </c>
+      <c r="L175">
+        <v>159</v>
+      </c>
+      <c r="M175">
+        <v>0.87591200000000002</v>
+      </c>
+      <c r="N175">
+        <v>0.46220899999999998</v>
+      </c>
+      <c r="O175">
+        <v>4.2320000000000003E-2</v>
+      </c>
+      <c r="P175">
+        <v>5.0481119999999997</v>
+      </c>
+      <c r="X175" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="176" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>137</v>
+      </c>
+      <c r="B176" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D176" t="s">
+        <v>140</v>
+      </c>
+      <c r="E176" t="s">
+        <v>31</v>
+      </c>
+      <c r="F176" t="s">
+        <v>31</v>
+      </c>
+      <c r="G176">
+        <v>0</v>
+      </c>
+      <c r="H176">
+        <v>56</v>
+      </c>
+      <c r="I176" t="s">
+        <v>31</v>
+      </c>
+      <c r="J176" t="s">
+        <v>31</v>
+      </c>
+      <c r="K176">
+        <v>0</v>
+      </c>
+      <c r="L176">
+        <v>55</v>
+      </c>
+      <c r="M176" t="s">
+        <v>31</v>
+      </c>
+      <c r="N176" t="s">
+        <v>31</v>
+      </c>
+      <c r="O176" t="s">
+        <v>31</v>
+      </c>
+      <c r="P176" t="s">
+        <v>31</v>
+      </c>
+      <c r="X176" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="177" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>137</v>
+      </c>
+      <c r="B177" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D177" t="s">
+        <v>141</v>
+      </c>
+      <c r="E177" t="s">
+        <v>31</v>
+      </c>
+      <c r="F177" t="s">
+        <v>31</v>
+      </c>
+      <c r="G177">
+        <v>8</v>
+      </c>
+      <c r="H177">
+        <v>241</v>
+      </c>
+      <c r="I177" t="s">
+        <v>31</v>
+      </c>
+      <c r="J177" t="s">
+        <v>31</v>
+      </c>
+      <c r="K177">
+        <v>5</v>
+      </c>
+      <c r="L177">
+        <v>198</v>
+      </c>
+      <c r="M177">
+        <v>4.1268700000000003</v>
+      </c>
+      <c r="N177">
+        <v>1.3145230000000001</v>
+      </c>
+      <c r="O177">
+        <v>0.436944</v>
+      </c>
+      <c r="P177">
+        <v>3.954669</v>
+      </c>
+      <c r="X177" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="178" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>137</v>
+      </c>
+      <c r="B178" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D178" t="s">
+        <v>142</v>
+      </c>
+      <c r="E178" t="s">
+        <v>31</v>
+      </c>
+      <c r="F178" t="s">
+        <v>31</v>
+      </c>
+      <c r="G178">
+        <v>101</v>
+      </c>
+      <c r="H178">
+        <v>2314</v>
+      </c>
+      <c r="I178" t="s">
+        <v>31</v>
+      </c>
+      <c r="J178" t="s">
+        <v>31</v>
+      </c>
+      <c r="K178">
+        <v>224</v>
+      </c>
+      <c r="L178">
+        <v>4670</v>
+      </c>
+      <c r="M178">
+        <v>94.997219000000001</v>
+      </c>
+      <c r="N178">
+        <v>0.90996999999999995</v>
+      </c>
+      <c r="O178">
+        <v>0.72331500000000004</v>
+      </c>
+      <c r="P178">
+        <v>1.144792</v>
+      </c>
+      <c r="X178" t="s">
         <v>22</v>
       </c>
     </row>
@@ -6757,12 +11011,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E6B89F4-E48E-4E03-B88F-4C83697BDFFF}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.08984375" customWidth="1"/>
     <col min="5" max="5" width="14.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.36328125" bestFit="1" customWidth="1"/>
@@ -6947,10 +11201,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c r="B7" s="1">
-        <v>44958</v>
+        <v>44470</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>95</v>
@@ -6959,7 +11213,7 @@
         <v>2</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -6976,19 +11230,19 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c r="B8" s="1">
-        <v>44317</v>
+        <v>44470</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -7011,7 +11265,7 @@
         <v>44958</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D9" s="2">
         <v>2</v>
@@ -7037,10 +11291,10 @@
         <v>35</v>
       </c>
       <c r="B10" s="1">
-        <v>44958</v>
+        <v>44317</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D10" s="2">
         <v>2</v>
@@ -7066,10 +11320,10 @@
         <v>35</v>
       </c>
       <c r="B11" s="1">
-        <v>44317</v>
+        <v>44958</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D11" s="2">
         <v>2</v>
@@ -7084,10 +11338,10 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -7098,7 +11352,7 @@
         <v>44958</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D12" s="2">
         <v>2</v>
@@ -7113,7 +11367,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -7121,60 +11375,60 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1">
-        <v>44713</v>
+        <v>44317</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D13" s="2">
         <v>2</v>
       </c>
       <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <v>1</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
       <c r="I13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="B14" s="1">
-        <v>44378</v>
+        <v>44958</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D14" s="2">
         <v>2</v>
       </c>
       <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
         <v>1</v>
       </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
       <c r="I14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
@@ -7185,7 +11439,7 @@
         <v>44713</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D15" s="2">
         <v>2</v>
@@ -7211,10 +11465,10 @@
         <v>60</v>
       </c>
       <c r="B16" s="1">
-        <v>44713</v>
+        <v>44378</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -7232,7 +11486,7 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -7243,7 +11497,7 @@
         <v>44713</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -7261,21 +11515,21 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B18" s="1">
-        <v>44287</v>
+        <v>44713</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D18" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -7290,53 +11544,53 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B19" s="1">
-        <v>44287</v>
+        <v>44713</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D19" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
         <v>1</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B20" s="1">
-        <v>44927</v>
+        <v>44287</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D20" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -7348,27 +11602,27 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B21" s="1">
-        <v>44927</v>
+        <v>44287</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>94</v>
       </c>
       <c r="D21" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -7377,24 +11631,24 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="B22" s="1">
-        <v>44927</v>
+        <v>44470</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D22" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -7411,22 +11665,22 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="B23" s="1">
-        <v>44409</v>
+        <v>44470</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D23" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -7440,16 +11694,16 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="B24" s="1">
-        <v>44409</v>
+        <v>44470</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="D24" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -7469,16 +11723,16 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B25" s="1">
-        <v>44866</v>
+        <v>44470</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D25" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -7498,22 +11752,22 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="B26" s="1">
-        <v>44866</v>
+        <v>44927</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D26" s="2">
         <v>2</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -7523,6 +11777,673 @@
       </c>
       <c r="I26">
         <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" s="1">
+        <v>44927</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="2">
+        <v>2</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>72</v>
+      </c>
+      <c r="B28" s="1">
+        <v>44927</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" s="2">
+        <v>2</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" s="1">
+        <v>44409</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" s="2">
+        <v>2</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="1">
+        <v>44409</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" s="2">
+        <v>2</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" s="1">
+        <v>44866</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="2">
+        <v>2</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="1">
+        <v>44866</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" s="2">
+        <v>2</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>116</v>
+      </c>
+      <c r="B33" s="1">
+        <v>44621</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D33" s="2">
+        <v>2</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>116</v>
+      </c>
+      <c r="B34" s="1">
+        <v>44621</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D34" s="2">
+        <v>2</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>116</v>
+      </c>
+      <c r="B35" s="1">
+        <v>44621</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D35" s="2">
+        <v>2</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>122</v>
+      </c>
+      <c r="B36" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D36" s="2">
+        <v>2</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>122</v>
+      </c>
+      <c r="B37" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D37" s="2">
+        <v>2</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>122</v>
+      </c>
+      <c r="B38" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D38" s="2">
+        <v>2</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>122</v>
+      </c>
+      <c r="B39" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D39" s="2">
+        <v>2</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>122</v>
+      </c>
+      <c r="B40" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D40" s="2">
+        <v>2</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>134</v>
+      </c>
+      <c r="B41" s="1">
+        <v>44805</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D41" s="2">
+        <v>2</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>134</v>
+      </c>
+      <c r="B42" s="1">
+        <v>44805</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D42" s="2">
+        <v>2</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>134</v>
+      </c>
+      <c r="B43" s="1">
+        <v>44805</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D43" s="2">
+        <v>2</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>134</v>
+      </c>
+      <c r="B44" s="1">
+        <v>44805</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D44" s="2">
+        <v>2</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>137</v>
+      </c>
+      <c r="B45" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D45" s="2">
+        <v>2</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>137</v>
+      </c>
+      <c r="B46" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D46" s="2">
+        <v>2</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>137</v>
+      </c>
+      <c r="B47" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D47" s="2">
+        <v>2</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>137</v>
+      </c>
+      <c r="B48" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" s="2">
+        <v>2</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>137</v>
+      </c>
+      <c r="B49" s="1">
+        <v>44470</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D49" s="2">
+        <v>2</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Datasets/primary_info.xlsx
+++ b/Datasets/primary_info.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniofleicester-my.sharepoint.com/personal/crn4_leicester_ac_uk/Documents/PhD/WP2/3. Create tool/Datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="420" documentId="13_ncr:1_{009773F8-B678-42EB-90F1-9F0C232CDCBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{907FD90A-E196-465D-9806-713BC011015B}"/>
+  <xr:revisionPtr revIDLastSave="428" documentId="13_ncr:1_{009773F8-B678-42EB-90F1-9F0C232CDCBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7AC4BA5-6815-43AA-ABB9-2837077CCF59}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{E19E56DC-86BE-4713-A769-C66B74D62B61}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{E19E56DC-86BE-4713-A769-C66B74D62B61}"/>
   </bookViews>
   <sheets>
     <sheet name="Studies" sheetId="1" r:id="rId1"/>
     <sheet name="GRADE" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Studies!$A$1:$X$178</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1146,7 +1149,7 @@
         <v>44317</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
         <v>36</v>
@@ -1158,10 +1161,10 @@
         <v>31</v>
       </c>
       <c r="G5">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="I5" t="s">
         <v>31</v>
@@ -1170,22 +1173,10 @@
         <v>31</v>
       </c>
       <c r="K5">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>229</v>
-      </c>
-      <c r="M5">
-        <v>1.527301</v>
-      </c>
-      <c r="N5">
-        <v>1.0687709999999999</v>
-      </c>
-      <c r="O5">
-        <v>0.68051099999999998</v>
-      </c>
-      <c r="P5">
-        <v>1.67855</v>
+        <v>224</v>
       </c>
       <c r="X5" t="s">
         <v>58</v>
@@ -1199,7 +1190,7 @@
         <v>44317</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
         <v>37</v>
@@ -1211,7 +1202,7 @@
         <v>31</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>20</v>
@@ -1223,22 +1214,10 @@
         <v>31</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <v>20</v>
-      </c>
-      <c r="M6">
-        <v>5.8058999999999999E-2</v>
-      </c>
-      <c r="N6">
-        <v>0.5</v>
-      </c>
-      <c r="O6">
-        <v>4.9182999999999998E-2</v>
-      </c>
-      <c r="P6">
-        <v>5.0830599999999997</v>
       </c>
       <c r="X6" t="s">
         <v>58</v>
@@ -1252,10 +1231,10 @@
         <v>44317</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
         <v>31</v>
@@ -1264,10 +1243,10 @@
         <v>31</v>
       </c>
       <c r="G7">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="H7">
-        <v>179</v>
+        <v>228</v>
       </c>
       <c r="I7" t="s">
         <v>31</v>
@@ -1276,22 +1255,22 @@
         <v>31</v>
       </c>
       <c r="K7">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="L7">
-        <v>171</v>
+        <v>105</v>
       </c>
       <c r="M7">
-        <v>0.40039599999999997</v>
+        <v>88.5</v>
       </c>
       <c r="N7">
-        <v>0.47765400000000002</v>
+        <v>0.877193</v>
       </c>
       <c r="O7">
-        <v>0.197579</v>
+        <v>0.54556800000000005</v>
       </c>
       <c r="P7">
-        <v>1.154744</v>
+        <v>1.4103969999999999</v>
       </c>
       <c r="X7" t="s">
         <v>22</v>
@@ -1302,13 +1281,13 @@
         <v>35</v>
       </c>
       <c r="B8" s="1">
-        <v>44958</v>
+        <v>44317</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
         <v>31</v>
@@ -1317,10 +1296,10 @@
         <v>31</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I8" t="s">
         <v>31</v>
@@ -1329,25 +1308,25 @@
         <v>31</v>
       </c>
       <c r="K8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L8">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="M8">
-        <v>0.115594</v>
+        <v>11.5</v>
       </c>
       <c r="N8">
-        <v>0.54901999999999995</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="O8">
-        <v>0.10613400000000001</v>
+        <v>0.3</v>
       </c>
       <c r="P8">
-        <v>2.8400099999999999</v>
+        <v>4.22</v>
       </c>
       <c r="X8" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.35">
@@ -1358,10 +1337,10 @@
         <v>44958</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
         <v>31</v>
@@ -1370,10 +1349,10 @@
         <v>31</v>
       </c>
       <c r="G9">
-        <v>10</v>
+        <v>171</v>
       </c>
       <c r="H9">
-        <v>69</v>
+        <v>228</v>
       </c>
       <c r="I9" t="s">
         <v>31</v>
@@ -1382,22 +1361,22 @@
         <v>31</v>
       </c>
       <c r="K9">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="L9">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="M9">
-        <v>0.415265</v>
+        <v>3.500273</v>
       </c>
       <c r="N9">
-        <v>1.213768</v>
+        <v>0.984375</v>
       </c>
       <c r="O9">
-        <v>0.51014700000000002</v>
+        <v>0.86388100000000001</v>
       </c>
       <c r="P9">
-        <v>2.8878629999999998</v>
+        <v>1.1216759999999999</v>
       </c>
       <c r="X9" t="s">
         <v>22</v>
@@ -1411,10 +1390,10 @@
         <v>44958</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
         <v>31</v>
@@ -1423,10 +1402,10 @@
         <v>31</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="H10">
-        <v>257</v>
+        <v>51</v>
       </c>
       <c r="I10" t="s">
         <v>31</v>
@@ -1435,25 +1414,25 @@
         <v>31</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="L10">
-        <v>254</v>
+        <v>50</v>
       </c>
       <c r="M10">
-        <v>6.8178000000000002E-2</v>
+        <v>0.28551799999999999</v>
       </c>
       <c r="N10">
-        <v>4.9416339999999996</v>
+        <v>1.4161220000000001</v>
       </c>
       <c r="O10">
-        <v>0.58139600000000002</v>
+        <v>0.89650200000000002</v>
       </c>
       <c r="P10">
-        <v>42.001891000000001</v>
+        <v>2.2369180000000002</v>
       </c>
       <c r="X10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
@@ -1464,10 +1443,10 @@
         <v>44958</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
         <v>31</v>
@@ -1476,10 +1455,10 @@
         <v>31</v>
       </c>
       <c r="G11">
-        <v>14</v>
+        <v>257</v>
       </c>
       <c r="H11">
-        <v>231</v>
+        <v>320</v>
       </c>
       <c r="I11" t="s">
         <v>31</v>
@@ -1488,22 +1467,22 @@
         <v>31</v>
       </c>
       <c r="K11">
-        <v>19</v>
+        <v>130</v>
       </c>
       <c r="L11">
-        <v>240</v>
+        <v>163</v>
       </c>
       <c r="M11">
-        <v>0.70235199999999998</v>
+        <v>6.6862830000000004</v>
       </c>
       <c r="N11">
-        <v>0.76554999999999995</v>
+        <v>1.0069950000000001</v>
       </c>
       <c r="O11">
-        <v>0.39319599999999999</v>
+        <v>0.91621699999999995</v>
       </c>
       <c r="P11">
-        <v>1.4905200000000001</v>
+        <v>1.106768</v>
       </c>
       <c r="X11" t="s">
         <v>22</v>
@@ -1514,26 +1493,26 @@
         <v>35</v>
       </c>
       <c r="B12" s="1">
-        <v>44317</v>
+        <v>44958</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12">
+        <v>31</v>
+      </c>
+      <c r="H12">
         <v>43</v>
       </c>
-      <c r="E12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12">
-        <v>25</v>
-      </c>
-      <c r="H12">
-        <v>228</v>
-      </c>
       <c r="I12" t="s">
         <v>31</v>
       </c>
@@ -1541,25 +1520,25 @@
         <v>31</v>
       </c>
       <c r="K12">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="L12">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="M12">
-        <v>0.74170499999999995</v>
+        <v>0.72387299999999999</v>
       </c>
       <c r="N12">
-        <v>0.95943000000000001</v>
+        <v>1.107143</v>
       </c>
       <c r="O12">
-        <v>0.50169799999999998</v>
+        <v>0.83082</v>
       </c>
       <c r="P12">
-        <v>1.834781</v>
+        <v>1.475368</v>
       </c>
       <c r="X12" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.35">
@@ -1570,10 +1549,10 @@
         <v>44958</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E13" t="s">
         <v>31</v>
@@ -1582,10 +1561,10 @@
         <v>31</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>3832</v>
       </c>
       <c r="H13">
-        <v>40</v>
+        <v>5795</v>
       </c>
       <c r="I13" t="s">
         <v>31</v>
@@ -1594,25 +1573,25 @@
         <v>31</v>
       </c>
       <c r="K13">
-        <v>10</v>
+        <v>3822</v>
       </c>
       <c r="L13">
-        <v>39</v>
+        <v>5763</v>
       </c>
       <c r="M13">
-        <v>0.147929</v>
+        <v>88.006018999999995</v>
       </c>
       <c r="N13">
-        <v>0.19500000000000001</v>
+        <v>0.99707999999999997</v>
       </c>
       <c r="O13">
-        <v>4.5617999999999999E-2</v>
+        <v>0.97145099999999995</v>
       </c>
       <c r="P13">
-        <v>0.83355599999999996</v>
+        <v>1.023385</v>
       </c>
       <c r="X13" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.35">
@@ -1623,10 +1602,10 @@
         <v>44958</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
         <v>31</v>
@@ -1635,10 +1614,10 @@
         <v>31</v>
       </c>
       <c r="G14">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="H14">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="I14" t="s">
         <v>31</v>
@@ -1647,25 +1626,25 @@
         <v>31</v>
       </c>
       <c r="K14">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="L14">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="M14">
-        <v>0.58537700000000004</v>
+        <v>0.79803299999999999</v>
       </c>
       <c r="N14">
-        <v>0.87654299999999996</v>
+        <v>0.95652199999999998</v>
       </c>
       <c r="O14">
-        <v>0.42244700000000002</v>
+        <v>0.72766799999999998</v>
       </c>
       <c r="P14">
-        <v>1.818754</v>
+        <v>1.25735</v>
       </c>
       <c r="X14" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.35">
@@ -1673,13 +1652,13 @@
         <v>35</v>
       </c>
       <c r="B15" s="1">
-        <v>44958</v>
+        <v>44317</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s">
         <v>31</v>
@@ -1688,10 +1667,10 @@
         <v>31</v>
       </c>
       <c r="G15">
-        <v>352</v>
+        <v>34</v>
       </c>
       <c r="H15">
-        <v>1074</v>
+        <v>235</v>
       </c>
       <c r="I15" t="s">
         <v>31</v>
@@ -1700,25 +1679,25 @@
         <v>31</v>
       </c>
       <c r="K15">
-        <v>300</v>
+        <v>31</v>
       </c>
       <c r="L15">
-        <v>904</v>
+        <v>229</v>
       </c>
       <c r="M15">
-        <v>18.837778</v>
+        <v>1.527301</v>
       </c>
       <c r="N15">
-        <v>0.98760999999999999</v>
+        <v>1.0687709999999999</v>
       </c>
       <c r="O15">
-        <v>0.87063699999999999</v>
+        <v>0.68051099999999998</v>
       </c>
       <c r="P15">
-        <v>1.1202989999999999</v>
+        <v>1.67855</v>
       </c>
       <c r="X15" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.35">
@@ -1732,7 +1711,7 @@
         <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E16" t="s">
         <v>31</v>
@@ -1741,10 +1720,10 @@
         <v>31</v>
       </c>
       <c r="G16">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="I16" t="s">
         <v>31</v>
@@ -1753,25 +1732,25 @@
         <v>31</v>
       </c>
       <c r="K16">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L16">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="M16">
-        <v>0.48129300000000003</v>
+        <v>5.8058999999999999E-2</v>
       </c>
       <c r="N16">
-        <v>0.65359500000000004</v>
+        <v>0.5</v>
       </c>
       <c r="O16">
-        <v>0.29219099999999998</v>
+        <v>4.9182999999999998E-2</v>
       </c>
       <c r="P16">
-        <v>1.462008</v>
+        <v>5.0830599999999997</v>
       </c>
       <c r="X16" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.35">
@@ -1779,13 +1758,13 @@
         <v>35</v>
       </c>
       <c r="B17" s="1">
-        <v>44958</v>
+        <v>44317</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>95</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E17" t="s">
         <v>31</v>
@@ -1794,10 +1773,10 @@
         <v>31</v>
       </c>
       <c r="G17">
-        <v>141</v>
+        <v>7</v>
       </c>
       <c r="H17">
-        <v>614</v>
+        <v>179</v>
       </c>
       <c r="I17" t="s">
         <v>31</v>
@@ -1806,22 +1785,22 @@
         <v>31</v>
       </c>
       <c r="K17">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="L17">
-        <v>307</v>
+        <v>171</v>
       </c>
       <c r="M17">
-        <v>4.4525050000000004</v>
+        <v>0.40039599999999997</v>
       </c>
       <c r="N17">
-        <v>1.119048</v>
+        <v>0.47765400000000002</v>
       </c>
       <c r="O17">
-        <v>0.85979899999999998</v>
+        <v>0.197579</v>
       </c>
       <c r="P17">
-        <v>1.456466</v>
+        <v>1.154744</v>
       </c>
       <c r="X17" t="s">
         <v>22</v>
@@ -1832,13 +1811,13 @@
         <v>35</v>
       </c>
       <c r="B18" s="1">
-        <v>44958</v>
+        <v>44317</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>95</v>
       </c>
       <c r="D18" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E18" t="s">
         <v>31</v>
@@ -1847,10 +1826,10 @@
         <v>31</v>
       </c>
       <c r="G18">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H18">
-        <v>320</v>
+        <v>228</v>
       </c>
       <c r="I18" t="s">
         <v>31</v>
@@ -1859,22 +1838,22 @@
         <v>31</v>
       </c>
       <c r="K18">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L18">
-        <v>163</v>
+        <v>105</v>
       </c>
       <c r="M18">
-        <v>0.83953800000000001</v>
+        <v>0.74170499999999995</v>
       </c>
       <c r="N18">
-        <v>1.055134</v>
+        <v>0.95943000000000001</v>
       </c>
       <c r="O18">
-        <v>0.57369300000000001</v>
+        <v>0.50169799999999998</v>
       </c>
       <c r="P18">
-        <v>1.9406000000000001</v>
+        <v>1.834781</v>
       </c>
       <c r="X18" t="s">
         <v>22</v>
@@ -1885,52 +1864,52 @@
         <v>35</v>
       </c>
       <c r="B19" s="1">
-        <v>44958</v>
+        <v>44317</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>95</v>
       </c>
       <c r="D19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19">
+        <v>8</v>
+      </c>
+      <c r="H19">
+        <v>51</v>
+      </c>
+      <c r="I19" t="s">
+        <v>31</v>
+      </c>
+      <c r="J19" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19">
+        <v>12</v>
+      </c>
+      <c r="L19">
         <v>50</v>
       </c>
-      <c r="E19" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19">
-        <v>6</v>
-      </c>
-      <c r="H19">
-        <v>43</v>
-      </c>
-      <c r="I19" t="s">
-        <v>31</v>
-      </c>
-      <c r="J19" t="s">
-        <v>31</v>
-      </c>
-      <c r="K19">
-        <v>11</v>
-      </c>
-      <c r="L19">
-        <v>43</v>
-      </c>
       <c r="M19">
-        <v>0.38482899999999998</v>
+        <v>0.48129300000000003</v>
       </c>
       <c r="N19">
-        <v>0.54545500000000002</v>
+        <v>0.65359500000000004</v>
       </c>
       <c r="O19">
-        <v>0.221667</v>
+        <v>0.29219099999999998</v>
       </c>
       <c r="P19">
-        <v>1.3421940000000001</v>
+        <v>1.462008</v>
       </c>
       <c r="X19" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.35">
@@ -1991,13 +1970,13 @@
         <v>35</v>
       </c>
       <c r="B21" s="1">
-        <v>44958</v>
+        <v>44317</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>95</v>
       </c>
       <c r="D21" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E21" t="s">
         <v>31</v>
@@ -2006,10 +1985,10 @@
         <v>31</v>
       </c>
       <c r="G21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H21">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="I21" t="s">
         <v>31</v>
@@ -2021,22 +2000,22 @@
         <v>14</v>
       </c>
       <c r="L21">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="M21">
-        <v>0.51285800000000004</v>
+        <v>0.66848399999999997</v>
       </c>
       <c r="N21">
-        <v>0.56064700000000001</v>
+        <v>0.71428599999999998</v>
       </c>
       <c r="O21">
-        <v>0.25703399999999998</v>
+        <v>0.360792</v>
       </c>
       <c r="P21">
-        <v>1.222893</v>
+        <v>1.4141220000000001</v>
       </c>
       <c r="X21" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.35">
@@ -2050,7 +2029,7 @@
         <v>95</v>
       </c>
       <c r="D22" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="E22" t="s">
         <v>31</v>
@@ -2059,10 +2038,10 @@
         <v>31</v>
       </c>
       <c r="G22">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>462</v>
+        <v>17</v>
       </c>
       <c r="I22" t="s">
         <v>31</v>
@@ -2071,25 +2050,25 @@
         <v>31</v>
       </c>
       <c r="K22">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="L22">
-        <v>462</v>
+        <v>14</v>
       </c>
       <c r="M22">
-        <v>3.0239199999999999</v>
+        <v>0.115594</v>
       </c>
       <c r="N22">
-        <v>0.830986</v>
+        <v>0.54901999999999995</v>
       </c>
       <c r="O22">
-        <v>0.60324500000000003</v>
+        <v>0.10613400000000001</v>
       </c>
       <c r="P22">
-        <v>1.1447039999999999</v>
+        <v>2.8400099999999999</v>
       </c>
       <c r="X22" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.35">
@@ -2097,13 +2076,13 @@
         <v>35</v>
       </c>
       <c r="B23" s="1">
-        <v>44317</v>
+        <v>44958</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>95</v>
       </c>
       <c r="D23" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="E23" t="s">
         <v>31</v>
@@ -2115,7 +2094,7 @@
         <v>10</v>
       </c>
       <c r="H23">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="I23" t="s">
         <v>31</v>
@@ -2124,25 +2103,25 @@
         <v>31</v>
       </c>
       <c r="K23">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L23">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="M23">
-        <v>0.66848399999999997</v>
+        <v>0.415265</v>
       </c>
       <c r="N23">
-        <v>0.71428599999999998</v>
+        <v>1.213768</v>
       </c>
       <c r="O23">
-        <v>0.360792</v>
+        <v>0.51014700000000002</v>
       </c>
       <c r="P23">
-        <v>1.4141220000000001</v>
+        <v>2.8878629999999998</v>
       </c>
       <c r="X23" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.35">
@@ -2156,7 +2135,7 @@
         <v>95</v>
       </c>
       <c r="D24" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="E24" t="s">
         <v>31</v>
@@ -2165,10 +2144,10 @@
         <v>31</v>
       </c>
       <c r="G24">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H24">
-        <v>80</v>
+        <v>257</v>
       </c>
       <c r="I24" t="s">
         <v>31</v>
@@ -2177,25 +2156,25 @@
         <v>31</v>
       </c>
       <c r="K24">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="M24">
-        <v>0.755104</v>
+        <v>6.8178000000000002E-2</v>
       </c>
       <c r="N24">
-        <v>1.3846149999999999</v>
+        <v>4.9416339999999996</v>
       </c>
       <c r="O24">
-        <v>0.72823499999999997</v>
+        <v>0.58139600000000002</v>
       </c>
       <c r="P24">
-        <v>2.6326100000000001</v>
+        <v>42.001891000000001</v>
       </c>
       <c r="X24" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.35">
@@ -2209,7 +2188,7 @@
         <v>95</v>
       </c>
       <c r="D25" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="E25" t="s">
         <v>31</v>
@@ -2218,10 +2197,10 @@
         <v>31</v>
       </c>
       <c r="G25">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H25">
-        <v>52</v>
+        <v>231</v>
       </c>
       <c r="I25" t="s">
         <v>31</v>
@@ -2230,22 +2209,22 @@
         <v>31</v>
       </c>
       <c r="K25">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="L25">
-        <v>51</v>
+        <v>240</v>
       </c>
       <c r="M25">
-        <v>0.62933399999999995</v>
+        <v>0.70235199999999998</v>
       </c>
       <c r="N25">
-        <v>0.82988200000000001</v>
+        <v>0.76554999999999995</v>
       </c>
       <c r="O25">
-        <v>0.41048899999999999</v>
+        <v>0.39319599999999999</v>
       </c>
       <c r="P25">
-        <v>1.677764</v>
+        <v>1.4905200000000001</v>
       </c>
       <c r="X25" t="s">
         <v>22</v>
@@ -4367,10 +4346,10 @@
         <v>44958</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D60" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E60" t="s">
         <v>31</v>
@@ -4379,10 +4358,10 @@
         <v>31</v>
       </c>
       <c r="G60">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="H60">
-        <v>235</v>
+        <v>40</v>
       </c>
       <c r="I60" t="s">
         <v>31</v>
@@ -4391,25 +4370,25 @@
         <v>31</v>
       </c>
       <c r="K60">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="L60">
-        <v>229</v>
+        <v>39</v>
       </c>
       <c r="M60">
-        <v>3.0132330000000001</v>
+        <v>0.147929</v>
       </c>
       <c r="N60">
-        <v>1.045771</v>
+        <v>0.19500000000000001</v>
       </c>
       <c r="O60">
-        <v>0.71191599999999999</v>
+        <v>4.5617999999999999E-2</v>
       </c>
       <c r="P60">
-        <v>1.5361880000000001</v>
+        <v>0.83355599999999996</v>
       </c>
       <c r="X60" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.35">
@@ -4420,10 +4399,10 @@
         <v>44958</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D61" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E61" t="s">
         <v>31</v>
@@ -4435,7 +4414,7 @@
         <v>8</v>
       </c>
       <c r="H61">
-        <v>257</v>
+        <v>36</v>
       </c>
       <c r="I61" t="s">
         <v>31</v>
@@ -4444,22 +4423,22 @@
         <v>31</v>
       </c>
       <c r="K61">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="L61">
-        <v>254</v>
+        <v>71</v>
       </c>
       <c r="M61">
-        <v>0.26425199999999999</v>
+        <v>0.58537700000000004</v>
       </c>
       <c r="N61">
-        <v>2.6355379999999999</v>
+        <v>0.87654299999999996</v>
       </c>
       <c r="O61">
-        <v>0.70720499999999997</v>
+        <v>0.42244700000000002</v>
       </c>
       <c r="P61">
-        <v>9.821847</v>
+        <v>1.818754</v>
       </c>
       <c r="X61" t="s">
         <v>58</v>
@@ -4473,10 +4452,10 @@
         <v>44958</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D62" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E62" t="s">
         <v>31</v>
@@ -4485,10 +4464,10 @@
         <v>31</v>
       </c>
       <c r="G62">
-        <v>44</v>
+        <v>352</v>
       </c>
       <c r="H62">
-        <v>228</v>
+        <v>1074</v>
       </c>
       <c r="I62" t="s">
         <v>31</v>
@@ -4497,22 +4476,22 @@
         <v>31</v>
       </c>
       <c r="K62">
-        <v>22</v>
+        <v>300</v>
       </c>
       <c r="L62">
-        <v>105</v>
+        <v>904</v>
       </c>
       <c r="M62">
-        <v>2.154855</v>
+        <v>18.837778</v>
       </c>
       <c r="N62">
-        <v>0.92105300000000001</v>
+        <v>0.98760999999999999</v>
       </c>
       <c r="O62">
-        <v>0.583426</v>
+        <v>0.87063699999999999</v>
       </c>
       <c r="P62">
-        <v>1.454064</v>
+        <v>1.1202989999999999</v>
       </c>
       <c r="X62" t="s">
         <v>22</v>
@@ -4526,10 +4505,10 @@
         <v>44958</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D63" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E63" t="s">
         <v>31</v>
@@ -4538,10 +4517,10 @@
         <v>31</v>
       </c>
       <c r="G63">
-        <v>347</v>
+        <v>141</v>
       </c>
       <c r="H63">
-        <v>701</v>
+        <v>614</v>
       </c>
       <c r="I63" t="s">
         <v>31</v>
@@ -4550,25 +4529,25 @@
         <v>31</v>
       </c>
       <c r="K63">
-        <v>275</v>
+        <v>63</v>
       </c>
       <c r="L63">
-        <v>606</v>
+        <v>307</v>
       </c>
       <c r="M63">
-        <v>26.219619999999999</v>
+        <v>4.4525050000000004</v>
       </c>
       <c r="N63">
-        <v>1.090816</v>
+        <v>1.119048</v>
       </c>
       <c r="O63">
-        <v>0.97233599999999998</v>
+        <v>0.85979899999999998</v>
       </c>
       <c r="P63">
-        <v>1.223733</v>
+        <v>1.456466</v>
       </c>
       <c r="X63" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.35">
@@ -4579,10 +4558,10 @@
         <v>44958</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D64" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E64" t="s">
         <v>31</v>
@@ -4591,10 +4570,10 @@
         <v>31</v>
       </c>
       <c r="G64">
-        <v>199</v>
+        <v>29</v>
       </c>
       <c r="H64">
-        <v>614</v>
+        <v>320</v>
       </c>
       <c r="I64" t="s">
         <v>31</v>
@@ -4603,22 +4582,22 @@
         <v>31</v>
       </c>
       <c r="K64">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="L64">
-        <v>307</v>
+        <v>163</v>
       </c>
       <c r="M64">
-        <v>9.2676479999999994</v>
+        <v>0.83953800000000001</v>
       </c>
       <c r="N64">
-        <v>1.1569769999999999</v>
+        <v>1.055134</v>
       </c>
       <c r="O64">
-        <v>0.93538299999999996</v>
+        <v>0.57369300000000001</v>
       </c>
       <c r="P64">
-        <v>1.4310659999999999</v>
+        <v>1.9406000000000001</v>
       </c>
       <c r="X64" t="s">
         <v>22</v>
@@ -4632,10 +4611,10 @@
         <v>44958</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D65" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E65" t="s">
         <v>31</v>
@@ -4644,10 +4623,10 @@
         <v>31</v>
       </c>
       <c r="G65">
-        <v>1568</v>
+        <v>6</v>
       </c>
       <c r="H65">
-        <v>5493</v>
+        <v>43</v>
       </c>
       <c r="I65" t="s">
         <v>31</v>
@@ -4656,25 +4635,25 @@
         <v>31</v>
       </c>
       <c r="K65">
-        <v>1568</v>
+        <v>11</v>
       </c>
       <c r="L65">
-        <v>5448</v>
+        <v>43</v>
       </c>
       <c r="M65">
-        <v>59.080393000000001</v>
+        <v>0.38482899999999998</v>
       </c>
       <c r="N65">
-        <v>0.99180800000000002</v>
+        <v>0.54545500000000002</v>
       </c>
       <c r="O65">
-        <v>0.93486999999999998</v>
+        <v>0.221667</v>
       </c>
       <c r="P65">
-        <v>1.0522130000000001</v>
+        <v>1.3421940000000001</v>
       </c>
       <c r="X65" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66" spans="1:24" x14ac:dyDescent="0.35">
@@ -4685,10 +4664,10 @@
         <v>44958</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D66" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E66" t="s">
         <v>31</v>
@@ -4697,10 +4676,10 @@
         <v>31</v>
       </c>
       <c r="G66">
-        <v>171</v>
+        <v>8</v>
       </c>
       <c r="H66">
-        <v>228</v>
+        <v>53</v>
       </c>
       <c r="I66" t="s">
         <v>31</v>
@@ -4709,22 +4688,22 @@
         <v>31</v>
       </c>
       <c r="K66">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="L66">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="M66">
-        <v>3.500273</v>
+        <v>0.51285800000000004</v>
       </c>
       <c r="N66">
-        <v>0.984375</v>
+        <v>0.56064700000000001</v>
       </c>
       <c r="O66">
-        <v>0.86388100000000001</v>
+        <v>0.25703399999999998</v>
       </c>
       <c r="P66">
-        <v>1.1216759999999999</v>
+        <v>1.222893</v>
       </c>
       <c r="X66" t="s">
         <v>22</v>
@@ -4738,10 +4717,10 @@
         <v>44958</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D67" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E67" t="s">
         <v>31</v>
@@ -4750,10 +4729,10 @@
         <v>31</v>
       </c>
       <c r="G67">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="H67">
-        <v>51</v>
+        <v>462</v>
       </c>
       <c r="I67" t="s">
         <v>31</v>
@@ -4762,22 +4741,22 @@
         <v>31</v>
       </c>
       <c r="K67">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="L67">
-        <v>50</v>
+        <v>462</v>
       </c>
       <c r="M67">
-        <v>0.28551799999999999</v>
+        <v>3.0239199999999999</v>
       </c>
       <c r="N67">
-        <v>1.4161220000000001</v>
+        <v>0.830986</v>
       </c>
       <c r="O67">
-        <v>0.89650200000000002</v>
+        <v>0.60324500000000003</v>
       </c>
       <c r="P67">
-        <v>2.2369180000000002</v>
+        <v>1.1447039999999999</v>
       </c>
       <c r="X67" t="s">
         <v>22</v>
@@ -4791,10 +4770,10 @@
         <v>44958</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D68" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E68" t="s">
         <v>31</v>
@@ -4803,10 +4782,10 @@
         <v>31</v>
       </c>
       <c r="G68">
-        <v>257</v>
+        <v>18</v>
       </c>
       <c r="H68">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="I68" t="s">
         <v>31</v>
@@ -4815,22 +4794,22 @@
         <v>31</v>
       </c>
       <c r="K68">
-        <v>130</v>
+        <v>13</v>
       </c>
       <c r="L68">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="M68">
-        <v>6.6862830000000004</v>
+        <v>0.755104</v>
       </c>
       <c r="N68">
-        <v>1.0069950000000001</v>
+        <v>1.3846149999999999</v>
       </c>
       <c r="O68">
-        <v>0.91621699999999995</v>
+        <v>0.72823499999999997</v>
       </c>
       <c r="P68">
-        <v>1.106768</v>
+        <v>2.6326100000000001</v>
       </c>
       <c r="X68" t="s">
         <v>22</v>
@@ -4844,10 +4823,10 @@
         <v>44958</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D69" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E69" t="s">
         <v>31</v>
@@ -4856,10 +4835,10 @@
         <v>31</v>
       </c>
       <c r="G69">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="H69">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="I69" t="s">
         <v>31</v>
@@ -4868,25 +4847,25 @@
         <v>31</v>
       </c>
       <c r="K69">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="L69">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="M69">
-        <v>0.72387299999999999</v>
+        <v>0.62933399999999995</v>
       </c>
       <c r="N69">
-        <v>1.107143</v>
+        <v>0.82988200000000001</v>
       </c>
       <c r="O69">
-        <v>0.83082</v>
+        <v>0.41048899999999999</v>
       </c>
       <c r="P69">
-        <v>1.475368</v>
+        <v>1.677764</v>
       </c>
       <c r="X69" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.35">
@@ -4897,10 +4876,10 @@
         <v>44958</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D70" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E70" t="s">
         <v>31</v>
@@ -4909,10 +4888,10 @@
         <v>31</v>
       </c>
       <c r="G70">
-        <v>3832</v>
+        <v>54</v>
       </c>
       <c r="H70">
-        <v>5795</v>
+        <v>228</v>
       </c>
       <c r="I70" t="s">
         <v>31</v>
@@ -4921,22 +4900,22 @@
         <v>31</v>
       </c>
       <c r="K70">
-        <v>3822</v>
+        <v>19</v>
       </c>
       <c r="L70">
-        <v>5763</v>
+        <v>105</v>
       </c>
       <c r="M70">
-        <v>88.006018999999995</v>
+        <v>14.914524999999999</v>
       </c>
       <c r="N70">
-        <v>0.99707999999999997</v>
+        <v>1.308864</v>
       </c>
       <c r="O70">
-        <v>0.97145099999999995</v>
+        <v>0.81892699999999996</v>
       </c>
       <c r="P70">
-        <v>1.023385</v>
+        <v>2.0919159999999999</v>
       </c>
       <c r="X70" t="s">
         <v>22</v>
@@ -4950,10 +4929,10 @@
         <v>44958</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D71" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="E71" t="s">
         <v>31</v>
@@ -4962,10 +4941,10 @@
         <v>31</v>
       </c>
       <c r="G71">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="H71">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I71" t="s">
         <v>31</v>
@@ -4974,25 +4953,25 @@
         <v>31</v>
       </c>
       <c r="K71">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="L71">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="M71">
-        <v>0.79803299999999999</v>
+        <v>10.218532</v>
       </c>
       <c r="N71">
-        <v>0.95652199999999998</v>
+        <v>0.78</v>
       </c>
       <c r="O71">
-        <v>0.72766799999999998</v>
+        <v>0.42051899999999998</v>
       </c>
       <c r="P71">
-        <v>1.25735</v>
+        <v>1.446785</v>
       </c>
       <c r="X71" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.35">
@@ -5000,13 +4979,13 @@
         <v>35</v>
       </c>
       <c r="B72" s="1">
-        <v>44317</v>
+        <v>44958</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D72" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E72" t="s">
         <v>31</v>
@@ -5015,10 +4994,10 @@
         <v>31</v>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="H72">
-        <v>227</v>
+        <v>614</v>
       </c>
       <c r="I72" t="s">
         <v>31</v>
@@ -5027,13 +5006,25 @@
         <v>31</v>
       </c>
       <c r="K72">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="L72">
-        <v>224</v>
+        <v>307</v>
+      </c>
+      <c r="M72">
+        <v>29.240273999999999</v>
+      </c>
+      <c r="N72">
+        <v>1.2654319999999999</v>
+      </c>
+      <c r="O72">
+        <v>1.017868</v>
+      </c>
+      <c r="P72">
+        <v>1.5732090000000001</v>
       </c>
       <c r="X72" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="73" spans="1:24" x14ac:dyDescent="0.35">
@@ -5041,13 +5032,13 @@
         <v>35</v>
       </c>
       <c r="B73" s="1">
-        <v>44317</v>
+        <v>44958</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D73" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E73" t="s">
         <v>31</v>
@@ -5056,10 +5047,10 @@
         <v>31</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H73">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="I73" t="s">
         <v>31</v>
@@ -5068,10 +5059,22 @@
         <v>31</v>
       </c>
       <c r="K73">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L73">
-        <v>20</v>
+        <v>163</v>
+      </c>
+      <c r="M73">
+        <v>19.607727000000001</v>
+      </c>
+      <c r="N73">
+        <v>0.98878699999999997</v>
+      </c>
+      <c r="O73">
+        <v>0.68417799999999995</v>
+      </c>
+      <c r="P73">
+        <v>1.429014</v>
       </c>
       <c r="X73" t="s">
         <v>58</v>
@@ -5082,13 +5085,13 @@
         <v>35</v>
       </c>
       <c r="B74" s="1">
-        <v>44317</v>
+        <v>44958</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D74" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E74" t="s">
         <v>31</v>
@@ -5097,10 +5100,10 @@
         <v>31</v>
       </c>
       <c r="G74">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H74">
-        <v>228</v>
+        <v>1075</v>
       </c>
       <c r="I74" t="s">
         <v>31</v>
@@ -5109,25 +5112,25 @@
         <v>31</v>
       </c>
       <c r="K74">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="L74">
-        <v>105</v>
+        <v>905</v>
       </c>
       <c r="M74">
-        <v>88.5</v>
+        <v>9.301444</v>
       </c>
       <c r="N74">
-        <v>0.877193</v>
+        <v>2.244961</v>
       </c>
       <c r="O74">
-        <v>0.54556800000000005</v>
+        <v>1.163178</v>
       </c>
       <c r="P74">
-        <v>1.4103969999999999</v>
+        <v>4.3328290000000003</v>
       </c>
       <c r="X74" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
     </row>
     <row r="75" spans="1:24" x14ac:dyDescent="0.35">
@@ -5135,13 +5138,13 @@
         <v>35</v>
       </c>
       <c r="B75" s="1">
-        <v>44317</v>
+        <v>44958</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D75" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="E75" t="s">
         <v>31</v>
@@ -5150,10 +5153,10 @@
         <v>31</v>
       </c>
       <c r="G75">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H75">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="I75" t="s">
         <v>31</v>
@@ -5162,25 +5165,25 @@
         <v>31</v>
       </c>
       <c r="K75">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="L75">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="M75">
-        <v>11.5</v>
+        <v>16.717497999999999</v>
       </c>
       <c r="N75">
-        <v>1.1299999999999999</v>
+        <v>0.86339600000000005</v>
       </c>
       <c r="O75">
-        <v>0.3</v>
+        <v>0.563608</v>
       </c>
       <c r="P75">
-        <v>4.22</v>
+        <v>1.322646</v>
       </c>
       <c r="X75" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
     </row>
     <row r="76" spans="1:24" x14ac:dyDescent="0.35">
@@ -5191,10 +5194,10 @@
         <v>44958</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D76" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E76" t="s">
         <v>31</v>
@@ -5203,10 +5206,10 @@
         <v>31</v>
       </c>
       <c r="G76">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="H76">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="I76" t="s">
         <v>31</v>
@@ -5215,25 +5218,25 @@
         <v>31</v>
       </c>
       <c r="K76">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="L76">
-        <v>105</v>
+        <v>229</v>
       </c>
       <c r="M76">
-        <v>14.914524999999999</v>
+        <v>3.0132330000000001</v>
       </c>
       <c r="N76">
-        <v>1.308864</v>
+        <v>1.045771</v>
       </c>
       <c r="O76">
-        <v>0.81892699999999996</v>
+        <v>0.71191599999999999</v>
       </c>
       <c r="P76">
-        <v>2.0919159999999999</v>
+        <v>1.5361880000000001</v>
       </c>
       <c r="X76" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
     </row>
     <row r="77" spans="1:24" x14ac:dyDescent="0.35">
@@ -5244,10 +5247,10 @@
         <v>44958</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D77" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E77" t="s">
         <v>31</v>
@@ -5256,10 +5259,10 @@
         <v>31</v>
       </c>
       <c r="G77">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H77">
-        <v>40</v>
+        <v>257</v>
       </c>
       <c r="I77" t="s">
         <v>31</v>
@@ -5268,25 +5271,25 @@
         <v>31</v>
       </c>
       <c r="K77">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L77">
-        <v>39</v>
+        <v>254</v>
       </c>
       <c r="M77">
-        <v>10.218532</v>
+        <v>0.26425199999999999</v>
       </c>
       <c r="N77">
-        <v>0.78</v>
+        <v>2.6355379999999999</v>
       </c>
       <c r="O77">
-        <v>0.42051899999999998</v>
+        <v>0.70720499999999997</v>
       </c>
       <c r="P77">
-        <v>1.446785</v>
+        <v>9.821847</v>
       </c>
       <c r="X77" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78" spans="1:24" x14ac:dyDescent="0.35">
@@ -5297,10 +5300,10 @@
         <v>44958</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D78" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E78" t="s">
         <v>31</v>
@@ -5309,10 +5312,10 @@
         <v>31</v>
       </c>
       <c r="G78">
-        <v>205</v>
+        <v>44</v>
       </c>
       <c r="H78">
-        <v>614</v>
+        <v>228</v>
       </c>
       <c r="I78" t="s">
         <v>31</v>
@@ -5321,25 +5324,25 @@
         <v>31</v>
       </c>
       <c r="K78">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="L78">
-        <v>307</v>
+        <v>105</v>
       </c>
       <c r="M78">
-        <v>29.240273999999999</v>
+        <v>2.154855</v>
       </c>
       <c r="N78">
-        <v>1.2654319999999999</v>
+        <v>0.92105300000000001</v>
       </c>
       <c r="O78">
-        <v>1.017868</v>
+        <v>0.583426</v>
       </c>
       <c r="P78">
-        <v>1.5732090000000001</v>
+        <v>1.454064</v>
       </c>
       <c r="X78" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.35">
@@ -5350,10 +5353,10 @@
         <v>44958</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D79" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E79" t="s">
         <v>31</v>
@@ -5362,10 +5365,10 @@
         <v>31</v>
       </c>
       <c r="G79">
-        <v>66</v>
+        <v>347</v>
       </c>
       <c r="H79">
-        <v>320</v>
+        <v>701</v>
       </c>
       <c r="I79" t="s">
         <v>31</v>
@@ -5374,25 +5377,25 @@
         <v>31</v>
       </c>
       <c r="K79">
-        <v>34</v>
+        <v>275</v>
       </c>
       <c r="L79">
-        <v>163</v>
+        <v>606</v>
       </c>
       <c r="M79">
-        <v>19.607727000000001</v>
+        <v>26.219619999999999</v>
       </c>
       <c r="N79">
-        <v>0.98878699999999997</v>
+        <v>1.090816</v>
       </c>
       <c r="O79">
-        <v>0.68417799999999995</v>
+        <v>0.97233599999999998</v>
       </c>
       <c r="P79">
-        <v>1.429014</v>
+        <v>1.223733</v>
       </c>
       <c r="X79" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80" spans="1:24" x14ac:dyDescent="0.35">
@@ -5403,10 +5406,10 @@
         <v>44958</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D80" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E80" t="s">
         <v>31</v>
@@ -5415,10 +5418,10 @@
         <v>31</v>
       </c>
       <c r="G80">
-        <v>32</v>
+        <v>199</v>
       </c>
       <c r="H80">
-        <v>1075</v>
+        <v>614</v>
       </c>
       <c r="I80" t="s">
         <v>31</v>
@@ -5427,25 +5430,25 @@
         <v>31</v>
       </c>
       <c r="K80">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="L80">
-        <v>905</v>
+        <v>307</v>
       </c>
       <c r="M80">
-        <v>9.301444</v>
+        <v>9.2676479999999994</v>
       </c>
       <c r="N80">
-        <v>2.244961</v>
+        <v>1.1569769999999999</v>
       </c>
       <c r="O80">
-        <v>1.163178</v>
+        <v>0.93538299999999996</v>
       </c>
       <c r="P80">
-        <v>4.3328290000000003</v>
+        <v>1.4310659999999999</v>
       </c>
       <c r="X80" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81" spans="1:24" x14ac:dyDescent="0.35">
@@ -5456,10 +5459,10 @@
         <v>44958</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D81" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E81" t="s">
         <v>31</v>
@@ -5468,10 +5471,10 @@
         <v>31</v>
       </c>
       <c r="G81">
-        <v>22</v>
+        <v>1568</v>
       </c>
       <c r="H81">
-        <v>53</v>
+        <v>5493</v>
       </c>
       <c r="I81" t="s">
         <v>31</v>
@@ -5480,25 +5483,25 @@
         <v>31</v>
       </c>
       <c r="K81">
-        <v>25</v>
+        <v>1568</v>
       </c>
       <c r="L81">
-        <v>52</v>
+        <v>5448</v>
       </c>
       <c r="M81">
-        <v>16.717497999999999</v>
+        <v>59.080393000000001</v>
       </c>
       <c r="N81">
-        <v>0.86339600000000005</v>
+        <v>0.99180800000000002</v>
       </c>
       <c r="O81">
-        <v>0.563608</v>
+        <v>0.93486999999999998</v>
       </c>
       <c r="P81">
-        <v>1.322646</v>
+        <v>1.0522130000000001</v>
       </c>
       <c r="X81" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82" spans="1:24" x14ac:dyDescent="0.35">
